--- a/GearSage-client/pkgGear/data_raw/olympic_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/olympic_rod_import.xlsx
@@ -54,8 +54,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyFill="1"/>
@@ -464,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,50 +529,55 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>fit_style_tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>images</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>series_positioning</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>main_selling_points</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>official_reference_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>market_status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>player_positioning</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>player_selling_points</t>
         </is>
@@ -588,40 +617,45 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/olympic_rods/OR1000_20_VIGORE.jpg</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>強靭かつ繊細に！進化した「ビゴーレ」。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>51,000 / 51,500 / 52,000 / 52,500 / 49,000</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>強靭かつ繊細に！進化した「ビゴーレ」。 今回のビゴーレは広大なフィールドに合わせ、バスを探していくためのキャスタビリティ、アプローチが困難なスポットに打ち込めるロングレングスモデルを中心にリニューアル。それぞれの釣法に対しブランクス、グリップデザイン、ガイドセッティングを拘り、機能性を突き詰めました。ブランクスには全アイテム、オリムピックの「G-MAPS製法」はもちろん。メイン材料に東レ「トレカ®T1100G」を採用。ガイドには各アイテム毎に使用用途に最も適したガイドを配置。チタンフレームトルザイトリングガイドを採用し（77XHを除く）飛距離・感度を徹底的に追及しました。</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>淡水 Bass / VIGORE / cover・巻物・大餌・PE遠投</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>cover、巻物、big bait 與 PE 遠投分工清楚 / 適合按技法選擇槍柄或直柄型號</t>
         </is>
@@ -661,40 +695,45 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/olympic_rods/OR1001_21_VELOCE_UX.jpg</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>強靭ビゴーレの血を引くベローチェUX</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>23,500 / 24,000 / 24,500 / 25,000 / 25,500 / 25,200</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>強靭ビゴーレの血を引くベローチェUX 名作ベローチェがUXシリーズで復活。おかっぱり、ボート問わず幅広いシーンで活躍するラインナップを用意し、本気の一歩を支えます。全番手ステンレスSiC-SリングKガイドを採用。“これさえあれば安心”アイテムから“かゆいところに手が届く”アイテムに至るまで徹底的にタフフィールドで鍛えこまれた実釣性能。ベローチェUXに死角なし。</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>淡水 Bass / VELOCE UX / 泛用打撃・cover・大餌・power finesse</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>cover、精細、遠投與大餌分工明確 / 入門主力線也能按技法和線組負荷選型</t>
         </is>
@@ -734,40 +773,45 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>溪流</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/olympic_rods/OR1002_18_Super_Bellezza.png</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>63,000 / 64,000 / 65,000</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>管釣鱒魚 / 細線小餌</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Area trout 系列定位清晰 / spoon、crank、minnow 等管釣小餌覆蓋完整</t>
         </is>
@@ -807,40 +851,45 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>溪流</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/olympic_rods/OR1003_26_Bellezza_PROTOTYPE.jpg</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>エリアトラウトにおける機能美の追求。</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>54,000 / 55,000 / 56,000 / 57,000 / 58,000</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>エリアトラウトにおける機能美の追求。 エリアトラウトでの主流となりつつある掛け調子のロッドを早くから展開してきたベレッツァ・プロトタイプが装いを新たに誕生。シャープで張りのあるブランクスは「トレカ®T1100G」・「トレカ®M40X」などを使用し、細身で軽量ながら十分なパワーを確保。エリアトラウトシーンで映えるハイグレードコルクとウッドシートのグリップ周りやエステルラインに対応したガイドセッティングを採用した、新生ベレッツァ・プロトタイプの機能美をご堪能ください。</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>管釣鱒魚 / 細線小餌</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Area trout 系列定位清晰 / spoon、crank、minnow 等管釣小餌覆蓋完整</t>
         </is>
@@ -880,40 +929,45 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>溪流</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/olympic_rods/OR1004_24_BELLEZZA_UX.jpg</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>エリアトラウトにUXという新たな選択肢。</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>23,500 / 22,500 / 24,000 / 24,500 / 23,000</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>エリアトラウトにUXという新たな選択肢。 次世代のエリアトラウトロッド、ベレッツァUXが誕生。アジングゲームを席巻するコルトシリーズのDNAを融合し、オリジナルカーボンリールシート「OP-01」を採用。高感度化することで水中をより鮮明にイメージすることが可能に。今までのエリアトラウトロッドの良さを残しつつもシビアなアタリを取ることができる今までにないモデルとなっています。</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>管釣鱒魚 / 細線小餌</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Area trout 系列定位清晰 / spoon、crank、minnow 等管釣小餌覆蓋完整</t>
         </is>
@@ -1156,4446 +1210,4446 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>ORD10000</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="29" t="inlineStr">
         <is>
           <t>20GVIGC-71H</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="29" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="29" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="29" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="29" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="29" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L2" s="5" t="str"/>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="L2" s="29" t="str"/>
+      <c r="M2" s="29" t="inlineStr">
         <is>
           <t>14-20</t>
         </is>
       </c>
-      <c r="N2" s="5" t="str"/>
-      <c r="O2" s="5" t="str"/>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="N2" s="29" t="str"/>
+      <c r="O2" s="29" t="str"/>
+      <c r="P2" s="29" t="inlineStr">
         <is>
           <t>Fuji ECS16 reel seat</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="str"/>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="Q2" s="29" t="str"/>
+      <c r="R2" s="29" t="inlineStr">
         <is>
           <t>51,000</t>
         </is>
       </c>
-      <c r="S2" s="5" t="str"/>
-      <c r="T2" s="5" t="str"/>
-      <c r="U2" s="5" t="str"/>
-      <c r="V2" s="5" t="str"/>
-      <c r="W2" s="5" t="str"/>
-      <c r="X2" s="5" t="str"/>
-      <c r="Y2" s="5" t="str"/>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="S2" s="29" t="str"/>
+      <c r="T2" s="29" t="str"/>
+      <c r="U2" s="29" t="str"/>
+      <c r="V2" s="29" t="str"/>
+      <c r="W2" s="29" t="str"/>
+      <c r="X2" s="29" t="str"/>
+      <c r="Y2" s="29" t="str"/>
+      <c r="Z2" s="29" t="inlineStr">
         <is>
           <t>1/4-1</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="str"/>
-      <c r="AB2" s="5" t="inlineStr">
+      <c r="AA2" s="29" t="str"/>
+      <c r="AB2" s="29" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AC2" s="29" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD2" s="5" t="str"/>
-      <c r="AE2" s="5" t="inlineStr">
+      <c r="AD2" s="29" t="str"/>
+      <c r="AE2" s="29" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF2" s="5" t="str"/>
-      <c r="AG2" s="5" t="inlineStr">
+      <c r="AF2" s="29" t="str"/>
+      <c r="AG2" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH2" s="5" t="inlineStr">
+      <c r="AH2" s="29" t="inlineStr">
         <is>
           <t>Bass 障礙打撃：Texas、Punch Shot、Wacky 和 Neko 的落點控制與控線更穩，cover 內補刺和拉離障礙更有餘量。</t>
         </is>
       </c>
-      <c r="AI2" s="5" t="inlineStr">
+      <c r="AI2" s="29" t="inlineStr">
         <is>
           <t>Texas Rig / Punch Shot Rig / Wacky Rig / Neko Rig</t>
         </is>
       </c>
-      <c r="AJ2" s="5" t="str"/>
-      <c r="AK2" s="5" t="str"/>
-      <c r="AL2" s="5" t="inlineStr">
+      <c r="AJ2" s="29" t="str"/>
+      <c r="AK2" s="29" t="str"/>
+      <c r="AL2" s="29" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM2" s="5" t="inlineStr">
+      <c r="AM2" s="29" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸邊與船上 cover 打撃 / weed edge</t>
         </is>
       </c>
-      <c r="AN2" s="5" t="inlineStr">
+      <c r="AN2" s="29" t="inlineStr">
         <is>
           <t>Texas 與 Punch Shot 主軸的障礙打撃竿</t>
         </is>
       </c>
-      <c r="AO2" s="5" t="inlineStr">
+      <c r="AO2" s="29" t="inlineStr">
         <is>
           <t>3/16-3/8oz Texas 和 1/4-1oz Punch Shot 落點控制清楚，能在 weed cover 內補刺並把魚拉離障礙；Wacky、Neko 可作慢速誘食補充。</t>
         </is>
       </c>
-      <c r="AP2" s="5" t="inlineStr">
+      <c r="AP2" s="29" t="inlineStr">
         <is>
           <t>打ち物の釣りに特化したモデル。3/16～3/8オンスシンカーのテキサスリグ、1/4～1オンスのパンチショットでウィードを攻略。ロングストレートワームのワッキー、ネコリグにも対応。おかっぱり、ボートどちらでもメインに扱える打ち物ロッドです。</t>
         </is>
       </c>
-      <c r="AQ2" s="5" t="str"/>
-      <c r="AR2" s="5" t="inlineStr">
+      <c r="AQ2" s="29" t="str"/>
+      <c r="AR2" s="29" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>ORD10001</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>20GVIGC-75M</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="29" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="L3" s="5" t="str"/>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="L3" s="29" t="str"/>
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t>10-16</t>
         </is>
       </c>
-      <c r="N3" s="5" t="str"/>
-      <c r="O3" s="5" t="str"/>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="N3" s="29" t="str"/>
+      <c r="O3" s="29" t="str"/>
+      <c r="P3" s="29" t="inlineStr">
         <is>
           <t>Fuji ECS16 reel seat</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="str"/>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="Q3" s="29" t="str"/>
+      <c r="R3" s="29" t="inlineStr">
         <is>
           <t>51,500</t>
         </is>
       </c>
-      <c r="S3" s="5" t="str"/>
-      <c r="T3" s="5" t="str"/>
-      <c r="U3" s="5" t="str"/>
-      <c r="V3" s="5" t="str"/>
-      <c r="W3" s="5" t="str"/>
-      <c r="X3" s="5" t="str"/>
-      <c r="Y3" s="5" t="str"/>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="S3" s="29" t="str"/>
+      <c r="T3" s="29" t="str"/>
+      <c r="U3" s="29" t="str"/>
+      <c r="V3" s="29" t="str"/>
+      <c r="W3" s="29" t="str"/>
+      <c r="X3" s="29" t="str"/>
+      <c r="Y3" s="29" t="str"/>
+      <c r="Z3" s="29" t="inlineStr">
         <is>
           <t>1/4-1</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="str"/>
-      <c r="AB3" s="5" t="inlineStr">
+      <c r="AA3" s="29" t="str"/>
+      <c r="AB3" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AC3" s="29" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD3" s="5" t="str"/>
-      <c r="AE3" s="5" t="inlineStr">
+      <c r="AD3" s="29" t="str"/>
+      <c r="AE3" s="29" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF3" s="5" t="str"/>
-      <c r="AG3" s="5" t="inlineStr">
+      <c r="AF3" s="29" t="str"/>
+      <c r="AG3" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH3" s="5" t="inlineStr">
+      <c r="AH3" s="29" t="inlineStr">
         <is>
           <t>Bass 巻物 / 操作硬餌：Vibration 和 Jerkbait 是主軸，Regular-Fast 調性保留操作性；Scone Rig、Metal Vibration 和 Metal Jig 作為冬季或吸い込み bite 補充。</t>
         </is>
       </c>
-      <c r="AI3" s="5" t="inlineStr">
+      <c r="AI3" s="29" t="inlineStr">
         <is>
           <t>Vibration / Jerkbait / Scone Rig / Metal Vibration / Metal Jig</t>
         </is>
       </c>
-      <c r="AJ3" s="5" t="str"/>
-      <c r="AK3" s="5" t="str"/>
-      <c r="AL3" s="5" t="inlineStr">
+      <c r="AJ3" s="29" t="str"/>
+      <c r="AK3" s="29" t="str"/>
+      <c r="AL3" s="29" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM3" s="5" t="inlineStr">
+      <c r="AM3" s="29" t="inlineStr">
         <is>
           <t>淡水 Bass / 開放水域與岸投硬餌搜索 / 冬季金屬餌</t>
         </is>
       </c>
-      <c r="AN3" s="5" t="inlineStr">
+      <c r="AN3" s="29" t="inlineStr">
         <is>
           <t>Vibration、Jerkbait 主軸的巻物與操作硬餌竿</t>
         </is>
       </c>
-      <c r="AO3" s="5" t="inlineStr">
+      <c r="AO3" s="29" t="inlineStr">
         <is>
           <t>1/2-5/8oz Vibration、Jerkbait 連續搜索時保留操作性，Scone Rig 可承接吸い込み bite；冬季 Metal Vibration / Metal Jig 也能做反應搜索。</t>
         </is>
       </c>
-      <c r="AP3" s="5" t="inlineStr">
+      <c r="AP3" s="29" t="inlineStr">
         <is>
           <t>1/4～1オンス程度のハードベイトでの巻きの釣りを想定し設計。若干ファーストよりなアクションに仕上げることで操作性も増し、様々なリグにも対応する。メインは1/2～5/8オンス程度のバイブレーションやジャークベイトであるがスコーンリグなどの吸い込みバイトにも対応する。冬季のメタルジグ、メタルバイブなどにもおすすめです。</t>
         </is>
       </c>
-      <c r="AQ3" s="5" t="str"/>
-      <c r="AR3" s="5" t="inlineStr">
+      <c r="AQ3" s="29" t="str"/>
+      <c r="AR3" s="29" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ORD10002</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>20GVIGC-76MH</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t>195</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="L4" s="5" t="str"/>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="L4" s="29" t="str"/>
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t>12-20</t>
         </is>
       </c>
-      <c r="N4" s="5" t="str"/>
-      <c r="O4" s="5" t="str"/>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="N4" s="29" t="str"/>
+      <c r="O4" s="29" t="str"/>
+      <c r="P4" s="29" t="inlineStr">
         <is>
           <t>Fuji ECS17 reel seat</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="str"/>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="Q4" s="29" t="str"/>
+      <c r="R4" s="29" t="inlineStr">
         <is>
           <t>52,000</t>
         </is>
       </c>
-      <c r="S4" s="5" t="str"/>
-      <c r="T4" s="5" t="str"/>
-      <c r="U4" s="5" t="str"/>
-      <c r="V4" s="5" t="str"/>
-      <c r="W4" s="5" t="str"/>
-      <c r="X4" s="5" t="str"/>
-      <c r="Y4" s="5" t="str"/>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="S4" s="29" t="str"/>
+      <c r="T4" s="29" t="str"/>
+      <c r="U4" s="29" t="str"/>
+      <c r="V4" s="29" t="str"/>
+      <c r="W4" s="29" t="str"/>
+      <c r="X4" s="29" t="str"/>
+      <c r="Y4" s="29" t="str"/>
+      <c r="Z4" s="29" t="inlineStr">
         <is>
           <t>3/8-2</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="str"/>
-      <c r="AB4" s="5" t="inlineStr">
+      <c r="AA4" s="29" t="str"/>
+      <c r="AB4" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="inlineStr">
+      <c r="AC4" s="29" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD4" s="5" t="str"/>
-      <c r="AE4" s="5" t="inlineStr">
+      <c r="AD4" s="29" t="str"/>
+      <c r="AE4" s="29" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF4" s="5" t="str"/>
-      <c r="AG4" s="5" t="inlineStr">
+      <c r="AF4" s="29" t="str"/>
+      <c r="AG4" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH4" s="5" t="inlineStr">
+      <c r="AH4" s="29" t="inlineStr">
         <is>
           <t>Bass 中重型巻物：Spinnerbait Slow Roll 放首位，竿身要讀出 blade 振動並承接巻き負荷；Chatterbait 和 Swim Jig 作為同級 moving bait 延伸。</t>
         </is>
       </c>
-      <c r="AI4" s="5" t="inlineStr">
+      <c r="AI4" s="29" t="inlineStr">
         <is>
           <t>Spinnerbait Slow Roll / Heavy Spinnerbait / Chatterbait / Swim Jig</t>
         </is>
       </c>
-      <c r="AJ4" s="5" t="str"/>
-      <c r="AK4" s="5" t="str"/>
-      <c r="AL4" s="5" t="inlineStr">
+      <c r="AJ4" s="29" t="str"/>
+      <c r="AK4" s="29" t="str"/>
+      <c r="AL4" s="29" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM4" s="5" t="inlineStr">
+      <c r="AM4" s="29" t="inlineStr">
         <is>
           <t>淡水 Bass / 中重型巻物搜索 / lake grass edge</t>
         </is>
       </c>
-      <c r="AN4" s="5" t="inlineStr">
+      <c r="AN4" s="29" t="inlineStr">
         <is>
           <t>Spinnerbait Slow Roll 與中重型 moving bait 專用</t>
         </is>
       </c>
-      <c r="AO4" s="5" t="inlineStr">
+      <c r="AO4" s="29" t="inlineStr">
         <is>
           <t>1/2-1.5oz 巻物負荷下竿身彎曲過渡穩，能讀出 blade 振動；太軸單鉤補刺速度和力量足，適合 slow roll、Chatterbait、Swim Jig 搜索。</t>
         </is>
       </c>
-      <c r="AP4" s="5" t="inlineStr">
+      <c r="AP4" s="29" t="inlineStr">
         <is>
           <t>1/2～1・1/2オンスの巻物系ルアーを扱いやすく設計。スピナーベイトの超スローロール時でもブレードの振動を伝える感度。巻き負荷に対してカーブが移行するしなやかさを持ちながら太軸のシングルフックを瞬時に貫通させるスピードとパワーを両立させた。</t>
         </is>
       </c>
-      <c r="AQ4" s="5" t="str"/>
-      <c r="AR4" s="5" t="inlineStr">
+      <c r="AQ4" s="29" t="str"/>
+      <c r="AR4" s="29" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>ORD10003</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>20GVIGC-77XH</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>XH</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>2.31</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="29" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="L5" s="5" t="str"/>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="L5" s="29" t="str"/>
+      <c r="M5" s="29" t="inlineStr">
         <is>
           <t>16-25</t>
         </is>
       </c>
-      <c r="N5" s="5" t="str"/>
-      <c r="O5" s="5" t="str"/>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="N5" s="29" t="str"/>
+      <c r="O5" s="29" t="str"/>
+      <c r="P5" s="29" t="inlineStr">
         <is>
           <t>Fuji ECS17 reel seat</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="str"/>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="Q5" s="29" t="str"/>
+      <c r="R5" s="29" t="inlineStr">
         <is>
           <t>52,500</t>
         </is>
       </c>
-      <c r="S5" s="5" t="str"/>
-      <c r="T5" s="5" t="str"/>
-      <c r="U5" s="5" t="str"/>
-      <c r="V5" s="5" t="str"/>
-      <c r="W5" s="5" t="str"/>
-      <c r="X5" s="5" t="str"/>
-      <c r="Y5" s="5" t="str"/>
-      <c r="Z5" s="5" t="inlineStr">
+      <c r="S5" s="29" t="str"/>
+      <c r="T5" s="29" t="str"/>
+      <c r="U5" s="29" t="str"/>
+      <c r="V5" s="29" t="str"/>
+      <c r="W5" s="29" t="str"/>
+      <c r="X5" s="29" t="str"/>
+      <c r="Y5" s="29" t="str"/>
+      <c r="Z5" s="29" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="AA5" s="5" t="str"/>
-      <c r="AB5" s="5" t="inlineStr">
+      <c r="AA5" s="29" t="str"/>
+      <c r="AB5" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="inlineStr">
+      <c r="AC5" s="29" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD5" s="5" t="str"/>
-      <c r="AE5" s="5" t="inlineStr">
+      <c r="AD5" s="29" t="str"/>
+      <c r="AE5" s="29" t="inlineStr">
         <is>
           <t>GRIP TYPE C</t>
         </is>
       </c>
-      <c r="AF5" s="5" t="str"/>
-      <c r="AG5" s="5" t="inlineStr">
+      <c r="AF5" s="29" t="str"/>
+      <c r="AG5" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH5" s="5" t="inlineStr">
+      <c r="AH5" s="29" t="inlineStr">
         <is>
           <t>Bass 大型餌：Big Bait 和 Crawler Bait 是官方主軸，XH blank 用於穩定高負荷拋投、減少飛行姿勢偏移，Swimbait 作為同負荷泳姿餌延伸。</t>
         </is>
       </c>
-      <c r="AI5" s="5" t="inlineStr">
+      <c r="AI5" s="29" t="inlineStr">
         <is>
           <t>Big Bait / Crawler Bait / Swimbait</t>
         </is>
       </c>
-      <c r="AJ5" s="5" t="str"/>
-      <c r="AK5" s="5" t="str"/>
-      <c r="AL5" s="5" t="inlineStr">
+      <c r="AJ5" s="29" t="str"/>
+      <c r="AK5" s="29" t="str"/>
+      <c r="AL5" s="29" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM5" s="5" t="inlineStr">
+      <c r="AM5" s="29" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型餌拋投 / 開放水域與精準打點</t>
         </is>
       </c>
-      <c r="AN5" s="5" t="inlineStr">
+      <c r="AN5" s="29" t="inlineStr">
         <is>
           <t>Big Bait、Crawler Bait、Swimbait 高負荷竿</t>
         </is>
       </c>
-      <c r="AO5" s="5" t="inlineStr">
+      <c r="AO5" s="29" t="inlineStr">
         <is>
           <t>XH blank 承接 Big Bait 和 Crawler Bait 的拋投負荷，4 軸組布和 T1100G 幫助減少 cast wobble；適合重餌精準落點和穩定泳姿回收。</t>
         </is>
       </c>
-      <c r="AP5" s="5" t="inlineStr">
+      <c r="AP5" s="29" t="inlineStr">
         <is>
           <t>ビッグベイト・クローラーベイトなどのルアーを快適に扱うよう設計。キャスト・操作時の負荷に対してカーブポイントが移行するテーパー設計で各ウェイトに対して快適に扱える。全身に４軸組布とトレカ®T1100Gを採用することによりキャストのブレを軽減し、飛行姿勢を安定させピンポイントキャストを容易にした。</t>
         </is>
       </c>
-      <c r="AQ5" s="5" t="str"/>
-      <c r="AR5" s="5" t="inlineStr">
+      <c r="AQ5" s="29" t="str"/>
+      <c r="AR5" s="29" t="inlineStr">
         <is>
           <t>■GRIP TYPE C</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>ORD10004</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>20GVIGS-610ML</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="L6" s="5" t="str"/>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="L6" s="29" t="str"/>
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t>4-10</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="29" t="inlineStr">
         <is>
           <t>0.5-1.2</t>
         </is>
       </c>
-      <c r="O6" s="5" t="str"/>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="O6" s="29" t="str"/>
+      <c r="P6" s="29" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="str"/>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="Q6" s="29" t="str"/>
+      <c r="R6" s="29" t="inlineStr">
         <is>
           <t>49,000</t>
         </is>
       </c>
-      <c r="S6" s="5" t="str"/>
-      <c r="T6" s="5" t="str"/>
-      <c r="U6" s="5" t="str"/>
-      <c r="V6" s="5" t="str"/>
-      <c r="W6" s="5" t="str"/>
-      <c r="X6" s="5" t="str"/>
-      <c r="Y6" s="5" t="str"/>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="S6" s="29" t="str"/>
+      <c r="T6" s="29" t="str"/>
+      <c r="U6" s="29" t="str"/>
+      <c r="V6" s="29" t="str"/>
+      <c r="W6" s="29" t="str"/>
+      <c r="X6" s="29" t="str"/>
+      <c r="Y6" s="29" t="str"/>
+      <c r="Z6" s="29" t="inlineStr">
         <is>
           <t>1/16-3/8</t>
         </is>
       </c>
-      <c r="AA6" s="5" t="str"/>
-      <c r="AB6" s="5" t="inlineStr">
+      <c r="AA6" s="29" t="str"/>
+      <c r="AB6" s="29" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="inlineStr">
+      <c r="AC6" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD6" s="5" t="str"/>
-      <c r="AE6" s="5" t="inlineStr">
+      <c r="AD6" s="29" t="str"/>
+      <c r="AE6" s="29" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF6" s="5" t="str"/>
-      <c r="AG6" s="5" t="inlineStr">
+      <c r="AF6" s="29" t="str"/>
+      <c r="AG6" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH6" s="5" t="inlineStr">
+      <c r="AH6" s="29" t="inlineStr">
         <is>
           <t>Bass 直柄 finesse / cover 兼用：No Sinker、Neko 和 Bug Lure 需要細線控線與竿尖讀感，小型 plug 可搜索；ML power 保留從 cover 拉魚的餘量。</t>
         </is>
       </c>
-      <c r="AI6" s="5" t="inlineStr">
+      <c r="AI6" s="29" t="inlineStr">
         <is>
           <t>No Sinker / Neko Rig / Bug Lure / Small Topwater Plug / Small Crankbait</t>
         </is>
       </c>
-      <c r="AJ6" s="5" t="str"/>
-      <c r="AK6" s="5" t="str"/>
-      <c r="AL6" s="5" t="inlineStr">
+      <c r="AJ6" s="29" t="str"/>
+      <c r="AK6" s="29" t="str"/>
+      <c r="AL6" s="29" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM6" s="5" t="inlineStr">
+      <c r="AM6" s="29" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸邊 light cover / 直柄精細與小型 plug</t>
         </is>
       </c>
-      <c r="AN6" s="5" t="inlineStr">
+      <c r="AN6" s="29" t="inlineStr">
         <is>
           <t>No Sinker、Neko、虫系兼小型 plug 的 power finesse spin</t>
         </is>
       </c>
-      <c r="AO6" s="5" t="inlineStr">
+      <c r="AO6" s="29" t="inlineStr">
         <is>
           <t>細線下能操作 No Sinker、Neko 和虫系，也能切到小型 plug 搜索；ML power 留有 cover 內控魚餘量，不只是純開放水域精細竿。</t>
         </is>
       </c>
-      <c r="AP6" s="5" t="inlineStr">
+      <c r="AP6" s="29" t="inlineStr">
         <is>
           <t>パワーと繊細さを持たせたバーサタイルスピン。ライトリグを意のままに操る繊細さとカバーからの魚を獲るパワーを持たせた。ノーシンカー、ネコリグ、虫系、プラグなど様々な釣りに適合しつつ、ランカー相手でも安心して対応できるロッドです。</t>
         </is>
       </c>
-      <c r="AQ6" s="5" t="str"/>
-      <c r="AR6" s="5" t="inlineStr">
+      <c r="AQ6" s="29" t="str"/>
+      <c r="AR6" s="29" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>ORD10005</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>GVIGS-6102ML</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>106.8</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="L7" s="5" t="str"/>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="L7" s="29" t="str"/>
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t>4-10</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="29" t="inlineStr">
         <is>
           <t>0.5-1.2</t>
         </is>
       </c>
-      <c r="O7" s="5" t="str"/>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="O7" s="29" t="str"/>
+      <c r="P7" s="29" t="inlineStr">
         <is>
           <t>Olympic OP-02 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="str"/>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="Q7" s="29" t="str"/>
+      <c r="R7" s="29" t="inlineStr">
         <is>
           <t>51,000</t>
         </is>
       </c>
-      <c r="S7" s="5" t="str"/>
-      <c r="T7" s="5" t="str"/>
-      <c r="U7" s="5" t="str"/>
-      <c r="V7" s="5" t="str"/>
-      <c r="W7" s="5" t="str"/>
-      <c r="X7" s="5" t="str"/>
-      <c r="Y7" s="5" t="str"/>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="S7" s="29" t="str"/>
+      <c r="T7" s="29" t="str"/>
+      <c r="U7" s="29" t="str"/>
+      <c r="V7" s="29" t="str"/>
+      <c r="W7" s="29" t="str"/>
+      <c r="X7" s="29" t="str"/>
+      <c r="Y7" s="29" t="str"/>
+      <c r="Z7" s="29" t="inlineStr">
         <is>
           <t>1/16-3/8</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="str"/>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AA7" s="29" t="str"/>
+      <c r="AB7" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AC7" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="str"/>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AD7" s="29" t="str"/>
+      <c r="AE7" s="29" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="str"/>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AF7" s="29" t="str"/>
+      <c r="AG7" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AH7" s="29" t="inlineStr">
         <is>
           <t>Bass 岸釣 light rig：中心切 2 piece 和 Regular-Fast 設定重點是攜行、拋投、誘い到 landing 的連貫性；Neko、No Sinker、Down Shot 以穩定操作為主。</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="inlineStr">
+      <c r="AI7" s="29" t="inlineStr">
         <is>
           <t>Neko Rig / No Sinker / Down Shot / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ7" s="5" t="str"/>
-      <c r="AK7" s="5" t="str"/>
-      <c r="AL7" s="5" t="inlineStr">
+      <c r="AJ7" s="29" t="str"/>
+      <c r="AK7" s="29" t="str"/>
+      <c r="AL7" s="29" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM7" s="5" t="inlineStr">
+      <c r="AM7" s="29" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸釣移動作戰 / light rig 全般</t>
         </is>
       </c>
-      <c r="AN7" s="5" t="inlineStr">
+      <c r="AN7" s="29" t="inlineStr">
         <is>
           <t>攜行取向的 light rig 泛用兩節直柄</t>
         </is>
       </c>
-      <c r="AO7" s="5" t="inlineStr">
+      <c r="AO7" s="29" t="inlineStr">
         <is>
           <t>中心切 2 piece 方便岸釣移動，Regular-Fast 設定讓 Neko、No Sinker、Down Shot 的拋投、誘い、landing 動作連貫；口徑保守，不擴寫到重 cover。</t>
         </is>
       </c>
-      <c r="AP7" s="5" t="inlineStr">
+      <c r="AP7" s="29" t="inlineStr">
         <is>
           <t>携帯性を優先したセンターカット2ピースモデル。ライトリグ全般に広域対応可能なレギュラーファストアクション。足場の安定しないおかっぱりでは、このレングスとアクション設定が効果的に働き、キャスト・誘い・ランディングまでの一連の動きをスムースに行えるロッドです。</t>
         </is>
       </c>
-      <c r="AQ7" s="5" t="str"/>
-      <c r="AR7" s="5" t="inlineStr">
+      <c r="AQ7" s="29" t="str"/>
+      <c r="AR7" s="29" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>ORD10006</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>20GVIGS-742M</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="29" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="L8" s="5" t="str"/>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="L8" s="29" t="str"/>
+      <c r="M8" s="29" t="inlineStr">
         <is>
           <t>6-10</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="29" t="inlineStr">
         <is>
           <t>0.5-1.2</t>
         </is>
       </c>
-      <c r="O8" s="5" t="str"/>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="O8" s="29" t="str"/>
+      <c r="P8" s="29" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="str"/>
-      <c r="R8" s="5" t="inlineStr">
+      <c r="Q8" s="29" t="str"/>
+      <c r="R8" s="29" t="inlineStr">
         <is>
           <t>51,000</t>
         </is>
       </c>
-      <c r="S8" s="5" t="str"/>
-      <c r="T8" s="5" t="str"/>
-      <c r="U8" s="5" t="str"/>
-      <c r="V8" s="5" t="str"/>
-      <c r="W8" s="5" t="str"/>
-      <c r="X8" s="5" t="str"/>
-      <c r="Y8" s="5" t="str"/>
-      <c r="Z8" s="5" t="inlineStr">
+      <c r="S8" s="29" t="str"/>
+      <c r="T8" s="29" t="str"/>
+      <c r="U8" s="29" t="str"/>
+      <c r="V8" s="29" t="str"/>
+      <c r="W8" s="29" t="str"/>
+      <c r="X8" s="29" t="str"/>
+      <c r="Y8" s="29" t="str"/>
+      <c r="Z8" s="29" t="inlineStr">
         <is>
           <t>3/16-3/4</t>
         </is>
       </c>
-      <c r="AA8" s="5" t="str"/>
-      <c r="AB8" s="5" t="inlineStr">
+      <c r="AA8" s="29" t="str"/>
+      <c r="AB8" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AC8" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD8" s="5" t="str"/>
-      <c r="AE8" s="5" t="inlineStr">
+      <c r="AD8" s="29" t="str"/>
+      <c r="AE8" s="29" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF8" s="5" t="str"/>
-      <c r="AG8" s="5" t="inlineStr">
+      <c r="AF8" s="29" t="str"/>
+      <c r="AG8" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH8" s="5" t="inlineStr">
+      <c r="AH8" s="29" t="inlineStr">
         <is>
           <t>Bass PE 遠投 finesse：Long Cast Neko、PE Down Shot 和 No Sinker 是主軸，長距離下要維持細微違和感讀取；Small Crankbait、Topwater 是 plug 操作補充。</t>
         </is>
       </c>
-      <c r="AI8" s="5" t="inlineStr">
+      <c r="AI8" s="29" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / PE Down Shot / No Sinker / Small Crankbait / Topwater Plug</t>
         </is>
       </c>
-      <c r="AJ8" s="5" t="str"/>
-      <c r="AK8" s="5" t="str"/>
-      <c r="AL8" s="5" t="inlineStr">
+      <c r="AJ8" s="29" t="str"/>
+      <c r="AK8" s="29" t="str"/>
+      <c r="AL8" s="29" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM8" s="5" t="inlineStr">
+      <c r="AM8" s="29" t="inlineStr">
         <is>
           <t>淡水 Bass / PE 遠投 / 開放水域 light rig 與 plug</t>
         </is>
       </c>
-      <c r="AN8" s="5" t="inlineStr">
+      <c r="AN8" s="29" t="inlineStr">
         <is>
           <t>PE light rig 遠投與 plug 操作兼用直柄</t>
         </is>
       </c>
-      <c r="AO8" s="5" t="inlineStr">
+      <c r="AO8" s="29" t="inlineStr">
         <is>
           <t>7'4" 長度和 M power 支撐 Long Cast Neko、PE Down Shot 的遠距控線，遠端細微違和感更容易讀取；Small Crankbait、Topwater 可做遠投搜索補充。</t>
         </is>
       </c>
-      <c r="AP8" s="5" t="inlineStr">
+      <c r="AP8" s="29" t="inlineStr">
         <is>
           <t>PEラインを使用したライトリグの遠投に特化したモデル。しなやかでありつつ、張りのあるブランクスは遠距離での繊細な操作や僅かな違和感を逃さない感度につながる。ライトリグだけではなくプラグの操作にも対応した遠投バーサタイルモデルです。</t>
         </is>
       </c>
-      <c r="AQ8" s="5" t="str"/>
-      <c r="AR8" s="5" t="inlineStr">
+      <c r="AQ8" s="29" t="str"/>
+      <c r="AR8" s="29" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>ORD10007</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>21GVELUC-65ML</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="28" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="L9" s="4" t="str"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="28" t="str"/>
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t>MAX14</t>
         </is>
       </c>
-      <c r="N9" s="4" t="str"/>
-      <c r="O9" s="4" t="str"/>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="N9" s="28" t="str"/>
+      <c r="O9" s="28" t="str"/>
+      <c r="P9" s="28" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="str"/>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="Q9" s="28" t="str"/>
+      <c r="R9" s="28" t="inlineStr">
         <is>
           <t>23,500</t>
         </is>
       </c>
-      <c r="S9" s="4" t="str"/>
-      <c r="T9" s="4" t="str"/>
-      <c r="U9" s="4" t="str"/>
-      <c r="V9" s="4" t="str"/>
-      <c r="W9" s="4" t="str"/>
-      <c r="X9" s="4" t="str"/>
-      <c r="Y9" s="4" t="str"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="S9" s="28" t="str"/>
+      <c r="T9" s="28" t="str"/>
+      <c r="U9" s="28" t="str"/>
+      <c r="V9" s="28" t="str"/>
+      <c r="W9" s="28" t="str"/>
+      <c r="X9" s="28" t="str"/>
+      <c r="Y9" s="28" t="str"/>
+      <c r="Z9" s="28" t="inlineStr">
         <is>
           <t>MAX3/4</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="str"/>
-      <c r="AB9" s="4" t="inlineStr">
+      <c r="AA9" s="28" t="str"/>
+      <c r="AB9" s="28" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AC9" s="28" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="str"/>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AD9" s="28" t="str"/>
+      <c r="AE9" s="28" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="str"/>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AF9" s="28" t="str"/>
+      <c r="AG9" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
+      <c r="AH9" s="28" t="inlineStr">
         <is>
           <t>Bass 小中型硬餌 / cover finesse：Topwater、Shallow Crankbait 負責搜索，Cover Neko 和 Small Rubber Jig 負責 cover 內精細打點。</t>
         </is>
       </c>
-      <c r="AI9" s="4" t="inlineStr">
+      <c r="AI9" s="28" t="inlineStr">
         <is>
           <t>Topwater Plug / Shallow Crankbait / Cover Neko / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="str"/>
-      <c r="AK9" s="4" t="str"/>
-      <c r="AL9" s="4" t="inlineStr">
+      <c r="AJ9" s="28" t="str"/>
+      <c r="AK9" s="28" t="str"/>
+      <c r="AL9" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM9" s="4" t="inlineStr">
+      <c r="AM9" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / shallow cover edge / 小中型硬餌與 cover finesse</t>
         </is>
       </c>
-      <c r="AN9" s="4" t="inlineStr">
+      <c r="AN9" s="28" t="inlineStr">
         <is>
           <t>小中型 Topwater / Shallow Crank 加 cover bait finesse</t>
         </is>
       </c>
-      <c r="AO9" s="4" t="inlineStr">
+      <c r="AO9" s="28" t="inlineStr">
         <is>
           <t>Topwater Plug、Shallow Crankbait 做近中距離搜索，Cover Neko 和 Small Rubber Jig 負責輕 cover 內精細打點；ML power 讓拋投準度和彎曲承接更友好。</t>
         </is>
       </c>
-      <c r="AP9" s="4" t="inlineStr">
+      <c r="AP9" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 トップウォータープラグやシャロークランクベイトなどの小型～中型ハードベイトをメインにカバーネコ、スモラバなどを使用したカバーベイトフィネスにも対応できるモデル。スムースなベントカーブが爽快なキャストフィールと高いキャストアキュラシーを可能にします。</t>
         </is>
       </c>
-      <c r="AQ9" s="4" t="inlineStr">
+      <c r="AQ9" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR9" s="4" t="inlineStr">
+      <c r="AR9" s="28" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>ORD10008</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>21GVELUC-69MH</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="28" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="28" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="L10" s="4" t="str"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="28" t="str"/>
+      <c r="M10" s="28" t="inlineStr">
         <is>
           <t>MAX20</t>
         </is>
       </c>
-      <c r="N10" s="4" t="str"/>
-      <c r="O10" s="4" t="str"/>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="N10" s="28" t="str"/>
+      <c r="O10" s="28" t="str"/>
+      <c r="P10" s="28" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="str"/>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="Q10" s="28" t="str"/>
+      <c r="R10" s="28" t="inlineStr">
         <is>
           <t>24,000</t>
         </is>
       </c>
-      <c r="S10" s="4" t="str"/>
-      <c r="T10" s="4" t="str"/>
-      <c r="U10" s="4" t="str"/>
-      <c r="V10" s="4" t="str"/>
-      <c r="W10" s="4" t="str"/>
-      <c r="X10" s="4" t="str"/>
-      <c r="Y10" s="4" t="str"/>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="S10" s="28" t="str"/>
+      <c r="T10" s="28" t="str"/>
+      <c r="U10" s="28" t="str"/>
+      <c r="V10" s="28" t="str"/>
+      <c r="W10" s="28" t="str"/>
+      <c r="X10" s="28" t="str"/>
+      <c r="Y10" s="28" t="str"/>
+      <c r="Z10" s="28" t="inlineStr">
         <is>
           <t>MAX1・1/4</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="str"/>
-      <c r="AB10" s="4" t="inlineStr">
+      <c r="AA10" s="28" t="str"/>
+      <c r="AB10" s="28" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr">
+      <c r="AC10" s="28" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="str"/>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AD10" s="28" t="str"/>
+      <c r="AE10" s="28" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="str"/>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AF10" s="28" t="str"/>
+      <c r="AG10" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
+      <c r="AH10" s="28" t="inlineStr">
         <is>
           <t>Bass power finesse bait：3/16-3/8oz Texas、Light Rubber Jig 和高比重 No Sinker 是打點核心，Spinnerbait / Chatterbait 作為 3/8-1/2oz 搜索切換。</t>
         </is>
       </c>
-      <c r="AI10" s="4" t="inlineStr">
+      <c r="AI10" s="28" t="inlineStr">
         <is>
           <t>Texas Rig / Light Rubber Jig / High-density No Sinker / Spinnerbait / Chatterbait</t>
         </is>
       </c>
-      <c r="AJ10" s="4" t="str"/>
-      <c r="AK10" s="4" t="str"/>
-      <c r="AL10" s="4" t="inlineStr">
+      <c r="AJ10" s="28" t="str"/>
+      <c r="AK10" s="28" t="str"/>
+      <c r="AL10" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM10" s="4" t="inlineStr">
+      <c r="AM10" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 邊緣與開放水域切換 / bait versatile</t>
         </is>
       </c>
-      <c r="AN10" s="4" t="inlineStr">
+      <c r="AN10" s="28" t="inlineStr">
         <is>
           <t>Texas、Light Rubber Jig 主軸的打撃搜索兩用</t>
         </is>
       </c>
-      <c r="AO10" s="4" t="inlineStr">
+      <c r="AO10" s="28" t="inlineStr">
         <is>
           <t>3/16-3/8oz Texas、Light Rubber Jig 和高比重 No Sinker 可精準打點，3/8-1/2oz Spinnerbait / Chatterbait 能快速搜索；一支竿覆蓋軟餌與 wire bait 切換。</t>
         </is>
       </c>
-      <c r="AP10" s="4" t="inlineStr">
+      <c r="AP10" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 3/16～3/8ozのテキサスリグ・ライトラバージグ、高比重ワームのノーシンカー、3/8oz～1/2oz程度のスピナーベイト・チャターベイトなどを高次元で使用可能なバーサタイルロッド。</t>
         </is>
       </c>
-      <c r="AQ10" s="4" t="inlineStr">
+      <c r="AQ10" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR10" s="4" t="inlineStr">
+      <c r="AR10" s="28" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>ORD10009</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>21GVELUC-610M</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="28" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="L11" s="4" t="str"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L11" s="28" t="str"/>
+      <c r="M11" s="28" t="inlineStr">
         <is>
           <t>MAX16</t>
         </is>
       </c>
-      <c r="N11" s="4" t="str"/>
-      <c r="O11" s="4" t="str"/>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="N11" s="28" t="str"/>
+      <c r="O11" s="28" t="str"/>
+      <c r="P11" s="28" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="str"/>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="Q11" s="28" t="str"/>
+      <c r="R11" s="28" t="inlineStr">
         <is>
           <t>24,500</t>
         </is>
       </c>
-      <c r="S11" s="4" t="str"/>
-      <c r="T11" s="4" t="str"/>
-      <c r="U11" s="4" t="str"/>
-      <c r="V11" s="4" t="str"/>
-      <c r="W11" s="4" t="str"/>
-      <c r="X11" s="4" t="str"/>
-      <c r="Y11" s="4" t="str"/>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="S11" s="28" t="str"/>
+      <c r="T11" s="28" t="str"/>
+      <c r="U11" s="28" t="str"/>
+      <c r="V11" s="28" t="str"/>
+      <c r="W11" s="28" t="str"/>
+      <c r="X11" s="28" t="str"/>
+      <c r="Y11" s="28" t="str"/>
+      <c r="Z11" s="28" t="inlineStr">
         <is>
           <t>MAX1</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="str"/>
-      <c r="AB11" s="4" t="inlineStr">
+      <c r="AA11" s="28" t="str"/>
+      <c r="AB11" s="28" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="inlineStr">
+      <c r="AC11" s="28" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="str"/>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AD11" s="28" t="str"/>
+      <c r="AE11" s="28" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="str"/>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AF11" s="28" t="str"/>
+      <c r="AG11" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
+      <c r="AH11" s="28" t="inlineStr">
         <is>
           <t>Bass bait versatile：中型 hardbait 和 1/2oz 內 Spinnerbait 負責搜索，高比重 No Sinker 與 1/4oz Texas 負責慢速打點；ベントカーブ重視拋投準度。</t>
         </is>
       </c>
-      <c r="AI11" s="4" t="inlineStr">
+      <c r="AI11" s="28" t="inlineStr">
         <is>
           <t>Medium Crankbait / Medium Minnow / Spinnerbait / High-density No Sinker / Texas Rig</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="str"/>
-      <c r="AK11" s="4" t="str"/>
-      <c r="AL11" s="4" t="inlineStr">
+      <c r="AJ11" s="28" t="str"/>
+      <c r="AK11" s="28" t="str"/>
+      <c r="AL11" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM11" s="4" t="inlineStr">
+      <c r="AM11" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / 開放水域中型硬餌 / 常規岸船泛用</t>
         </is>
       </c>
-      <c r="AN11" s="4" t="inlineStr">
+      <c r="AN11" s="28" t="inlineStr">
         <is>
           <t>Medium Crankbait、Spinnerbait 與高比重 No Sinker 泛用 bait</t>
         </is>
       </c>
-      <c r="AO11" s="4" t="inlineStr">
+      <c r="AO11" s="28" t="inlineStr">
         <is>
           <t>中型 Crankbait / Minnow 和 1/2oz 內 Spinnerbait 負責搜索，高比重 No Sinker、1/4oz Texas 負責慢速打點；彎曲曲線寬容，拋投手感和準度較友好。</t>
         </is>
       </c>
-      <c r="AP11" s="4" t="inlineStr">
+      <c r="AP11" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 中型のハードベイト、1/2ozまでのスピナーベイト、4～5インチ高比重ワームのノーシンカーから1/4oz前後のテキサスリグなどに高次元で対応するバーサタイルロッド。スムースなベントカーブが爽快なキャストフィールと高いキャストアキュラシーを可能にします。</t>
         </is>
       </c>
-      <c r="AQ11" s="4" t="inlineStr">
+      <c r="AQ11" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR11" s="4" t="inlineStr">
+      <c r="AR11" s="28" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>ORD10010</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>21GVELUC-70H</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>2.14</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="28" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="L12" s="4" t="str"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="L12" s="28" t="str"/>
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t>MAX20</t>
         </is>
       </c>
-      <c r="N12" s="4" t="str"/>
-      <c r="O12" s="4" t="str"/>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="N12" s="28" t="str"/>
+      <c r="O12" s="28" t="str"/>
+      <c r="P12" s="28" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="str"/>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="Q12" s="28" t="str"/>
+      <c r="R12" s="28" t="inlineStr">
         <is>
           <t>25,000</t>
         </is>
       </c>
-      <c r="S12" s="4" t="str"/>
-      <c r="T12" s="4" t="str"/>
-      <c r="U12" s="4" t="str"/>
-      <c r="V12" s="4" t="str"/>
-      <c r="W12" s="4" t="str"/>
-      <c r="X12" s="4" t="str"/>
-      <c r="Y12" s="4" t="str"/>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="S12" s="28" t="str"/>
+      <c r="T12" s="28" t="str"/>
+      <c r="U12" s="28" t="str"/>
+      <c r="V12" s="28" t="str"/>
+      <c r="W12" s="28" t="str"/>
+      <c r="X12" s="28" t="str"/>
+      <c r="Y12" s="28" t="str"/>
+      <c r="Z12" s="28" t="inlineStr">
         <is>
           <t>MAX1・1/2</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="str"/>
-      <c r="AB12" s="4" t="inlineStr">
+      <c r="AA12" s="28" t="str"/>
+      <c r="AB12" s="28" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AC12" s="28" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="str"/>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AD12" s="28" t="str"/>
+      <c r="AE12" s="28" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="str"/>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AF12" s="28" t="str"/>
+      <c r="AG12" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="inlineStr">
+      <c r="AH12" s="28" t="inlineStr">
         <is>
           <t>Bass heavy versatile：3/8oz 以上 Texas 和 Rubber Jig 是 cover game 主軸，Heavy Spinnerbait slow roll 與 Frog 用於 vegetation 和高阻力搜索。</t>
         </is>
       </c>
-      <c r="AI12" s="4" t="inlineStr">
+      <c r="AI12" s="28" t="inlineStr">
         <is>
           <t>Texas Rig / Rubber Jig / Heavy Spinnerbait / Frog</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="str"/>
-      <c r="AK12" s="4" t="str"/>
-      <c r="AL12" s="4" t="inlineStr">
+      <c r="AJ12" s="28" t="str"/>
+      <c r="AK12" s="28" t="str"/>
+      <c r="AL12" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM12" s="4" t="inlineStr">
+      <c r="AM12" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover / vegetation frog game</t>
         </is>
       </c>
-      <c r="AN12" s="4" t="inlineStr">
+      <c r="AN12" s="28" t="inlineStr">
         <is>
           <t>Texas、Rubber Jig、Heavy Spinnerbait、Frog 的重障礙泛用</t>
         </is>
       </c>
-      <c r="AO12" s="4" t="inlineStr">
+      <c r="AO12" s="28" t="inlineStr">
         <is>
           <t>3/8oz 以上 Texas 和 Rubber Jig 可攻 cover，Heavy Spinnerbait slow roll 能沿草邊搜索，Frog 可處理 vegetation；H power 更重視控魚和脫離障礙。</t>
         </is>
       </c>
-      <c r="AP12" s="4" t="inlineStr">
+      <c r="AP12" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 3/8oz以上のテキサスリグ・ラバージグを使用したカバーゲームをメインに1/2oz以上のヘビースピナーベイトのスローロール、ベジテーションエリアでのフロッグゲームに対応するヘビーバーサタイルロッド。</t>
         </is>
       </c>
-      <c r="AQ12" s="4" t="inlineStr">
+      <c r="AQ12" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR12" s="4" t="inlineStr">
+      <c r="AR12" s="28" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>ORD10011</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>21GVELUC-74X</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="28" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="28" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="L13" s="4" t="str"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="L13" s="28" t="str"/>
+      <c r="M13" s="28" t="inlineStr">
         <is>
           <t>MAX25</t>
         </is>
       </c>
-      <c r="N13" s="4" t="str"/>
-      <c r="O13" s="4" t="str"/>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="N13" s="28" t="str"/>
+      <c r="O13" s="28" t="str"/>
+      <c r="P13" s="28" t="inlineStr">
         <is>
           <t>Fuji TCS reel seat</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="str"/>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="Q13" s="28" t="str"/>
+      <c r="R13" s="28" t="inlineStr">
         <is>
           <t>25,500</t>
         </is>
       </c>
-      <c r="S13" s="4" t="str"/>
-      <c r="T13" s="4" t="str"/>
-      <c r="U13" s="4" t="str"/>
-      <c r="V13" s="4" t="str"/>
-      <c r="W13" s="4" t="str"/>
-      <c r="X13" s="4" t="str"/>
-      <c r="Y13" s="4" t="str"/>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="S13" s="28" t="str"/>
+      <c r="T13" s="28" t="str"/>
+      <c r="U13" s="28" t="str"/>
+      <c r="V13" s="28" t="str"/>
+      <c r="W13" s="28" t="str"/>
+      <c r="X13" s="28" t="str"/>
+      <c r="Y13" s="28" t="str"/>
+      <c r="Z13" s="28" t="inlineStr">
         <is>
           <t>MAX3</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="str"/>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AA13" s="28" t="str"/>
+      <c r="AB13" s="28" t="inlineStr">
         <is>
           <t>グリップ脱着式</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AC13" s="28" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="str"/>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AD13" s="28" t="str"/>
+      <c r="AE13" s="28" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="str"/>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AF13" s="28" t="str"/>
+      <c r="AG13" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
+      <c r="AH13" s="28" t="inlineStr">
         <is>
           <t>Bass 強力長竿：Heavy Texas 放首位對應 cover 打點，MAX3oz Big Bait / Swimbait 需要粘りのある blank 承接拋投負荷與跟隨咬口。</t>
         </is>
       </c>
-      <c r="AI13" s="4" t="inlineStr">
+      <c r="AI13" s="28" t="inlineStr">
         <is>
           <t>Heavy Texas Rig / Big Bait / Swimbait</t>
         </is>
       </c>
-      <c r="AJ13" s="4" t="str"/>
-      <c r="AK13" s="4" t="str"/>
-      <c r="AL13" s="4" t="inlineStr">
+      <c r="AJ13" s="28" t="str"/>
+      <c r="AK13" s="28" t="str"/>
+      <c r="AL13" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM13" s="4" t="inlineStr">
+      <c r="AM13" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover 與大型餌 / 遠距高負荷</t>
         </is>
       </c>
-      <c r="AN13" s="4" t="inlineStr">
+      <c r="AN13" s="28" t="inlineStr">
         <is>
           <t>Heavy Texas 與 MAX3oz Big Bait / Swimbait 強力竿</t>
         </is>
       </c>
-      <c r="AO13" s="4" t="inlineStr">
+      <c r="AO13" s="28" t="inlineStr">
         <is>
           <t>Heavy Texas 用於 cover 打點，Big Bait / Swimbait 可到 MAX3oz；不是單純硬竿，粘り能承接重餌拋投與咬口跟隨，grip joint 也利於攜行。</t>
         </is>
       </c>
-      <c r="AP13" s="4" t="inlineStr">
+      <c r="AP13" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 ただ硬いだけではなく適度に粘るブランクスを採用し、1/2oz以上のヘビーテキサス、MAX3ozまでのビッグベイト＆スイムベイトに対応したパワーロッド。持ち運びに便利なグリップ脱着式を採用。</t>
         </is>
       </c>
-      <c r="AQ13" s="4" t="inlineStr">
+      <c r="AQ13" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR13" s="4" t="inlineStr">
+      <c r="AR13" s="28" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>ORD10012</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>21GVELUS-64L</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="28" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="28" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="L14" s="4" t="str"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="L14" s="28" t="str"/>
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t>MAX6</t>
         </is>
       </c>
-      <c r="N14" s="4" t="str"/>
-      <c r="O14" s="4" t="str"/>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="N14" s="28" t="str"/>
+      <c r="O14" s="28" t="str"/>
+      <c r="P14" s="28" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="str"/>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="Q14" s="28" t="str"/>
+      <c r="R14" s="28" t="inlineStr">
         <is>
           <t>23,500</t>
         </is>
       </c>
-      <c r="S14" s="4" t="str"/>
-      <c r="T14" s="4" t="str"/>
-      <c r="U14" s="4" t="str"/>
-      <c r="V14" s="4" t="str"/>
-      <c r="W14" s="4" t="str"/>
-      <c r="X14" s="4" t="str"/>
-      <c r="Y14" s="4" t="str"/>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="S14" s="28" t="str"/>
+      <c r="T14" s="28" t="str"/>
+      <c r="U14" s="28" t="str"/>
+      <c r="V14" s="28" t="str"/>
+      <c r="W14" s="28" t="str"/>
+      <c r="X14" s="28" t="str"/>
+      <c r="Y14" s="28" t="str"/>
+      <c r="Z14" s="28" t="inlineStr">
         <is>
           <t>MAX1/4</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="str"/>
-      <c r="AB14" s="4" t="inlineStr">
+      <c r="AA14" s="28" t="str"/>
+      <c r="AB14" s="28" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="inlineStr">
+      <c r="AC14" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="str"/>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AD14" s="28" t="str"/>
+      <c r="AE14" s="28" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="str"/>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AF14" s="28" t="str"/>
+      <c r="AG14" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
+      <c r="AH14" s="28" t="inlineStr">
         <is>
           <t>Bass short spinning versatile：Light rig 全般是主軸，6’4” 提升近中距離操作和落點準度；Small Crankbait / Minnow 作為小型 plug 搜索補充。</t>
         </is>
       </c>
-      <c r="AI14" s="4" t="inlineStr">
+      <c r="AI14" s="28" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Crankbait / Small Minnow</t>
         </is>
       </c>
-      <c r="AJ14" s="4" t="str"/>
-      <c r="AK14" s="4" t="str"/>
-      <c r="AL14" s="4" t="inlineStr">
+      <c r="AJ14" s="28" t="str"/>
+      <c r="AK14" s="28" t="str"/>
+      <c r="AL14" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM14" s="4" t="inlineStr">
+      <c r="AM14" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / 近中距離 finesse / 小型 plug 搜索</t>
         </is>
       </c>
-      <c r="AN14" s="4" t="inlineStr">
+      <c r="AN14" s="28" t="inlineStr">
         <is>
           <t>短尺 light rig 與 small plug 直柄泛用</t>
         </is>
       </c>
-      <c r="AO14" s="4" t="inlineStr">
+      <c r="AO14" s="28" t="inlineStr">
         <is>
           <t>6'4" 長度提升近距離落點和竿尖操作，Neko、Down Shot、No Sinker 做食わせ，小型 Crankbait / Minnow 可搜索；較 regular 的調性讓拋投手感更順。</t>
         </is>
       </c>
-      <c r="AP14" s="4" t="inlineStr">
+      <c r="AP14" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 ライトリグ全般からスモールプラグまで高次元で対応したバーサタイルロッド。極端なファーストテーパーは避け、ややレギュラーよりなテーパーとすることで、爽快なキャストフィールとライトリグの操作性を追求。6’4”のレングスが高い操作性と飛距離を両立します。</t>
         </is>
       </c>
-      <c r="AQ14" s="4" t="inlineStr">
+      <c r="AQ14" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR14" s="4" t="str"/>
+      <c r="AR14" s="28" t="str"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>ORD10013</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>21GVELUS-610ML</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K15" s="28" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="L15" s="4" t="str"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="28" t="str"/>
+      <c r="M15" s="28" t="inlineStr">
         <is>
           <t>MAX6</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N15" s="28" t="inlineStr">
         <is>
           <t>MAX0.8</t>
         </is>
       </c>
-      <c r="O15" s="4" t="str"/>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="O15" s="28" t="str"/>
+      <c r="P15" s="28" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="str"/>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="Q15" s="28" t="str"/>
+      <c r="R15" s="28" t="inlineStr">
         <is>
           <t>24,000</t>
         </is>
       </c>
-      <c r="S15" s="4" t="str"/>
-      <c r="T15" s="4" t="str"/>
-      <c r="U15" s="4" t="str"/>
-      <c r="V15" s="4" t="str"/>
-      <c r="W15" s="4" t="str"/>
-      <c r="X15" s="4" t="str"/>
-      <c r="Y15" s="4" t="str"/>
-      <c r="Z15" s="4" t="inlineStr">
+      <c r="S15" s="28" t="str"/>
+      <c r="T15" s="28" t="str"/>
+      <c r="U15" s="28" t="str"/>
+      <c r="V15" s="28" t="str"/>
+      <c r="W15" s="28" t="str"/>
+      <c r="X15" s="28" t="str"/>
+      <c r="Y15" s="28" t="str"/>
+      <c r="Z15" s="28" t="inlineStr">
         <is>
           <t>MAX3/8</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="str"/>
-      <c r="AB15" s="4" t="inlineStr">
+      <c r="AA15" s="28" t="str"/>
+      <c r="AB15" s="28" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC15" s="4" t="inlineStr">
+      <c r="AC15" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="str"/>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AD15" s="28" t="str"/>
+      <c r="AE15" s="28" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="str"/>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AF15" s="28" t="str"/>
+      <c r="AG15" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="inlineStr">
+      <c r="AH15" s="28" t="inlineStr">
         <is>
           <t>Bass long versatile spin：利用 6’10” 的遠投性能投送 Neko、Down Shot 和 No Sinker，輕量平衡保留細操作；Small Plug 用於遠處搜索。</t>
         </is>
       </c>
-      <c r="AI15" s="4" t="inlineStr">
+      <c r="AI15" s="28" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / Down Shot / No Sinker / Small Crankbait / Small Minnow</t>
         </is>
       </c>
-      <c r="AJ15" s="4" t="str"/>
-      <c r="AK15" s="4" t="str"/>
-      <c r="AL15" s="4" t="inlineStr">
+      <c r="AJ15" s="28" t="str"/>
+      <c r="AK15" s="28" t="str"/>
+      <c r="AL15" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM15" s="4" t="inlineStr">
+      <c r="AM15" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸投遠投 finesse / 開放水域長距離控線</t>
         </is>
       </c>
-      <c r="AN15" s="4" t="inlineStr">
+      <c r="AN15" s="28" t="inlineStr">
         <is>
           <t>Long Cast Neko、Down Shot 與小型 plug 的長尺直柄</t>
         </is>
       </c>
-      <c r="AO15" s="4" t="inlineStr">
+      <c r="AO15" s="28" t="inlineStr">
         <is>
           <t>6'10" 長度放大 light rig 投送距離，輕量平衡保留細操作；Neko、Down Shot、No Sinker 是主軸，小型 Crankbait / Minnow 用於遠處搜索。</t>
         </is>
       </c>
-      <c r="AP15" s="4" t="inlineStr">
+      <c r="AP15" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 ロッドレングスを活かしたロングキャスト性能と幅広いルアーに対応したロングバーサタイルスピン。6’10”というレングスを感じさせない軽量感とロッドバランスにより繊細な操作を可能にします。</t>
         </is>
       </c>
-      <c r="AQ15" s="4" t="inlineStr">
+      <c r="AQ15" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR15" s="4" t="str"/>
+      <c r="AR15" s="28" t="str"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>ORD10014</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>21GVELUS-611H-PF</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="28" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="28" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="28" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="L16" s="4" t="str"/>
-      <c r="M16" s="4" t="str"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="L16" s="28" t="str"/>
+      <c r="M16" s="28" t="str"/>
+      <c r="N16" s="28" t="inlineStr">
         <is>
           <t>MAX2</t>
         </is>
       </c>
-      <c r="O16" s="4" t="str"/>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="O16" s="28" t="str"/>
+      <c r="P16" s="28" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="str"/>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="Q16" s="28" t="str"/>
+      <c r="R16" s="28" t="inlineStr">
         <is>
           <t>25,200</t>
         </is>
       </c>
-      <c r="S16" s="4" t="str"/>
-      <c r="T16" s="4" t="str"/>
-      <c r="U16" s="4" t="str"/>
-      <c r="V16" s="4" t="str"/>
-      <c r="W16" s="4" t="str"/>
-      <c r="X16" s="4" t="str"/>
-      <c r="Y16" s="4" t="str"/>
-      <c r="Z16" s="4" t="inlineStr">
+      <c r="S16" s="28" t="str"/>
+      <c r="T16" s="28" t="str"/>
+      <c r="U16" s="28" t="str"/>
+      <c r="V16" s="28" t="str"/>
+      <c r="W16" s="28" t="str"/>
+      <c r="X16" s="28" t="str"/>
+      <c r="Y16" s="28" t="str"/>
+      <c r="Z16" s="28" t="inlineStr">
         <is>
           <t>MAX3/4</t>
         </is>
       </c>
-      <c r="AA16" s="4" t="str"/>
-      <c r="AB16" s="4" t="inlineStr">
+      <c r="AA16" s="28" t="str"/>
+      <c r="AB16" s="28" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC16" s="4" t="inlineStr">
+      <c r="AC16" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD16" s="4" t="str"/>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AD16" s="28" t="str"/>
+      <c r="AE16" s="28" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="str"/>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AF16" s="28" t="str"/>
+      <c r="AG16" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="inlineStr">
+      <c r="AH16" s="28" t="inlineStr">
         <is>
           <t>Bass power finesse：PE 線下 Cover Neko、Small Rubber Jig 和高比重 No Sinker 能打進 heavy cover，控線和拉離障礙是重點。</t>
         </is>
       </c>
-      <c r="AI16" s="4" t="inlineStr">
+      <c r="AI16" s="28" t="inlineStr">
         <is>
           <t>Cover Neko / Small Rubber Jig / Heavy Cover No Sinker</t>
         </is>
       </c>
-      <c r="AJ16" s="4" t="str"/>
-      <c r="AK16" s="4" t="str"/>
-      <c r="AL16" s="4" t="inlineStr">
+      <c r="AJ16" s="28" t="str"/>
+      <c r="AK16" s="28" t="str"/>
+      <c r="AL16" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM16" s="4" t="inlineStr">
+      <c r="AM16" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover power finesse / PE 直柄強攻</t>
         </is>
       </c>
-      <c r="AN16" s="4" t="inlineStr">
+      <c r="AN16" s="28" t="inlineStr">
         <is>
           <t>Cover Neko 與 Small Rubber Jig 的 heavy cover power spin</t>
         </is>
       </c>
-      <c r="AO16" s="4" t="inlineStr">
+      <c r="AO16" s="28" t="inlineStr">
         <is>
           <t>PE 線下可把 Cover Neko、Small Rubber Jig 和高比重 No Sinker 打進難攻 cover，短柄提升操作和起魚節奏；重點是精細餌進 cover 後的強制控魚。</t>
         </is>
       </c>
-      <c r="AP16" s="4" t="inlineStr">
+      <c r="AP16" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 難攻不落なヘビーカバーを攻略するパワースピニングモデル。ショートセッティングのセパレートハンドルは取り回しも抜群。他のパワーフィネスロッドと比べても圧倒的にパワフルで、通常では攻めあぐねてしまうようなヘビーカバーでも大胆に攻め込む事ができます。</t>
         </is>
       </c>
-      <c r="AQ16" s="4" t="inlineStr">
+      <c r="AQ16" s="28" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR16" s="4" t="str"/>
+      <c r="AR16" s="28" t="str"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>ORD10015</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>21GVELUS-742M</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="28" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K17" s="28" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="L17" s="4" t="str"/>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="L17" s="28" t="str"/>
+      <c r="M17" s="28" t="inlineStr">
         <is>
           <t>MAX8</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="28" t="inlineStr">
         <is>
           <t>MAX0.8</t>
         </is>
       </c>
-      <c r="O17" s="4" t="str"/>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="O17" s="28" t="str"/>
+      <c r="P17" s="28" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="str"/>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="Q17" s="28" t="str"/>
+      <c r="R17" s="28" t="inlineStr">
         <is>
           <t>25,500</t>
         </is>
       </c>
-      <c r="S17" s="4" t="str"/>
-      <c r="T17" s="4" t="str"/>
-      <c r="U17" s="4" t="str"/>
-      <c r="V17" s="4" t="str"/>
-      <c r="W17" s="4" t="str"/>
-      <c r="X17" s="4" t="str"/>
-      <c r="Y17" s="4" t="str"/>
-      <c r="Z17" s="4" t="inlineStr">
+      <c r="S17" s="28" t="str"/>
+      <c r="T17" s="28" t="str"/>
+      <c r="U17" s="28" t="str"/>
+      <c r="V17" s="28" t="str"/>
+      <c r="W17" s="28" t="str"/>
+      <c r="X17" s="28" t="str"/>
+      <c r="Y17" s="28" t="str"/>
+      <c r="Z17" s="28" t="inlineStr">
         <is>
           <t>MAX1/2</t>
         </is>
       </c>
-      <c r="AA17" s="4" t="str"/>
-      <c r="AB17" s="4" t="inlineStr">
+      <c r="AA17" s="28" t="str"/>
+      <c r="AB17" s="28" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC17" s="4" t="inlineStr">
+      <c r="AC17" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD17" s="4" t="str"/>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AD17" s="28" t="str"/>
+      <c r="AE17" s="28" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="str"/>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AF17" s="28" t="str"/>
+      <c r="AG17" s="28" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="inlineStr">
+      <c r="AH17" s="28" t="inlineStr">
         <is>
           <t>Bass PE long cast versatile：PE light rig 遠投是核心，Long Cast Neko、PE Down Shot 和 No Sinker 放前；1/2oz Spinnerbait、Vibration 作為較重搜索補充。</t>
         </is>
       </c>
-      <c r="AI17" s="4" t="inlineStr">
+      <c r="AI17" s="28" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / PE Down Shot / No Sinker / Spinnerbait / Vibration</t>
         </is>
       </c>
-      <c r="AJ17" s="4" t="str"/>
-      <c r="AK17" s="4" t="str"/>
-      <c r="AL17" s="4" t="inlineStr">
+      <c r="AJ17" s="28" t="str"/>
+      <c r="AK17" s="28" t="str"/>
+      <c r="AL17" s="28" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM17" s="4" t="inlineStr">
+      <c r="AM17" s="28" t="inlineStr">
         <is>
           <t>淡水 Bass / PE 遠投 / light rig 到中量 moving bait</t>
         </is>
       </c>
-      <c r="AN17" s="4" t="inlineStr">
+      <c r="AN17" s="28" t="inlineStr">
         <is>
           <t>PE 遠投 light rig 兼 1/2oz moving bait 直柄</t>
         </is>
       </c>
-      <c r="AO17" s="4" t="inlineStr">
+      <c r="AO17" s="28" t="inlineStr">
         <is>
           <t>Long Cast Neko、PE Down Shot、No Sinker 是核心，7'4" 長度提升遠投與回線效率；Spinnerbait、Vibration 可作較重搜索端，混合用途邊界清楚。</t>
         </is>
       </c>
-      <c r="AP17" s="4" t="inlineStr">
+      <c r="AP17" s="28" t="inlineStr">
         <is>
           <t>PEラインを使用しライトリグを遠投するスタイルに最適なモデル。ライトリグ全般から1/2ozまでのスピナーベイト、バイブレーション等のハードベイトにも対応したバーサタイル性能を持っています。</t>
         </is>
       </c>
-      <c r="AQ17" s="4" t="str"/>
-      <c r="AR17" s="4" t="str"/>
+      <c r="AQ17" s="28" t="str"/>
+      <c r="AR17" s="28" t="str"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>ORD10016</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>OR1002</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>GSBS-602XUL</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="29" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>93.7</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="29" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="29" t="inlineStr">
         <is>
           <t>0.4-3.5</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="29" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="N18" s="5" t="str"/>
-      <c r="O18" s="5" t="str"/>
-      <c r="P18" s="5" t="inlineStr">
+      <c r="N18" s="29" t="str"/>
+      <c r="O18" s="29" t="str"/>
+      <c r="P18" s="29" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q18" s="5" t="str"/>
-      <c r="R18" s="5" t="inlineStr">
+      <c r="Q18" s="29" t="str"/>
+      <c r="R18" s="29" t="inlineStr">
         <is>
           <t>63,000</t>
         </is>
       </c>
-      <c r="S18" s="5" t="str"/>
-      <c r="T18" s="5" t="str"/>
-      <c r="U18" s="5" t="str"/>
-      <c r="V18" s="5" t="str"/>
-      <c r="W18" s="5" t="str"/>
-      <c r="X18" s="5" t="str"/>
-      <c r="Y18" s="5" t="str"/>
-      <c r="Z18" s="5" t="str"/>
-      <c r="AA18" s="5" t="str"/>
-      <c r="AB18" s="5" t="inlineStr">
+      <c r="S18" s="29" t="str"/>
+      <c r="T18" s="29" t="str"/>
+      <c r="U18" s="29" t="str"/>
+      <c r="V18" s="29" t="str"/>
+      <c r="W18" s="29" t="str"/>
+      <c r="X18" s="29" t="str"/>
+      <c r="Y18" s="29" t="str"/>
+      <c r="Z18" s="29" t="str"/>
+      <c r="AA18" s="29" t="str"/>
+      <c r="AB18" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC18" s="5" t="inlineStr">
+      <c r="AC18" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD18" s="5" t="str"/>
-      <c r="AE18" s="5" t="inlineStr">
+      <c r="AD18" s="29" t="str"/>
+      <c r="AE18" s="29" t="inlineStr">
         <is>
           <t>High grade cork / burl wood</t>
         </is>
       </c>
-      <c r="AF18" s="5" t="str"/>
-      <c r="AG18" s="5" t="inlineStr">
+      <c r="AF18" s="29" t="str"/>
+      <c r="AG18" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH18" s="5" t="inlineStr">
+      <c r="AH18" s="29" t="inlineStr">
         <is>
           <t>管釣 super-light：XUL、0.4-3.5g、1-3lb 對應 Micro Spoon / Micro Crankbait，重點是低負荷出線、短咬口承接和細線控魚。</t>
         </is>
       </c>
-      <c r="AI18" s="5" t="inlineStr">
+      <c r="AI18" s="29" t="inlineStr">
         <is>
           <t>Micro Spoon / Micro Crankbait / Small Spoon</t>
         </is>
       </c>
-      <c r="AJ18" s="5" t="str"/>
-      <c r="AK18" s="5" t="str"/>
-      <c r="AL18" s="5" t="inlineStr">
+      <c r="AJ18" s="29" t="str"/>
+      <c r="AK18" s="29" t="str"/>
+      <c r="AL18" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM18" s="5" t="inlineStr">
+      <c r="AM18" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 小池高壓場 / micro spoon-crank</t>
         </is>
       </c>
-      <c r="AN18" s="5" t="inlineStr">
+      <c r="AN18" s="29" t="inlineStr">
         <is>
           <t>XUL micro spoon 與 micro crank 精細型</t>
         </is>
       </c>
-      <c r="AO18" s="5" t="inlineStr">
+      <c r="AO18" s="29" t="inlineStr">
         <is>
           <t>0.4-3.5g 與 1-3lb 線組適合低負荷 Micro Spoon、Micro Crankbait；高感 cork 與輕量 guide 對短咬口和細線控魚更有幫助。</t>
         </is>
       </c>
-      <c r="AP18" s="5" t="inlineStr">
+      <c r="AP18" s="29" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="AQ18" s="5" t="str"/>
-      <c r="AR18" s="5" t="str"/>
+      <c r="AQ18" s="29" t="str"/>
+      <c r="AR18" s="29" t="str"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>ORD10017</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>OR1002</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>GSBS-642UL</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
         <is>
           <t>98.8</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="29" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="29" t="inlineStr">
         <is>
           <t>0.5-5</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="29" t="inlineStr">
         <is>
           <t>1.5-4</t>
         </is>
       </c>
-      <c r="N19" s="5" t="str"/>
-      <c r="O19" s="5" t="str"/>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="N19" s="29" t="str"/>
+      <c r="O19" s="29" t="str"/>
+      <c r="P19" s="29" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="str"/>
-      <c r="R19" s="5" t="inlineStr">
+      <c r="Q19" s="29" t="str"/>
+      <c r="R19" s="29" t="inlineStr">
         <is>
           <t>64,000</t>
         </is>
       </c>
-      <c r="S19" s="5" t="str"/>
-      <c r="T19" s="5" t="str"/>
-      <c r="U19" s="5" t="str"/>
-      <c r="V19" s="5" t="str"/>
-      <c r="W19" s="5" t="str"/>
-      <c r="X19" s="5" t="str"/>
-      <c r="Y19" s="5" t="str"/>
-      <c r="Z19" s="5" t="str"/>
-      <c r="AA19" s="5" t="str"/>
-      <c r="AB19" s="5" t="inlineStr">
+      <c r="S19" s="29" t="str"/>
+      <c r="T19" s="29" t="str"/>
+      <c r="U19" s="29" t="str"/>
+      <c r="V19" s="29" t="str"/>
+      <c r="W19" s="29" t="str"/>
+      <c r="X19" s="29" t="str"/>
+      <c r="Y19" s="29" t="str"/>
+      <c r="Z19" s="29" t="str"/>
+      <c r="AA19" s="29" t="str"/>
+      <c r="AB19" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="inlineStr">
+      <c r="AC19" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD19" s="5" t="str"/>
-      <c r="AE19" s="5" t="inlineStr">
+      <c r="AD19" s="29" t="str"/>
+      <c r="AE19" s="29" t="inlineStr">
         <is>
           <t>High grade cork / burl wood</t>
         </is>
       </c>
-      <c r="AF19" s="5" t="str"/>
-      <c r="AG19" s="5" t="inlineStr">
+      <c r="AF19" s="29" t="str"/>
+      <c r="AG19" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH19" s="5" t="inlineStr">
+      <c r="AH19" s="29" t="inlineStr">
         <is>
           <t>管釣中量 lure：Spoon、Crankbait 和 Small Minnow 的拋投與回收穩定，兼顧細線操作和中距離控魚。</t>
         </is>
       </c>
-      <c r="AI19" s="5" t="inlineStr">
+      <c r="AI19" s="29" t="inlineStr">
         <is>
           <t>Spoon / Crankbait / Small Minnow</t>
         </is>
       </c>
-      <c r="AJ19" s="5" t="str"/>
-      <c r="AK19" s="5" t="str"/>
-      <c r="AL19" s="5" t="inlineStr">
+      <c r="AJ19" s="29" t="str"/>
+      <c r="AK19" s="29" t="str"/>
+      <c r="AL19" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM19" s="5" t="inlineStr">
+      <c r="AM19" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 標準池 spoon-crank / 中距離控魚</t>
         </is>
       </c>
-      <c r="AN19" s="5" t="inlineStr">
+      <c r="AN19" s="29" t="inlineStr">
         <is>
           <t>UL spoon、crank、small minnow 中量泛用</t>
         </is>
       </c>
-      <c r="AO19" s="5" t="inlineStr">
+      <c r="AO19" s="29" t="inlineStr">
         <is>
           <t>0.5-5g、1.5-4lb 覆蓋標準 Spoon、Crankbait 和 Small Minnow，較 602XUL 更能應付中距離和稍大魚，仍保留細線操作感。</t>
         </is>
       </c>
-      <c r="AP19" s="5" t="inlineStr">
+      <c r="AP19" s="29" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="AQ19" s="5" t="str"/>
-      <c r="AR19" s="5" t="str"/>
+      <c r="AQ19" s="29" t="str"/>
+      <c r="AR19" s="29" t="str"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>ORD10018</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>OR1002</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>GSBS-672L</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="29" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="29" t="inlineStr">
         <is>
           <t>102.6</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="29" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="29" t="inlineStr">
         <is>
           <t>0.6-7</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="29" t="inlineStr">
         <is>
           <t>2-5</t>
         </is>
       </c>
-      <c r="N20" s="5" t="str"/>
-      <c r="O20" s="5" t="str"/>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="N20" s="29" t="str"/>
+      <c r="O20" s="29" t="str"/>
+      <c r="P20" s="29" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="str"/>
-      <c r="R20" s="5" t="inlineStr">
+      <c r="Q20" s="29" t="str"/>
+      <c r="R20" s="29" t="inlineStr">
         <is>
           <t>65,000</t>
         </is>
       </c>
-      <c r="S20" s="5" t="str"/>
-      <c r="T20" s="5" t="str"/>
-      <c r="U20" s="5" t="str"/>
-      <c r="V20" s="5" t="str"/>
-      <c r="W20" s="5" t="str"/>
-      <c r="X20" s="5" t="str"/>
-      <c r="Y20" s="5" t="str"/>
-      <c r="Z20" s="5" t="str"/>
-      <c r="AA20" s="5" t="str"/>
-      <c r="AB20" s="5" t="inlineStr">
+      <c r="S20" s="29" t="str"/>
+      <c r="T20" s="29" t="str"/>
+      <c r="U20" s="29" t="str"/>
+      <c r="V20" s="29" t="str"/>
+      <c r="W20" s="29" t="str"/>
+      <c r="X20" s="29" t="str"/>
+      <c r="Y20" s="29" t="str"/>
+      <c r="Z20" s="29" t="str"/>
+      <c r="AA20" s="29" t="str"/>
+      <c r="AB20" s="29" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC20" s="5" t="inlineStr">
+      <c r="AC20" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD20" s="5" t="str"/>
-      <c r="AE20" s="5" t="inlineStr">
+      <c r="AD20" s="29" t="str"/>
+      <c r="AE20" s="29" t="inlineStr">
         <is>
           <t>High grade cork / burl wood</t>
         </is>
       </c>
-      <c r="AF20" s="5" t="str"/>
-      <c r="AG20" s="5" t="inlineStr">
+      <c r="AF20" s="29" t="str"/>
+      <c r="AG20" s="29" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH20" s="5" t="inlineStr">
+      <c r="AH20" s="29" t="inlineStr">
         <is>
           <t>管釣中大型 lure：Full-size Spoon、Crankbait 和 Minnow 負荷更高，長距離控線與大型 trout 控魚比小餌型號更有餘量。</t>
         </is>
       </c>
-      <c r="AI20" s="5" t="inlineStr">
+      <c r="AI20" s="29" t="inlineStr">
         <is>
           <t>Full-size Spoon / Crankbait / Minnow</t>
         </is>
       </c>
-      <c r="AJ20" s="5" t="str"/>
-      <c r="AK20" s="5" t="str"/>
-      <c r="AL20" s="5" t="inlineStr">
+      <c r="AJ20" s="29" t="str"/>
+      <c r="AK20" s="29" t="str"/>
+      <c r="AL20" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM20" s="5" t="inlineStr">
+      <c r="AM20" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 大池遠投 / full-size lure</t>
         </is>
       </c>
-      <c r="AN20" s="5" t="inlineStr">
+      <c r="AN20" s="29" t="inlineStr">
         <is>
           <t>L power full-size spoon / crank / minnow 強化型</t>
         </is>
       </c>
-      <c r="AO20" s="5" t="inlineStr">
+      <c r="AO20" s="29" t="inlineStr">
         <is>
           <t>0.6-7g、2-5lb 可承接 Full-size Spoon、Crankbait、Minnow，長度和 L power 更適合大池遠投與較大型 trout 控魚。</t>
         </is>
       </c>
-      <c r="AP20" s="5" t="inlineStr">
+      <c r="AP20" s="29" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="AQ20" s="5" t="str"/>
-      <c r="AR20" s="5" t="str"/>
+      <c r="AQ20" s="29" t="str"/>
+      <c r="AR20" s="29" t="str"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>ORD10019</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>26GBELPS-572XUL-S</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="28" t="inlineStr">
         <is>
           <t>87.4</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="28" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="28" t="inlineStr">
         <is>
           <t>0.2-2.5</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M21" s="28" t="inlineStr">
         <is>
           <t>MAX3</t>
         </is>
       </c>
-      <c r="N21" s="4" t="str"/>
-      <c r="O21" s="4" t="str"/>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="N21" s="28" t="str"/>
+      <c r="O21" s="28" t="str"/>
+      <c r="P21" s="28" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="str"/>
-      <c r="R21" s="4" t="inlineStr">
+      <c r="Q21" s="28" t="str"/>
+      <c r="R21" s="28" t="inlineStr">
         <is>
           <t>54,000</t>
         </is>
       </c>
-      <c r="S21" s="4" t="str"/>
-      <c r="T21" s="4" t="str"/>
-      <c r="U21" s="4" t="str"/>
-      <c r="V21" s="4" t="str"/>
-      <c r="W21" s="4" t="str"/>
-      <c r="X21" s="4" t="str"/>
-      <c r="Y21" s="4" t="str"/>
-      <c r="Z21" s="4" t="str"/>
-      <c r="AA21" s="4" t="str"/>
-      <c r="AB21" s="4" t="inlineStr">
+      <c r="S21" s="28" t="str"/>
+      <c r="T21" s="28" t="str"/>
+      <c r="U21" s="28" t="str"/>
+      <c r="V21" s="28" t="str"/>
+      <c r="W21" s="28" t="str"/>
+      <c r="X21" s="28" t="str"/>
+      <c r="Y21" s="28" t="str"/>
+      <c r="Z21" s="28" t="str"/>
+      <c r="AA21" s="28" t="str"/>
+      <c r="AB21" s="28" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC21" s="4" t="inlineStr">
+      <c r="AC21" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD21" s="4" t="str"/>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AD21" s="28" t="str"/>
+      <c r="AE21" s="28" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="str"/>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AF21" s="28" t="str"/>
+      <c r="AG21" s="28" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
+      <c r="AH21" s="28" t="inlineStr">
         <is>
           <t>管釣 solid tip 微小餌：Micro Spoon、Micro Crankbait 在シビア狀況下更容易讓魚口殘留，Vertical Spoon 可利用 tubular 部分張力做縦釣り。</t>
         </is>
       </c>
-      <c r="AI21" s="4" t="inlineStr">
+      <c r="AI21" s="28" t="inlineStr">
         <is>
           <t>Micro Spoon / Micro Crankbait / Vertical Spoon</t>
         </is>
       </c>
-      <c r="AJ21" s="4" t="str"/>
-      <c r="AK21" s="4" t="str"/>
-      <c r="AL21" s="4" t="inlineStr">
+      <c r="AJ21" s="28" t="str"/>
+      <c r="AK21" s="28" t="str"/>
+      <c r="AL21" s="28" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM21" s="4" t="inlineStr">
+      <c r="AM21" s="28" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 高壓慢魚 / ester line micro lure</t>
         </is>
       </c>
-      <c r="AN21" s="4" t="inlineStr">
+      <c r="AN21" s="28" t="inlineStr">
         <is>
           <t>solid tip micro spoon / micro crank 掛け型精細</t>
         </is>
       </c>
-      <c r="AO21" s="4" t="inlineStr">
+      <c r="AO21" s="28" t="inlineStr">
         <is>
           <t>Micro Spoon、Micro Crankbait 在シビア場更容易讓魚口殘留，solid tip 吸收短咬，tubular 部分張力可補縦釣り操作。</t>
         </is>
       </c>
-      <c r="AP21" s="4" t="inlineStr">
+      <c r="AP21" s="28" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉 マイクロスプーン、マイクロクランクなどに対応したシビアな状況下で活躍するソリッドティップモデル。チューブラーティップで掛からないときでも繊細なソリッドティップが曲がり込み、フックが口に残ることで掛けることが可能に。チューブラー部分の張りを活かし、縦釣りなどにも対応する。主流となりつつあるエステルラインに対応したガイドセッティング。</t>
         </is>
       </c>
-      <c r="AQ21" s="4" t="inlineStr">
+      <c r="AQ21" s="28" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉</t>
         </is>
       </c>
-      <c r="AR21" s="4" t="str"/>
+      <c r="AR21" s="28" t="str"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>ORD10020</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>26GBELPS-582SUL-T</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I22" s="28" t="inlineStr">
         <is>
           <t>88.6</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K22" s="28" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="28" t="inlineStr">
         <is>
           <t>0.5-3.5</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N22" s="4" t="str"/>
-      <c r="O22" s="4" t="str"/>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="N22" s="28" t="str"/>
+      <c r="O22" s="28" t="str"/>
+      <c r="P22" s="28" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="str"/>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="Q22" s="28" t="str"/>
+      <c r="R22" s="28" t="inlineStr">
         <is>
           <t>55,000</t>
         </is>
       </c>
-      <c r="S22" s="4" t="str"/>
-      <c r="T22" s="4" t="str"/>
-      <c r="U22" s="4" t="str"/>
-      <c r="V22" s="4" t="str"/>
-      <c r="W22" s="4" t="str"/>
-      <c r="X22" s="4" t="str"/>
-      <c r="Y22" s="4" t="str"/>
-      <c r="Z22" s="4" t="str"/>
-      <c r="AA22" s="4" t="str"/>
-      <c r="AB22" s="4" t="inlineStr">
+      <c r="S22" s="28" t="str"/>
+      <c r="T22" s="28" t="str"/>
+      <c r="U22" s="28" t="str"/>
+      <c r="V22" s="28" t="str"/>
+      <c r="W22" s="28" t="str"/>
+      <c r="X22" s="28" t="str"/>
+      <c r="Y22" s="28" t="str"/>
+      <c r="Z22" s="28" t="str"/>
+      <c r="AA22" s="28" t="str"/>
+      <c r="AB22" s="28" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC22" s="4" t="inlineStr">
+      <c r="AC22" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD22" s="4" t="str"/>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AD22" s="28" t="str"/>
+      <c r="AE22" s="28" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="str"/>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AF22" s="28" t="str"/>
+      <c r="AG22" s="28" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH22" s="4" t="inlineStr">
+      <c r="AH22" s="28" t="inlineStr">
         <is>
           <t>管釣掛け型巻き：1.6g Spoon 和 Crankbait 是常用主軸，張りを活かして掛けに行く；Twitching Plug 作為操作系 plug 補充。</t>
         </is>
       </c>
-      <c r="AI22" s="4" t="inlineStr">
+      <c r="AI22" s="28" t="inlineStr">
         <is>
           <t>1.6g Spoon / Crankbait / Twitching Plug</t>
         </is>
       </c>
-      <c r="AJ22" s="4" t="str"/>
-      <c r="AK22" s="4" t="str"/>
-      <c r="AL22" s="4" t="inlineStr">
+      <c r="AJ22" s="28" t="str"/>
+      <c r="AK22" s="28" t="str"/>
+      <c r="AL22" s="28" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM22" s="4" t="inlineStr">
+      <c r="AM22" s="28" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 標準放流後節奏 / spoon-crank 巻き</t>
         </is>
       </c>
-      <c r="AN22" s="4" t="inlineStr">
+      <c r="AN22" s="28" t="inlineStr">
         <is>
           <t>1.6g Spoon 與 Crankbait 的掛け型巻き竿</t>
         </is>
       </c>
-      <c r="AO22" s="4" t="inlineStr">
+      <c r="AO22" s="28" t="inlineStr">
         <is>
           <t>1.6g 前後 Spoon、Crankbait 平收時能主動掛けに行く，張りを活かして操作系 plug 也能處理；適合 ester line 主流配置。</t>
         </is>
       </c>
-      <c r="AP22" s="4" t="inlineStr">
+      <c r="AP22" s="28" t="inlineStr">
         <is>
           <t>エリアトラウトでは一般的となる1.6g前後のスプーンやクランクなどのプラグといった巻きの釣りに幅広く対応するモデル。バイトを掛けていくスタイルのロッドとなっており、張りを活かした操作系のプラグなどにも対応。主流となりつつあるエステルラインに対応したガイドセッティング。</t>
         </is>
       </c>
-      <c r="AQ22" s="4" t="str"/>
-      <c r="AR22" s="4" t="str"/>
+      <c r="AQ22" s="28" t="str"/>
+      <c r="AR22" s="28" t="str"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>ORD10021</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>26GBELPS-612UL-T</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="28" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K23" s="28" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="28" t="inlineStr">
         <is>
           <t>0.6-5</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M23" s="28" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N23" s="4" t="str"/>
-      <c r="O23" s="4" t="str"/>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="N23" s="28" t="str"/>
+      <c r="O23" s="28" t="str"/>
+      <c r="P23" s="28" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="str"/>
-      <c r="R23" s="4" t="inlineStr">
+      <c r="Q23" s="28" t="str"/>
+      <c r="R23" s="28" t="inlineStr">
         <is>
           <t>56,000</t>
         </is>
       </c>
-      <c r="S23" s="4" t="str"/>
-      <c r="T23" s="4" t="str"/>
-      <c r="U23" s="4" t="str"/>
-      <c r="V23" s="4" t="str"/>
-      <c r="W23" s="4" t="str"/>
-      <c r="X23" s="4" t="str"/>
-      <c r="Y23" s="4" t="str"/>
-      <c r="Z23" s="4" t="str"/>
-      <c r="AA23" s="4" t="str"/>
-      <c r="AB23" s="4" t="inlineStr">
+      <c r="S23" s="28" t="str"/>
+      <c r="T23" s="28" t="str"/>
+      <c r="U23" s="28" t="str"/>
+      <c r="V23" s="28" t="str"/>
+      <c r="W23" s="28" t="str"/>
+      <c r="X23" s="28" t="str"/>
+      <c r="Y23" s="28" t="str"/>
+      <c r="Z23" s="28" t="str"/>
+      <c r="AA23" s="28" t="str"/>
+      <c r="AB23" s="28" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC23" s="4" t="inlineStr">
+      <c r="AC23" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD23" s="4" t="str"/>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AD23" s="28" t="str"/>
+      <c r="AE23" s="28" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="str"/>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AF23" s="28" t="str"/>
+      <c r="AG23" s="28" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
+      <c r="AH23" s="28" t="inlineStr">
         <is>
           <t>管釣放流 / 大型 plug：Heavy Spoon、Full-size Crankbait 和 Minnow Twitching 負荷更高，出線和補刺要支撐大型 trout。</t>
         </is>
       </c>
-      <c r="AI23" s="4" t="inlineStr">
+      <c r="AI23" s="28" t="inlineStr">
         <is>
           <t>Heavy Spoon / Full-size Crankbait / Minnow Twitching</t>
         </is>
       </c>
-      <c r="AJ23" s="4" t="str"/>
-      <c r="AK23" s="4" t="str"/>
-      <c r="AL23" s="4" t="inlineStr">
+      <c r="AJ23" s="28" t="str"/>
+      <c r="AK23" s="28" t="str"/>
+      <c r="AL23" s="28" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM23" s="4" t="inlineStr">
+      <c r="AM23" s="28" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 放流狩り / 大型 plug 與色物</t>
         </is>
       </c>
-      <c r="AN23" s="4" t="inlineStr">
+      <c r="AN23" s="28" t="inlineStr">
         <is>
           <t>Heavy Spoon、Full-size Crank、Minnow Twitching 攻擊型</t>
         </is>
       </c>
-      <c r="AO23" s="4" t="inlineStr">
+      <c r="AO23" s="28" t="inlineStr">
         <is>
           <t>重め Spoon 和 Full-size Crank 用於放流魚快速搜索，Fast taper 可做 Minnow Twitching；bat power 對大型 trout 和色物更安心。</t>
         </is>
       </c>
-      <c r="AP23" s="4" t="inlineStr">
+      <c r="AP23" s="28" t="inlineStr">
         <is>
           <t>放流狩りなどで使用する重めのスプーンや、フルサイズクランクなどの大型プラグの使用を想定したモデル。ファーストテーパーなアクションはミノーのトゥイッチングにも対応。バットパワーがあるので色物など大型狙いにもおすすめ。</t>
         </is>
       </c>
-      <c r="AQ23" s="4" t="str"/>
-      <c r="AR23" s="4" t="str"/>
+      <c r="AQ23" s="28" t="str"/>
+      <c r="AR23" s="28" t="str"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>ORD10022</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>26GBELPS-642L-T</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="28" t="inlineStr">
         <is>
           <t>98.8</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="28" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="28" t="inlineStr">
         <is>
           <t>1-7</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M24" s="28" t="inlineStr">
         <is>
           <t>MAX5</t>
         </is>
       </c>
-      <c r="N24" s="4" t="str"/>
-      <c r="O24" s="4" t="str"/>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="N24" s="28" t="str"/>
+      <c r="O24" s="28" t="str"/>
+      <c r="P24" s="28" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="str"/>
-      <c r="R24" s="4" t="inlineStr">
+      <c r="Q24" s="28" t="str"/>
+      <c r="R24" s="28" t="inlineStr">
         <is>
           <t>57,000</t>
         </is>
       </c>
-      <c r="S24" s="4" t="str"/>
-      <c r="T24" s="4" t="str"/>
-      <c r="U24" s="4" t="str"/>
-      <c r="V24" s="4" t="str"/>
-      <c r="W24" s="4" t="str"/>
-      <c r="X24" s="4" t="str"/>
-      <c r="Y24" s="4" t="str"/>
-      <c r="Z24" s="4" t="str"/>
-      <c r="AA24" s="4" t="str"/>
-      <c r="AB24" s="4" t="inlineStr">
+      <c r="S24" s="28" t="str"/>
+      <c r="T24" s="28" t="str"/>
+      <c r="U24" s="28" t="str"/>
+      <c r="V24" s="28" t="str"/>
+      <c r="W24" s="28" t="str"/>
+      <c r="X24" s="28" t="str"/>
+      <c r="Y24" s="28" t="str"/>
+      <c r="Z24" s="28" t="str"/>
+      <c r="AA24" s="28" t="str"/>
+      <c r="AB24" s="28" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="inlineStr">
+      <c r="AC24" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD24" s="4" t="str"/>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AD24" s="28" t="str"/>
+      <c r="AE24" s="28" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="str"/>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AF24" s="28" t="str"/>
+      <c r="AG24" s="28" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH24" s="4" t="inlineStr">
+      <c r="AH24" s="28" t="inlineStr">
         <is>
           <t>管釣大型 trout：Large Plug、Full-size Spoon 和 Full-size Crankbait 為主，較粗線徑與高負荷 lure 出線更穩。</t>
         </is>
       </c>
-      <c r="AI24" s="4" t="inlineStr">
+      <c r="AI24" s="28" t="inlineStr">
         <is>
           <t>Large Plug / Full-size Spoon / Full-size Crankbait</t>
         </is>
       </c>
-      <c r="AJ24" s="4" t="str"/>
-      <c r="AK24" s="4" t="str"/>
-      <c r="AL24" s="4" t="inlineStr">
+      <c r="AJ24" s="28" t="str"/>
+      <c r="AK24" s="28" t="str"/>
+      <c r="AL24" s="28" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM24" s="4" t="inlineStr">
+      <c r="AM24" s="28" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 大規模 pond / 超大型 trout</t>
         </is>
       </c>
-      <c r="AN24" s="4" t="inlineStr">
+      <c r="AN24" s="28" t="inlineStr">
         <is>
           <t>Large Plug、Full-size Spoon 的大型魚 power 型</t>
         </is>
       </c>
-      <c r="AO24" s="4" t="inlineStr">
+      <c r="AO24" s="28" t="inlineStr">
         <is>
           <t>L power 對大型 plug、Full-size Spoon 負荷更穩，適合大規模 pond 搜索和超大型 trout 控魚；不是 micro lure 精細路線。</t>
         </is>
       </c>
-      <c r="AP24" s="4" t="inlineStr">
+      <c r="AP24" s="28" t="inlineStr">
         <is>
           <t>比較的大規模なポンドで大型のプラグやスプーンなどを使用し、大型のトラウトを狙うことを想定したモデル。シリーズ内で最もパワーがあるので超大型といわれるサイズとも渡り合えるロッド。</t>
         </is>
       </c>
-      <c r="AQ24" s="4" t="str"/>
-      <c r="AR24" s="4" t="str"/>
+      <c r="AQ24" s="28" t="str"/>
+      <c r="AR24" s="28" t="str"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>ORD10023</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>26GBELPS-672SUL-T</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="28" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="28" t="inlineStr">
         <is>
           <t>102.6</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K25" s="28" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="28" t="inlineStr">
         <is>
           <t>0.5-4</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M25" s="28" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N25" s="4" t="str"/>
-      <c r="O25" s="4" t="str"/>
-      <c r="P25" s="4" t="inlineStr">
+      <c r="N25" s="28" t="str"/>
+      <c r="O25" s="28" t="str"/>
+      <c r="P25" s="28" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q25" s="4" t="str"/>
-      <c r="R25" s="4" t="inlineStr">
+      <c r="Q25" s="28" t="str"/>
+      <c r="R25" s="28" t="inlineStr">
         <is>
           <t>58,000</t>
         </is>
       </c>
-      <c r="S25" s="4" t="str"/>
-      <c r="T25" s="4" t="str"/>
-      <c r="U25" s="4" t="str"/>
-      <c r="V25" s="4" t="str"/>
-      <c r="W25" s="4" t="str"/>
-      <c r="X25" s="4" t="str"/>
-      <c r="Y25" s="4" t="str"/>
-      <c r="Z25" s="4" t="str"/>
-      <c r="AA25" s="4" t="str"/>
-      <c r="AB25" s="4" t="inlineStr">
+      <c r="S25" s="28" t="str"/>
+      <c r="T25" s="28" t="str"/>
+      <c r="U25" s="28" t="str"/>
+      <c r="V25" s="28" t="str"/>
+      <c r="W25" s="28" t="str"/>
+      <c r="X25" s="28" t="str"/>
+      <c r="Y25" s="28" t="str"/>
+      <c r="Z25" s="28" t="str"/>
+      <c r="AA25" s="28" t="str"/>
+      <c r="AB25" s="28" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC25" s="4" t="inlineStr">
+      <c r="AC25" s="28" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD25" s="4" t="str"/>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AD25" s="28" t="str"/>
+      <c r="AE25" s="28" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="str"/>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AF25" s="28" t="str"/>
+      <c r="AG25" s="28" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH25" s="4" t="inlineStr">
+      <c r="AH25" s="28" t="inlineStr">
         <is>
           <t>管釣遠投：Long Cast Spoon、Crankbait 和 Minnow 用於大池沖目搜索，長竿出線與遠距離控魚是重點。</t>
         </is>
       </c>
-      <c r="AI25" s="4" t="inlineStr">
+      <c r="AI25" s="28" t="inlineStr">
         <is>
           <t>Long Cast Spoon / Long Cast Crankbait / Minnow</t>
         </is>
       </c>
-      <c r="AJ25" s="4" t="str"/>
-      <c r="AK25" s="4" t="str"/>
-      <c r="AL25" s="4" t="inlineStr">
+      <c r="AJ25" s="28" t="str"/>
+      <c r="AK25" s="28" t="str"/>
+      <c r="AL25" s="28" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM25" s="4" t="inlineStr">
+      <c r="AM25" s="28" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 大池沖目遠投 / 未被打擾魚群</t>
         </is>
       </c>
-      <c r="AN25" s="4" t="inlineStr">
+      <c r="AN25" s="28" t="inlineStr">
         <is>
           <t>Long Cast Spoon / Crank 遠投搜索型</t>
         </is>
       </c>
-      <c r="AO25" s="4" t="inlineStr">
+      <c r="AO25" s="28" t="inlineStr">
         <is>
           <t>6'7" 長度把 Spoon、Crankbait 投到大池沖目，SUL 調性在遠距離中魚後更不易脫鉤；適合找未被釣壓干擾的魚。</t>
         </is>
       </c>
-      <c r="AP25" s="4" t="inlineStr">
+      <c r="AP25" s="28" t="inlineStr">
         <is>
           <t>大規模ポンドなどで狙われていない沖にいる大型を遠投して釣っていくことを想定したモデル。様々なルアーを扱えるアクションに設定。また、その6’7”というレングスを活かし、バラシを抑えて寄せてくることが可能。</t>
         </is>
       </c>
-      <c r="AQ25" s="4" t="str"/>
-      <c r="AR25" s="4" t="str"/>
+      <c r="AQ25" s="28" t="str"/>
+      <c r="AR25" s="28" t="str"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>ORD10024</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>24GBELUS-582XUL-T</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="29" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="29" t="inlineStr">
         <is>
           <t>89.5</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="29" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="29" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="29" t="inlineStr">
         <is>
           <t>0.4-3.5</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M26" s="29" t="inlineStr">
         <is>
           <t>MAX3</t>
         </is>
       </c>
-      <c r="N26" s="5" t="str"/>
-      <c r="O26" s="5" t="str"/>
-      <c r="P26" s="5" t="inlineStr">
+      <c r="N26" s="29" t="str"/>
+      <c r="O26" s="29" t="str"/>
+      <c r="P26" s="29" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q26" s="5" t="str"/>
-      <c r="R26" s="5" t="inlineStr">
+      <c r="Q26" s="29" t="str"/>
+      <c r="R26" s="29" t="inlineStr">
         <is>
           <t>23,500</t>
         </is>
       </c>
-      <c r="S26" s="5" t="str"/>
-      <c r="T26" s="5" t="str"/>
-      <c r="U26" s="5" t="str"/>
-      <c r="V26" s="5" t="str"/>
-      <c r="W26" s="5" t="str"/>
-      <c r="X26" s="5" t="str"/>
-      <c r="Y26" s="5" t="str"/>
-      <c r="Z26" s="5" t="str"/>
-      <c r="AA26" s="5" t="str"/>
-      <c r="AB26" s="5" t="inlineStr">
+      <c r="S26" s="29" t="str"/>
+      <c r="T26" s="29" t="str"/>
+      <c r="U26" s="29" t="str"/>
+      <c r="V26" s="29" t="str"/>
+      <c r="W26" s="29" t="str"/>
+      <c r="X26" s="29" t="str"/>
+      <c r="Y26" s="29" t="str"/>
+      <c r="Z26" s="29" t="str"/>
+      <c r="AA26" s="29" t="str"/>
+      <c r="AB26" s="29" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC26" s="5" t="inlineStr">
+      <c r="AC26" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD26" s="5" t="str"/>
-      <c r="AE26" s="5" t="str"/>
-      <c r="AF26" s="5" t="str"/>
-      <c r="AG26" s="5" t="inlineStr">
+      <c r="AD26" s="29" t="str"/>
+      <c r="AE26" s="29" t="str"/>
+      <c r="AF26" s="29" t="str"/>
+      <c r="AG26" s="29" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH26" s="5" t="inlineStr">
+      <c r="AH26" s="29" t="inlineStr">
         <is>
           <t>管釣 micro 巻き：Micro Spoon 和 Micro Crankbait 一定速 retrieve 是核心，XUL tubular 保持低負荷出線，柔軟性用來承接 short bite。</t>
         </is>
       </c>
-      <c r="AI26" s="5" t="inlineStr">
+      <c r="AI26" s="29" t="inlineStr">
         <is>
           <t>Micro Spoon / Micro Crankbait</t>
         </is>
       </c>
-      <c r="AJ26" s="5" t="str"/>
-      <c r="AK26" s="5" t="str"/>
-      <c r="AL26" s="5" t="inlineStr">
+      <c r="AJ26" s="29" t="str"/>
+      <c r="AK26" s="29" t="str"/>
+      <c r="AL26" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM26" s="5" t="inlineStr">
+      <c r="AM26" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / micro spoon-crank 定速巻き</t>
         </is>
       </c>
-      <c r="AN26" s="5" t="inlineStr">
+      <c r="AN26" s="29" t="inlineStr">
         <is>
           <t>Micro Spoon、Micro Crankbait short-bite 對應型</t>
         </is>
       </c>
-      <c r="AO26" s="5" t="inlineStr">
+      <c r="AO26" s="29" t="inlineStr">
         <is>
           <t>定速 retrieve micro lure 時，XUL tubular 和柔軟性降低彈口；OP-01 碳纖 reel seat 提升短咬口感知。</t>
         </is>
       </c>
-      <c r="AP26" s="5" t="inlineStr">
+      <c r="AP26" s="29" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉 マイクロスプーンやマイクロクランクを一定スピードでリトリーブするような巻きの釣りを主体としたモデル。ショートバイトを弾かず乗せることができる柔軟性を持ちながらもオリジナルカーボンリールシートによって高感度化も実現しました。</t>
         </is>
       </c>
-      <c r="AQ26" s="5" t="inlineStr">
+      <c r="AQ26" s="29" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉</t>
         </is>
       </c>
-      <c r="AR26" s="5" t="str"/>
+      <c r="AR26" s="29" t="str"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>ORD10025</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>25GBELUS-612SUL-S</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="29" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="29" t="inlineStr">
         <is>
           <t>95.0</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="29" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="29" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" s="29" t="inlineStr">
         <is>
           <t>0.4-4.0</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" s="29" t="inlineStr">
         <is>
           <t>MAX 4</t>
         </is>
       </c>
-      <c r="N27" s="5" t="str"/>
-      <c r="O27" s="5" t="str"/>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="N27" s="29" t="str"/>
+      <c r="O27" s="29" t="str"/>
+      <c r="P27" s="29" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="str"/>
-      <c r="R27" s="5" t="inlineStr">
+      <c r="Q27" s="29" t="str"/>
+      <c r="R27" s="29" t="inlineStr">
         <is>
           <t>22,500</t>
         </is>
       </c>
-      <c r="S27" s="5" t="str"/>
-      <c r="T27" s="5" t="str"/>
-      <c r="U27" s="5" t="str"/>
-      <c r="V27" s="5" t="str"/>
-      <c r="W27" s="5" t="str"/>
-      <c r="X27" s="5" t="str"/>
-      <c r="Y27" s="5" t="str"/>
-      <c r="Z27" s="5" t="str"/>
-      <c r="AA27" s="5" t="str"/>
-      <c r="AB27" s="5" t="inlineStr">
+      <c r="S27" s="29" t="str"/>
+      <c r="T27" s="29" t="str"/>
+      <c r="U27" s="29" t="str"/>
+      <c r="V27" s="29" t="str"/>
+      <c r="W27" s="29" t="str"/>
+      <c r="X27" s="29" t="str"/>
+      <c r="Y27" s="29" t="str"/>
+      <c r="Z27" s="29" t="str"/>
+      <c r="AA27" s="29" t="str"/>
+      <c r="AB27" s="29" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC27" s="5" t="inlineStr">
+      <c r="AC27" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD27" s="5" t="str"/>
-      <c r="AE27" s="5" t="str"/>
-      <c r="AF27" s="5" t="str"/>
-      <c r="AG27" s="5" t="inlineStr">
+      <c r="AD27" s="29" t="str"/>
+      <c r="AE27" s="29" t="str"/>
+      <c r="AF27" s="29" t="str"/>
+      <c r="AG27" s="29" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH27" s="5" t="inlineStr">
+      <c r="AH27" s="29" t="inlineStr">
         <is>
           <t>管釣 slow retrieve：Slow Spoon 與 Micro Crankbait 是主軸，solid tip 讓 short bite 時 hook 留在口內，掛けた後由 belly 順暢吸收魚的反撲。</t>
         </is>
       </c>
-      <c r="AI27" s="5" t="inlineStr">
+      <c r="AI27" s="29" t="inlineStr">
         <is>
           <t>Slow Retrieve Spoon / Micro Crankbait / Spoon</t>
         </is>
       </c>
-      <c r="AJ27" s="5" t="str"/>
-      <c r="AK27" s="5" t="str"/>
-      <c r="AL27" s="5" t="inlineStr">
+      <c r="AJ27" s="29" t="str"/>
+      <c r="AK27" s="29" t="str"/>
+      <c r="AL27" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM27" s="5" t="inlineStr">
+      <c r="AM27" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / slow retrieve / 高壓短咬</t>
         </is>
       </c>
-      <c r="AN27" s="5" t="inlineStr">
+      <c r="AN27" s="29" t="inlineStr">
         <is>
           <t>Slow Spoon 與 Micro Crank solid tip 乗せ掛け型</t>
         </is>
       </c>
-      <c r="AO27" s="5" t="inlineStr">
+      <c r="AO27" s="29" t="inlineStr">
         <is>
           <t>Slow Spoon、Micro Crankbait 是主軸，solid tip 讓高壓短咬時 hook 留在口內，掛けた後 belly 順暢彎曲降低脫鉤。</t>
         </is>
       </c>
-      <c r="AP27" s="5" t="inlineStr">
+      <c r="AP27" s="29" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉 スプーニングとマイクロクランクのスローリトリーブがメインとなるモデル。繊細なソリッドティップを採用することで、ショートバイトが多発するシビアな状況下でもフックを口に残し、掛けた後はスムースに曲がりこむベリーで魚をバラさずにキャッチすることが可能です。</t>
         </is>
       </c>
-      <c r="AQ27" s="5" t="inlineStr">
+      <c r="AQ27" s="29" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉</t>
         </is>
       </c>
-      <c r="AR27" s="5" t="str"/>
+      <c r="AR27" s="29" t="str"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>ORD10026</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>24GBELUS-622SUL-T</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="29" t="inlineStr">
         <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="29" t="inlineStr">
         <is>
           <t>97.0</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="29" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="29" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" s="29" t="inlineStr">
         <is>
           <t>0.5-5</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M28" s="29" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N28" s="5" t="str"/>
-      <c r="O28" s="5" t="str"/>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="N28" s="29" t="str"/>
+      <c r="O28" s="29" t="str"/>
+      <c r="P28" s="29" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q28" s="5" t="str"/>
-      <c r="R28" s="5" t="inlineStr">
+      <c r="Q28" s="29" t="str"/>
+      <c r="R28" s="29" t="inlineStr">
         <is>
           <t>24,000</t>
         </is>
       </c>
-      <c r="S28" s="5" t="str"/>
-      <c r="T28" s="5" t="str"/>
-      <c r="U28" s="5" t="str"/>
-      <c r="V28" s="5" t="str"/>
-      <c r="W28" s="5" t="str"/>
-      <c r="X28" s="5" t="str"/>
-      <c r="Y28" s="5" t="str"/>
-      <c r="Z28" s="5" t="str"/>
-      <c r="AA28" s="5" t="str"/>
-      <c r="AB28" s="5" t="inlineStr">
+      <c r="S28" s="29" t="str"/>
+      <c r="T28" s="29" t="str"/>
+      <c r="U28" s="29" t="str"/>
+      <c r="V28" s="29" t="str"/>
+      <c r="W28" s="29" t="str"/>
+      <c r="X28" s="29" t="str"/>
+      <c r="Y28" s="29" t="str"/>
+      <c r="Z28" s="29" t="str"/>
+      <c r="AA28" s="29" t="str"/>
+      <c r="AB28" s="29" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="inlineStr">
+      <c r="AC28" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD28" s="5" t="str"/>
-      <c r="AE28" s="5" t="str"/>
-      <c r="AF28" s="5" t="str"/>
-      <c r="AG28" s="5" t="inlineStr">
+      <c r="AD28" s="29" t="str"/>
+      <c r="AE28" s="29" t="str"/>
+      <c r="AF28" s="29" t="str"/>
+      <c r="AG28" s="29" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH28" s="5" t="inlineStr">
+      <c r="AH28" s="29" t="inlineStr">
         <is>
           <t>管釣操作系 plug：Vibration、Minnow Twitching 和 Bottom Bump Plug 的抖動、跳底與停頓更清楚，也能切回 spooning。</t>
         </is>
       </c>
-      <c r="AI28" s="5" t="inlineStr">
+      <c r="AI28" s="29" t="inlineStr">
         <is>
           <t>Vibration / Minnow Twitching / Spoon / Bottom Bump Plug</t>
         </is>
       </c>
-      <c r="AJ28" s="5" t="str"/>
-      <c r="AK28" s="5" t="str"/>
-      <c r="AL28" s="5" t="inlineStr">
+      <c r="AJ28" s="29" t="str"/>
+      <c r="AK28" s="29" t="str"/>
+      <c r="AL28" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM28" s="5" t="inlineStr">
+      <c r="AM28" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / bottom-twitch 操作系 plug / spooning 兼用</t>
         </is>
       </c>
-      <c r="AN28" s="5" t="inlineStr">
+      <c r="AN28" s="29" t="inlineStr">
         <is>
           <t>Vibration、Minnow Twitching、Bottom Bump 操作型</t>
         </is>
       </c>
-      <c r="AO28" s="5" t="inlineStr">
+      <c r="AO28" s="29" t="inlineStr">
         <is>
           <t>Fast-ish action 讓 Vibration、Minnow Twitching 和 Bottom Bump 更清楚，遇到穩定魚情可切回 Spoon；不是單純慢巻き型。</t>
         </is>
       </c>
-      <c r="AP28" s="5" t="inlineStr">
+      <c r="AP28" s="29" t="inlineStr">
         <is>
           <t>ファーストよりのアクションでボトムバンプやトゥイッチングなどルアーを操作しやすいモデル。バイブレーションやミノーなどのプラグ全般を得意としていますが、スプーニングにも高次元で対応します。</t>
         </is>
       </c>
-      <c r="AQ28" s="5" t="str"/>
-      <c r="AR28" s="5" t="str"/>
+      <c r="AQ28" s="29" t="str"/>
+      <c r="AR28" s="29" t="str"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>ORD10027</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>24GBELUS-652UL-T</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="29" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="29" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="29" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="29" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" s="29" t="inlineStr">
         <is>
           <t>0.6-7</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M29" s="29" t="inlineStr">
         <is>
           <t>MAX5</t>
         </is>
       </c>
-      <c r="N29" s="5" t="str"/>
-      <c r="O29" s="5" t="str"/>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="N29" s="29" t="str"/>
+      <c r="O29" s="29" t="str"/>
+      <c r="P29" s="29" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="str"/>
-      <c r="R29" s="5" t="inlineStr">
+      <c r="Q29" s="29" t="str"/>
+      <c r="R29" s="29" t="inlineStr">
         <is>
           <t>24,500</t>
         </is>
       </c>
-      <c r="S29" s="5" t="str"/>
-      <c r="T29" s="5" t="str"/>
-      <c r="U29" s="5" t="str"/>
-      <c r="V29" s="5" t="str"/>
-      <c r="W29" s="5" t="str"/>
-      <c r="X29" s="5" t="str"/>
-      <c r="Y29" s="5" t="str"/>
-      <c r="Z29" s="5" t="str"/>
-      <c r="AA29" s="5" t="str"/>
-      <c r="AB29" s="5" t="inlineStr">
+      <c r="S29" s="29" t="str"/>
+      <c r="T29" s="29" t="str"/>
+      <c r="U29" s="29" t="str"/>
+      <c r="V29" s="29" t="str"/>
+      <c r="W29" s="29" t="str"/>
+      <c r="X29" s="29" t="str"/>
+      <c r="Y29" s="29" t="str"/>
+      <c r="Z29" s="29" t="str"/>
+      <c r="AA29" s="29" t="str"/>
+      <c r="AB29" s="29" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="inlineStr">
+      <c r="AC29" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD29" s="5" t="str"/>
-      <c r="AE29" s="5" t="str"/>
-      <c r="AF29" s="5" t="str"/>
-      <c r="AG29" s="5" t="inlineStr">
+      <c r="AD29" s="29" t="str"/>
+      <c r="AE29" s="29" t="str"/>
+      <c r="AF29" s="29" t="str"/>
+      <c r="AG29" s="29" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH29" s="5" t="inlineStr">
+      <c r="AH29" s="29" t="inlineStr">
         <is>
           <t>管釣遠投 / 大型 trout：Long Cast Crankbait、Spoon 和 Minnow 覆蓋沖目魚群，張りのある blank 支撐遠距離補刺。</t>
         </is>
       </c>
-      <c r="AI29" s="5" t="inlineStr">
+      <c r="AI29" s="29" t="inlineStr">
         <is>
           <t>Long Cast Crankbait / Long Cast Spoon / Minnow</t>
         </is>
       </c>
-      <c r="AJ29" s="5" t="str"/>
-      <c r="AK29" s="5" t="str"/>
-      <c r="AL29" s="5" t="inlineStr">
+      <c r="AJ29" s="29" t="str"/>
+      <c r="AK29" s="29" t="str"/>
+      <c r="AL29" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM29" s="5" t="inlineStr">
+      <c r="AM29" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 沖目遠投 / 大型 trout</t>
         </is>
       </c>
-      <c r="AN29" s="5" t="inlineStr">
+      <c r="AN29" s="29" t="inlineStr">
         <is>
           <t>Long Cast Crankbait / Spoon 遠投泛用型</t>
         </is>
       </c>
-      <c r="AO29" s="5" t="inlineStr">
+      <c r="AO29" s="29" t="inlineStr">
         <is>
           <t>較長竿身和系列最強 bat power 讓 Long Cast Crankbait、Spoon、Minnow 能覆蓋沖目魚，對大型 trout 補刺和控魚更穩。</t>
         </is>
       </c>
-      <c r="AP29" s="5" t="inlineStr">
+      <c r="AP29" s="29" t="inlineStr">
         <is>
           <t>長めのレングスで、ロングキャストして沖の魚を狙って獲っていくモデル。全体的に張りのあるブランクスでプラグ全般からスプーニングまで幅広く対応。シリーズ中もっともバットパワーがあるので大型トラウト狙いにもおすすめの1本です。</t>
         </is>
       </c>
-      <c r="AQ29" s="5" t="str"/>
-      <c r="AR29" s="5" t="str"/>
+      <c r="AQ29" s="29" t="str"/>
+      <c r="AR29" s="29" t="str"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>ORD10028</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>25GBELUS-682SUL-T</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="29" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="29" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="29" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="29" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="29" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L30" s="29" t="inlineStr">
         <is>
           <t>0.5-5.0</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M30" s="29" t="inlineStr">
         <is>
           <t>MAX 4</t>
         </is>
       </c>
-      <c r="N30" s="5" t="str"/>
-      <c r="O30" s="5" t="str"/>
-      <c r="P30" s="5" t="inlineStr">
+      <c r="N30" s="29" t="str"/>
+      <c r="O30" s="29" t="str"/>
+      <c r="P30" s="29" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q30" s="5" t="str"/>
-      <c r="R30" s="5" t="inlineStr">
+      <c r="Q30" s="29" t="str"/>
+      <c r="R30" s="29" t="inlineStr">
         <is>
           <t>23,000</t>
         </is>
       </c>
-      <c r="S30" s="5" t="str"/>
-      <c r="T30" s="5" t="str"/>
-      <c r="U30" s="5" t="str"/>
-      <c r="V30" s="5" t="str"/>
-      <c r="W30" s="5" t="str"/>
-      <c r="X30" s="5" t="str"/>
-      <c r="Y30" s="5" t="str"/>
-      <c r="Z30" s="5" t="str"/>
-      <c r="AA30" s="5" t="str"/>
-      <c r="AB30" s="5" t="inlineStr">
+      <c r="S30" s="29" t="str"/>
+      <c r="T30" s="29" t="str"/>
+      <c r="U30" s="29" t="str"/>
+      <c r="V30" s="29" t="str"/>
+      <c r="W30" s="29" t="str"/>
+      <c r="X30" s="29" t="str"/>
+      <c r="Y30" s="29" t="str"/>
+      <c r="Z30" s="29" t="str"/>
+      <c r="AA30" s="29" t="str"/>
+      <c r="AB30" s="29" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC30" s="5" t="inlineStr">
+      <c r="AC30" s="29" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD30" s="5" t="str"/>
-      <c r="AE30" s="5" t="str"/>
-      <c r="AF30" s="5" t="str"/>
-      <c r="AG30" s="5" t="inlineStr">
+      <c r="AD30" s="29" t="str"/>
+      <c r="AE30" s="29" t="str"/>
+      <c r="AF30" s="29" t="str"/>
+      <c r="AG30" s="29" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH30" s="5" t="inlineStr">
+      <c r="AH30" s="29" t="inlineStr">
         <is>
           <t>管釣最長尺遠投：Long Cast Crankbait、Spoon 和 Minnow Twitching 覆蓋大場沖目，回收、操作與控魚距離更清楚。</t>
         </is>
       </c>
-      <c r="AI30" s="5" t="inlineStr">
+      <c r="AI30" s="29" t="inlineStr">
         <is>
           <t>Long Cast Crankbait / Long Cast Spoon / Minnow Twitching</t>
         </is>
       </c>
-      <c r="AJ30" s="5" t="str"/>
-      <c r="AK30" s="5" t="str"/>
-      <c r="AL30" s="5" t="inlineStr">
+      <c r="AJ30" s="29" t="str"/>
+      <c r="AK30" s="29" t="str"/>
+      <c r="AL30" s="29" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM30" s="5" t="inlineStr">
+      <c r="AM30" s="29" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 廣大場地最遠投 / plug-spoon 操作回收</t>
         </is>
       </c>
-      <c r="AN30" s="5" t="inlineStr">
+      <c r="AN30" s="29" t="inlineStr">
         <is>
           <t>最長尺 Long Cast Crank / Spoon / Minnow Twitching 型</t>
         </is>
       </c>
-      <c r="AO30" s="5" t="inlineStr">
+      <c r="AO30" s="29" t="inlineStr">
         <is>
           <t>6'8" 最長尺用來觸及大場未被打擾的沖目魚，Crankbait、Spoon 和 Minnow Twitching 都能處理，遠距離回收和控魚距離更有優勢。</t>
         </is>
       </c>
-      <c r="AP30" s="5" t="inlineStr">
+      <c r="AP30" s="29" t="inlineStr">
         <is>
           <t>プラグ全般からスプーンなど幅広いルアーのリトリーブや操作系の釣りに高次元に対応。シリーズ最長のレングスで、広大なエリアフィールドにおいて今まで手付かずだった沖にいるスレていない魚をロングキャストで狙うことができるモデル。</t>
         </is>
       </c>
-      <c r="AQ30" s="5" t="str"/>
-      <c r="AR30" s="5" t="str"/>
+      <c r="AQ30" s="29" t="str"/>
+      <c r="AR30" s="29" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GearSage-client/pkgGear/data_raw/olympic_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/olympic_rod_import.xlsx
@@ -54,8 +54,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,6 +502,10 @@
   </sheetPr>
   <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -984,8 +1000,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR30"/>
+  <dimension ref="A1:AS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1200,4456 +1220,4606 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>product_technical</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>Extra Spec 1</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Extra Spec 2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>ORD10000</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D2" s="29" t="inlineStr">
+      <c r="D2" s="41" t="inlineStr">
         <is>
           <t>20GVIGC-71H</t>
         </is>
       </c>
-      <c r="E2" s="29" t="inlineStr">
+      <c r="E2" s="41" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="F2" s="41" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="G2" s="29" t="inlineStr">
+      <c r="G2" s="41" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="41" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="J2" s="29" t="inlineStr">
+      <c r="J2" s="41" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="K2" s="29" t="inlineStr">
+      <c r="K2" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L2" s="29" t="str"/>
-      <c r="M2" s="29" t="inlineStr">
+      <c r="L2" s="41" t="str"/>
+      <c r="M2" s="41" t="inlineStr">
         <is>
           <t>14-20</t>
         </is>
       </c>
-      <c r="N2" s="29" t="str"/>
-      <c r="O2" s="29" t="str"/>
-      <c r="P2" s="29" t="inlineStr">
+      <c r="N2" s="41" t="str"/>
+      <c r="O2" s="41" t="str"/>
+      <c r="P2" s="41" t="inlineStr">
         <is>
           <t>Fuji ECS16 reel seat</t>
         </is>
       </c>
-      <c r="Q2" s="29" t="str"/>
-      <c r="R2" s="29" t="inlineStr">
+      <c r="Q2" s="41" t="str"/>
+      <c r="R2" s="41" t="inlineStr">
         <is>
           <t>51,000</t>
         </is>
       </c>
-      <c r="S2" s="29" t="str"/>
-      <c r="T2" s="29" t="str"/>
-      <c r="U2" s="29" t="str"/>
-      <c r="V2" s="29" t="str"/>
-      <c r="W2" s="29" t="str"/>
-      <c r="X2" s="29" t="str"/>
-      <c r="Y2" s="29" t="str"/>
-      <c r="Z2" s="29" t="inlineStr">
+      <c r="S2" s="41" t="str"/>
+      <c r="T2" s="41" t="str"/>
+      <c r="U2" s="41" t="str"/>
+      <c r="V2" s="41" t="str"/>
+      <c r="W2" s="41" t="str"/>
+      <c r="X2" s="41" t="str"/>
+      <c r="Y2" s="41" t="str"/>
+      <c r="Z2" s="41" t="inlineStr">
         <is>
           <t>1/4-1</t>
         </is>
       </c>
-      <c r="AA2" s="29" t="str"/>
-      <c r="AB2" s="29" t="inlineStr">
+      <c r="AA2" s="41" t="str"/>
+      <c r="AB2" s="41" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC2" s="29" t="inlineStr">
+      <c r="AC2" s="41" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD2" s="29" t="str"/>
-      <c r="AE2" s="29" t="inlineStr">
+      <c r="AD2" s="41" t="str"/>
+      <c r="AE2" s="41" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF2" s="29" t="str"/>
-      <c r="AG2" s="29" t="inlineStr">
+      <c r="AF2" s="41" t="str"/>
+      <c r="AG2" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH2" s="29" t="inlineStr">
+      <c r="AH2" s="41" t="inlineStr">
         <is>
           <t>Bass 障礙打撃：Texas、Punch Shot、Wacky 和 Neko 的落點控制與控線更穩，cover 內補刺和拉離障礙更有餘量。</t>
         </is>
       </c>
-      <c r="AI2" s="29" t="inlineStr">
+      <c r="AI2" s="41" t="inlineStr">
         <is>
           <t>Texas Rig / Punch Shot Rig / Wacky Rig / Neko Rig</t>
         </is>
       </c>
-      <c r="AJ2" s="29" t="str"/>
-      <c r="AK2" s="29" t="str"/>
-      <c r="AL2" s="29" t="inlineStr">
+      <c r="AJ2" s="41" t="str"/>
+      <c r="AK2" s="41" t="str"/>
+      <c r="AL2" s="41" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM2" s="29" t="inlineStr">
+      <c r="AM2" s="41" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸邊與船上 cover 打撃 / weed edge</t>
         </is>
       </c>
-      <c r="AN2" s="29" t="inlineStr">
+      <c r="AN2" s="41" t="inlineStr">
         <is>
           <t>Texas 與 Punch Shot 主軸的障礙打撃竿</t>
         </is>
       </c>
-      <c r="AO2" s="29" t="inlineStr">
+      <c r="AO2" s="41" t="inlineStr">
         <is>
           <t>3/16-3/8oz Texas 和 1/4-1oz Punch Shot 落點控制清楚，能在 weed cover 內補刺並把魚拉離障礙；Wacky、Neko 可作慢速誘食補充。</t>
         </is>
       </c>
-      <c r="AP2" s="29" t="inlineStr">
+      <c r="AP2" s="41" t="inlineStr">
         <is>
           <t>打ち物の釣りに特化したモデル。3/16～3/8オンスシンカーのテキサスリグ、1/4～1オンスのパンチショットでウィードを攻略。ロングストレートワームのワッキー、ネコリグにも対応。おかっぱり、ボートどちらでもメインに扱える打ち物ロッドです。</t>
         </is>
       </c>
-      <c r="AQ2" s="29" t="str"/>
-      <c r="AR2" s="29" t="inlineStr">
+      <c r="AQ2" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / G-MAPS製法 / クワトログラファイトクロスXX / チタンフレームトルザイトリングガイド / KWガイド / シングルフットガイド / ECS16リールシート</t>
+        </is>
+      </c>
+      <c r="AR2" s="41" t="str"/>
+      <c r="AS2" s="41" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>ORD10001</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>20GVIGC-75M</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H3" s="29" t="inlineStr">
+      <c r="H3" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="41" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="J3" s="29" t="inlineStr">
+      <c r="J3" s="41" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="41" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="L3" s="29" t="str"/>
-      <c r="M3" s="29" t="inlineStr">
+      <c r="L3" s="41" t="str"/>
+      <c r="M3" s="41" t="inlineStr">
         <is>
           <t>10-16</t>
         </is>
       </c>
-      <c r="N3" s="29" t="str"/>
-      <c r="O3" s="29" t="str"/>
-      <c r="P3" s="29" t="inlineStr">
+      <c r="N3" s="41" t="str"/>
+      <c r="O3" s="41" t="str"/>
+      <c r="P3" s="41" t="inlineStr">
         <is>
           <t>Fuji ECS16 reel seat</t>
         </is>
       </c>
-      <c r="Q3" s="29" t="str"/>
-      <c r="R3" s="29" t="inlineStr">
+      <c r="Q3" s="41" t="str"/>
+      <c r="R3" s="41" t="inlineStr">
         <is>
           <t>51,500</t>
         </is>
       </c>
-      <c r="S3" s="29" t="str"/>
-      <c r="T3" s="29" t="str"/>
-      <c r="U3" s="29" t="str"/>
-      <c r="V3" s="29" t="str"/>
-      <c r="W3" s="29" t="str"/>
-      <c r="X3" s="29" t="str"/>
-      <c r="Y3" s="29" t="str"/>
-      <c r="Z3" s="29" t="inlineStr">
+      <c r="S3" s="41" t="str"/>
+      <c r="T3" s="41" t="str"/>
+      <c r="U3" s="41" t="str"/>
+      <c r="V3" s="41" t="str"/>
+      <c r="W3" s="41" t="str"/>
+      <c r="X3" s="41" t="str"/>
+      <c r="Y3" s="41" t="str"/>
+      <c r="Z3" s="41" t="inlineStr">
         <is>
           <t>1/4-1</t>
         </is>
       </c>
-      <c r="AA3" s="29" t="str"/>
-      <c r="AB3" s="29" t="inlineStr">
+      <c r="AA3" s="41" t="str"/>
+      <c r="AB3" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC3" s="29" t="inlineStr">
+      <c r="AC3" s="41" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD3" s="29" t="str"/>
-      <c r="AE3" s="29" t="inlineStr">
+      <c r="AD3" s="41" t="str"/>
+      <c r="AE3" s="41" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF3" s="29" t="str"/>
-      <c r="AG3" s="29" t="inlineStr">
+      <c r="AF3" s="41" t="str"/>
+      <c r="AG3" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH3" s="29" t="inlineStr">
+      <c r="AH3" s="41" t="inlineStr">
         <is>
           <t>Bass 巻物 / 操作硬餌：Vibration 和 Jerkbait 是主軸，Regular-Fast 調性保留操作性；Scone Rig、Metal Vibration 和 Metal Jig 作為冬季或吸い込み bite 補充。</t>
         </is>
       </c>
-      <c r="AI3" s="29" t="inlineStr">
+      <c r="AI3" s="41" t="inlineStr">
         <is>
           <t>Vibration / Jerkbait / Scone Rig / Metal Vibration / Metal Jig</t>
         </is>
       </c>
-      <c r="AJ3" s="29" t="str"/>
-      <c r="AK3" s="29" t="str"/>
-      <c r="AL3" s="29" t="inlineStr">
+      <c r="AJ3" s="41" t="str"/>
+      <c r="AK3" s="41" t="str"/>
+      <c r="AL3" s="41" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM3" s="29" t="inlineStr">
+      <c r="AM3" s="41" t="inlineStr">
         <is>
           <t>淡水 Bass / 開放水域與岸投硬餌搜索 / 冬季金屬餌</t>
         </is>
       </c>
-      <c r="AN3" s="29" t="inlineStr">
+      <c r="AN3" s="41" t="inlineStr">
         <is>
           <t>Vibration、Jerkbait 主軸的巻物與操作硬餌竿</t>
         </is>
       </c>
-      <c r="AO3" s="29" t="inlineStr">
+      <c r="AO3" s="41" t="inlineStr">
         <is>
           <t>1/2-5/8oz Vibration、Jerkbait 連續搜索時保留操作性，Scone Rig 可承接吸い込み bite；冬季 Metal Vibration / Metal Jig 也能做反應搜索。</t>
         </is>
       </c>
-      <c r="AP3" s="29" t="inlineStr">
+      <c r="AP3" s="41" t="inlineStr">
         <is>
           <t>1/4～1オンス程度のハードベイトでの巻きの釣りを想定し設計。若干ファーストよりなアクションに仕上げることで操作性も増し、様々なリグにも対応する。メインは1/2～5/8オンス程度のバイブレーションやジャークベイトであるがスコーンリグなどの吸い込みバイトにも対応する。冬季のメタルジグ、メタルバイブなどにもおすすめです。</t>
         </is>
       </c>
-      <c r="AQ3" s="29" t="str"/>
-      <c r="AR3" s="29" t="inlineStr">
+      <c r="AQ3" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / G-MAPS製法 / クワトログラファイトクロスXX / チタンフレームトルザイトリングガイド / LRVガイド / KWガイド / シングルフットガイド / グリップ脱着式 / ECS16リールシート</t>
+        </is>
+      </c>
+      <c r="AR3" s="41" t="str"/>
+      <c r="AS3" s="41" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>ORD10002</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>20GVIGC-76MH</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>195</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="L4" s="29" t="str"/>
-      <c r="M4" s="29" t="inlineStr">
+      <c r="L4" s="41" t="str"/>
+      <c r="M4" s="41" t="inlineStr">
         <is>
           <t>12-20</t>
         </is>
       </c>
-      <c r="N4" s="29" t="str"/>
-      <c r="O4" s="29" t="str"/>
-      <c r="P4" s="29" t="inlineStr">
+      <c r="N4" s="41" t="str"/>
+      <c r="O4" s="41" t="str"/>
+      <c r="P4" s="41" t="inlineStr">
         <is>
           <t>Fuji ECS17 reel seat</t>
         </is>
       </c>
-      <c r="Q4" s="29" t="str"/>
-      <c r="R4" s="29" t="inlineStr">
+      <c r="Q4" s="41" t="str"/>
+      <c r="R4" s="41" t="inlineStr">
         <is>
           <t>52,000</t>
         </is>
       </c>
-      <c r="S4" s="29" t="str"/>
-      <c r="T4" s="29" t="str"/>
-      <c r="U4" s="29" t="str"/>
-      <c r="V4" s="29" t="str"/>
-      <c r="W4" s="29" t="str"/>
-      <c r="X4" s="29" t="str"/>
-      <c r="Y4" s="29" t="str"/>
-      <c r="Z4" s="29" t="inlineStr">
+      <c r="S4" s="41" t="str"/>
+      <c r="T4" s="41" t="str"/>
+      <c r="U4" s="41" t="str"/>
+      <c r="V4" s="41" t="str"/>
+      <c r="W4" s="41" t="str"/>
+      <c r="X4" s="41" t="str"/>
+      <c r="Y4" s="41" t="str"/>
+      <c r="Z4" s="41" t="inlineStr">
         <is>
           <t>3/8-2</t>
         </is>
       </c>
-      <c r="AA4" s="29" t="str"/>
-      <c r="AB4" s="29" t="inlineStr">
+      <c r="AA4" s="41" t="str"/>
+      <c r="AB4" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC4" s="29" t="inlineStr">
+      <c r="AC4" s="41" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD4" s="29" t="str"/>
-      <c r="AE4" s="29" t="inlineStr">
+      <c r="AD4" s="41" t="str"/>
+      <c r="AE4" s="41" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF4" s="29" t="str"/>
-      <c r="AG4" s="29" t="inlineStr">
+      <c r="AF4" s="41" t="str"/>
+      <c r="AG4" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH4" s="29" t="inlineStr">
+      <c r="AH4" s="41" t="inlineStr">
         <is>
           <t>Bass 中重型巻物：Spinnerbait Slow Roll 放首位，竿身要讀出 blade 振動並承接巻き負荷；Chatterbait 和 Swim Jig 作為同級 moving bait 延伸。</t>
         </is>
       </c>
-      <c r="AI4" s="29" t="inlineStr">
+      <c r="AI4" s="41" t="inlineStr">
         <is>
           <t>Spinnerbait Slow Roll / Heavy Spinnerbait / Chatterbait / Swim Jig</t>
         </is>
       </c>
-      <c r="AJ4" s="29" t="str"/>
-      <c r="AK4" s="29" t="str"/>
-      <c r="AL4" s="29" t="inlineStr">
+      <c r="AJ4" s="41" t="str"/>
+      <c r="AK4" s="41" t="str"/>
+      <c r="AL4" s="41" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM4" s="29" t="inlineStr">
+      <c r="AM4" s="41" t="inlineStr">
         <is>
           <t>淡水 Bass / 中重型巻物搜索 / lake grass edge</t>
         </is>
       </c>
-      <c r="AN4" s="29" t="inlineStr">
+      <c r="AN4" s="41" t="inlineStr">
         <is>
           <t>Spinnerbait Slow Roll 與中重型 moving bait 專用</t>
         </is>
       </c>
-      <c r="AO4" s="29" t="inlineStr">
+      <c r="AO4" s="41" t="inlineStr">
         <is>
           <t>1/2-1.5oz 巻物負荷下竿身彎曲過渡穩，能讀出 blade 振動；太軸單鉤補刺速度和力量足，適合 slow roll、Chatterbait、Swim Jig 搜索。</t>
         </is>
       </c>
-      <c r="AP4" s="29" t="inlineStr">
+      <c r="AP4" s="41" t="inlineStr">
         <is>
           <t>1/2～1・1/2オンスの巻物系ルアーを扱いやすく設計。スピナーベイトの超スローロール時でもブレードの振動を伝える感度。巻き負荷に対してカーブが移行するしなやかさを持ちながら太軸のシングルフックを瞬時に貫通させるスピードとパワーを両立させた。</t>
         </is>
       </c>
-      <c r="AQ4" s="29" t="str"/>
-      <c r="AR4" s="29" t="inlineStr">
+      <c r="AQ4" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / G-MAPS製法 / クワトログラファイトクロスXX / チタンフレームトルザイトリングガイド / LRVガイド / KWガイド / シングルフットガイド / グリップ脱着式 / ECS17リールシート</t>
+        </is>
+      </c>
+      <c r="AR4" s="41" t="str"/>
+      <c r="AS4" s="41" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>ORD10003</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>20GVIGC-77XH</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>XH</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>2.31</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="J5" s="29" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="K5" s="29" t="inlineStr">
+      <c r="K5" s="41" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="L5" s="29" t="str"/>
-      <c r="M5" s="29" t="inlineStr">
+      <c r="L5" s="41" t="str"/>
+      <c r="M5" s="41" t="inlineStr">
         <is>
           <t>16-25</t>
         </is>
       </c>
-      <c r="N5" s="29" t="str"/>
-      <c r="O5" s="29" t="str"/>
-      <c r="P5" s="29" t="inlineStr">
+      <c r="N5" s="41" t="str"/>
+      <c r="O5" s="41" t="str"/>
+      <c r="P5" s="41" t="inlineStr">
         <is>
           <t>Fuji ECS17 reel seat</t>
         </is>
       </c>
-      <c r="Q5" s="29" t="str"/>
-      <c r="R5" s="29" t="inlineStr">
+      <c r="Q5" s="41" t="str"/>
+      <c r="R5" s="41" t="inlineStr">
         <is>
           <t>52,500</t>
         </is>
       </c>
-      <c r="S5" s="29" t="str"/>
-      <c r="T5" s="29" t="str"/>
-      <c r="U5" s="29" t="str"/>
-      <c r="V5" s="29" t="str"/>
-      <c r="W5" s="29" t="str"/>
-      <c r="X5" s="29" t="str"/>
-      <c r="Y5" s="29" t="str"/>
-      <c r="Z5" s="29" t="inlineStr">
+      <c r="S5" s="41" t="str"/>
+      <c r="T5" s="41" t="str"/>
+      <c r="U5" s="41" t="str"/>
+      <c r="V5" s="41" t="str"/>
+      <c r="W5" s="41" t="str"/>
+      <c r="X5" s="41" t="str"/>
+      <c r="Y5" s="41" t="str"/>
+      <c r="Z5" s="41" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="AA5" s="29" t="str"/>
-      <c r="AB5" s="29" t="inlineStr">
+      <c r="AA5" s="41" t="str"/>
+      <c r="AB5" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC5" s="29" t="inlineStr">
+      <c r="AC5" s="41" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD5" s="29" t="str"/>
-      <c r="AE5" s="29" t="inlineStr">
+      <c r="AD5" s="41" t="str"/>
+      <c r="AE5" s="41" t="inlineStr">
         <is>
           <t>GRIP TYPE C</t>
         </is>
       </c>
-      <c r="AF5" s="29" t="str"/>
-      <c r="AG5" s="29" t="inlineStr">
+      <c r="AF5" s="41" t="str"/>
+      <c r="AG5" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH5" s="29" t="inlineStr">
+      <c r="AH5" s="41" t="inlineStr">
         <is>
           <t>Bass 大型餌：Big Bait 和 Crawler Bait 是官方主軸，XH blank 用於穩定高負荷拋投、減少飛行姿勢偏移，Swimbait 作為同負荷泳姿餌延伸。</t>
         </is>
       </c>
-      <c r="AI5" s="29" t="inlineStr">
+      <c r="AI5" s="41" t="inlineStr">
         <is>
           <t>Big Bait / Crawler Bait / Swimbait</t>
         </is>
       </c>
-      <c r="AJ5" s="29" t="str"/>
-      <c r="AK5" s="29" t="str"/>
-      <c r="AL5" s="29" t="inlineStr">
+      <c r="AJ5" s="41" t="str"/>
+      <c r="AK5" s="41" t="str"/>
+      <c r="AL5" s="41" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM5" s="29" t="inlineStr">
+      <c r="AM5" s="41" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型餌拋投 / 開放水域與精準打點</t>
         </is>
       </c>
-      <c r="AN5" s="29" t="inlineStr">
+      <c r="AN5" s="41" t="inlineStr">
         <is>
           <t>Big Bait、Crawler Bait、Swimbait 高負荷竿</t>
         </is>
       </c>
-      <c r="AO5" s="29" t="inlineStr">
+      <c r="AO5" s="41" t="inlineStr">
         <is>
           <t>XH blank 承接 Big Bait 和 Crawler Bait 的拋投負荷，4 軸組布和 T1100G 幫助減少 cast wobble；適合重餌精準落點和穩定泳姿回收。</t>
         </is>
       </c>
-      <c r="AP5" s="29" t="inlineStr">
+      <c r="AP5" s="41" t="inlineStr">
         <is>
           <t>ビッグベイト・クローラーベイトなどのルアーを快適に扱うよう設計。キャスト・操作時の負荷に対してカーブポイントが移行するテーパー設計で各ウェイトに対して快適に扱える。全身に４軸組布とトレカ®T1100Gを採用することによりキャストのブレを軽減し、飛行姿勢を安定させピンポイントキャストを容易にした。</t>
         </is>
       </c>
-      <c r="AQ5" s="29" t="str"/>
-      <c r="AR5" s="29" t="inlineStr">
+      <c r="AQ5" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / G-MAPS製法 / クワトログラファイトクロスXX / スーパークワトログラファイトクロス / ステンレスフレームSiC-Sリング / オールダブルフットKガイド / グリップ脱着式 / ECS17リールシート</t>
+        </is>
+      </c>
+      <c r="AR5" s="41" t="str"/>
+      <c r="AS5" s="41" t="inlineStr">
         <is>
           <t>■GRIP TYPE C</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>ORD10004</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>20GVIGS-610ML</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="41" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="H6" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="41" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr">
+      <c r="J6" s="41" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="K6" s="41" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="L6" s="29" t="str"/>
-      <c r="M6" s="29" t="inlineStr">
+      <c r="L6" s="41" t="str"/>
+      <c r="M6" s="41" t="inlineStr">
         <is>
           <t>4-10</t>
         </is>
       </c>
-      <c r="N6" s="29" t="inlineStr">
+      <c r="N6" s="41" t="inlineStr">
         <is>
           <t>0.5-1.2</t>
         </is>
       </c>
-      <c r="O6" s="29" t="str"/>
-      <c r="P6" s="29" t="inlineStr">
+      <c r="O6" s="41" t="str"/>
+      <c r="P6" s="41" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="str"/>
-      <c r="R6" s="29" t="inlineStr">
+      <c r="Q6" s="41" t="str"/>
+      <c r="R6" s="41" t="inlineStr">
         <is>
           <t>49,000</t>
         </is>
       </c>
-      <c r="S6" s="29" t="str"/>
-      <c r="T6" s="29" t="str"/>
-      <c r="U6" s="29" t="str"/>
-      <c r="V6" s="29" t="str"/>
-      <c r="W6" s="29" t="str"/>
-      <c r="X6" s="29" t="str"/>
-      <c r="Y6" s="29" t="str"/>
-      <c r="Z6" s="29" t="inlineStr">
+      <c r="S6" s="41" t="str"/>
+      <c r="T6" s="41" t="str"/>
+      <c r="U6" s="41" t="str"/>
+      <c r="V6" s="41" t="str"/>
+      <c r="W6" s="41" t="str"/>
+      <c r="X6" s="41" t="str"/>
+      <c r="Y6" s="41" t="str"/>
+      <c r="Z6" s="41" t="inlineStr">
         <is>
           <t>1/16-3/8</t>
         </is>
       </c>
-      <c r="AA6" s="29" t="str"/>
-      <c r="AB6" s="29" t="inlineStr">
+      <c r="AA6" s="41" t="str"/>
+      <c r="AB6" s="41" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC6" s="29" t="inlineStr">
+      <c r="AC6" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD6" s="29" t="str"/>
-      <c r="AE6" s="29" t="inlineStr">
+      <c r="AD6" s="41" t="str"/>
+      <c r="AE6" s="41" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF6" s="29" t="str"/>
-      <c r="AG6" s="29" t="inlineStr">
+      <c r="AF6" s="41" t="str"/>
+      <c r="AG6" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH6" s="29" t="inlineStr">
+      <c r="AH6" s="41" t="inlineStr">
         <is>
           <t>Bass 直柄 finesse / cover 兼用：No Sinker、Neko 和 Bug Lure 需要細線控線與竿尖讀感，小型 plug 可搜索；ML power 保留從 cover 拉魚的餘量。</t>
         </is>
       </c>
-      <c r="AI6" s="29" t="inlineStr">
+      <c r="AI6" s="41" t="inlineStr">
         <is>
           <t>No Sinker / Neko Rig / Bug Lure / Small Topwater Plug / Small Crankbait</t>
         </is>
       </c>
-      <c r="AJ6" s="29" t="str"/>
-      <c r="AK6" s="29" t="str"/>
-      <c r="AL6" s="29" t="inlineStr">
+      <c r="AJ6" s="41" t="str"/>
+      <c r="AK6" s="41" t="str"/>
+      <c r="AL6" s="41" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM6" s="29" t="inlineStr">
+      <c r="AM6" s="41" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸邊 light cover / 直柄精細與小型 plug</t>
         </is>
       </c>
-      <c r="AN6" s="29" t="inlineStr">
+      <c r="AN6" s="41" t="inlineStr">
         <is>
           <t>No Sinker、Neko、虫系兼小型 plug 的 power finesse spin</t>
         </is>
       </c>
-      <c r="AO6" s="29" t="inlineStr">
+      <c r="AO6" s="41" t="inlineStr">
         <is>
           <t>細線下能操作 No Sinker、Neko 和虫系，也能切到小型 plug 搜索；ML power 留有 cover 內控魚餘量，不只是純開放水域精細竿。</t>
         </is>
       </c>
-      <c r="AP6" s="29" t="inlineStr">
+      <c r="AP6" s="41" t="inlineStr">
         <is>
           <t>パワーと繊細さを持たせたバーサタイルスピン。ライトリグを意のままに操る繊細さとカバーからの魚を獲るパワーを持たせた。ノーシンカー、ネコリグ、虫系、プラグなど様々な釣りに適合しつつ、ランカー相手でも安心して対応できるロッドです。</t>
         </is>
       </c>
-      <c r="AQ6" s="29" t="str"/>
-      <c r="AR6" s="29" t="inlineStr">
+      <c r="AQ6" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / G-MAPS製法 / クワトログラファイトクロスXX / チタンフレームトルザイトリングガイド / VSSリールシート</t>
+        </is>
+      </c>
+      <c r="AR6" s="41" t="str"/>
+      <c r="AS6" s="41" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>ORD10005</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>GVIGS-6102ML</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="H7" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="41" t="inlineStr">
         <is>
           <t>106.8</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr">
+      <c r="J7" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
+      <c r="K7" s="41" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="L7" s="29" t="str"/>
-      <c r="M7" s="29" t="inlineStr">
+      <c r="L7" s="41" t="str"/>
+      <c r="M7" s="41" t="inlineStr">
         <is>
           <t>4-10</t>
         </is>
       </c>
-      <c r="N7" s="29" t="inlineStr">
+      <c r="N7" s="41" t="inlineStr">
         <is>
           <t>0.5-1.2</t>
         </is>
       </c>
-      <c r="O7" s="29" t="str"/>
-      <c r="P7" s="29" t="inlineStr">
+      <c r="O7" s="41" t="str"/>
+      <c r="P7" s="41" t="inlineStr">
         <is>
           <t>Olympic OP-02 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q7" s="29" t="str"/>
-      <c r="R7" s="29" t="inlineStr">
+      <c r="Q7" s="41" t="str"/>
+      <c r="R7" s="41" t="inlineStr">
         <is>
           <t>51,000</t>
         </is>
       </c>
-      <c r="S7" s="29" t="str"/>
-      <c r="T7" s="29" t="str"/>
-      <c r="U7" s="29" t="str"/>
-      <c r="V7" s="29" t="str"/>
-      <c r="W7" s="29" t="str"/>
-      <c r="X7" s="29" t="str"/>
-      <c r="Y7" s="29" t="str"/>
-      <c r="Z7" s="29" t="inlineStr">
+      <c r="S7" s="41" t="str"/>
+      <c r="T7" s="41" t="str"/>
+      <c r="U7" s="41" t="str"/>
+      <c r="V7" s="41" t="str"/>
+      <c r="W7" s="41" t="str"/>
+      <c r="X7" s="41" t="str"/>
+      <c r="Y7" s="41" t="str"/>
+      <c r="Z7" s="41" t="inlineStr">
         <is>
           <t>1/16-3/8</t>
         </is>
       </c>
-      <c r="AA7" s="29" t="str"/>
-      <c r="AB7" s="29" t="inlineStr">
+      <c r="AA7" s="41" t="str"/>
+      <c r="AB7" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC7" s="29" t="inlineStr">
+      <c r="AC7" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD7" s="29" t="str"/>
-      <c r="AE7" s="29" t="inlineStr">
+      <c r="AD7" s="41" t="str"/>
+      <c r="AE7" s="41" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF7" s="29" t="str"/>
-      <c r="AG7" s="29" t="inlineStr">
+      <c r="AF7" s="41" t="str"/>
+      <c r="AG7" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH7" s="29" t="inlineStr">
+      <c r="AH7" s="41" t="inlineStr">
         <is>
           <t>Bass 岸釣 light rig：中心切 2 piece 和 Regular-Fast 設定重點是攜行、拋投、誘い到 landing 的連貫性；Neko、No Sinker、Down Shot 以穩定操作為主。</t>
         </is>
       </c>
-      <c r="AI7" s="29" t="inlineStr">
+      <c r="AI7" s="41" t="inlineStr">
         <is>
           <t>Neko Rig / No Sinker / Down Shot / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ7" s="29" t="str"/>
-      <c r="AK7" s="29" t="str"/>
-      <c r="AL7" s="29" t="inlineStr">
+      <c r="AJ7" s="41" t="str"/>
+      <c r="AK7" s="41" t="str"/>
+      <c r="AL7" s="41" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM7" s="29" t="inlineStr">
+      <c r="AM7" s="41" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸釣移動作戰 / light rig 全般</t>
         </is>
       </c>
-      <c r="AN7" s="29" t="inlineStr">
+      <c r="AN7" s="41" t="inlineStr">
         <is>
           <t>攜行取向的 light rig 泛用兩節直柄</t>
         </is>
       </c>
-      <c r="AO7" s="29" t="inlineStr">
+      <c r="AO7" s="41" t="inlineStr">
         <is>
           <t>中心切 2 piece 方便岸釣移動，Regular-Fast 設定讓 Neko、No Sinker、Down Shot 的拋投、誘い、landing 動作連貫；口徑保守，不擴寫到重 cover。</t>
         </is>
       </c>
-      <c r="AP7" s="29" t="inlineStr">
+      <c r="AP7" s="41" t="inlineStr">
         <is>
           <t>携帯性を優先したセンターカット2ピースモデル。ライトリグ全般に広域対応可能なレギュラーファストアクション。足場の安定しないおかっぱりでは、このレングスとアクション設定が効果的に働き、キャスト・誘い・ランディングまでの一連の動きをスムースに行えるロッドです。</t>
         </is>
       </c>
-      <c r="AQ7" s="29" t="str"/>
-      <c r="AR7" s="29" t="inlineStr">
+      <c r="AQ7" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / G-MAPS製法 / クワトログラファイトクロスXX / チタンフレームトルザイトリングガイド / スピゴットフェルール（印籠継） / オリジナルカーボンリールシート OP-02</t>
+        </is>
+      </c>
+      <c r="AR7" s="41" t="str"/>
+      <c r="AS7" s="41" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>ORD10006</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>OR1000</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>20GVIGS-742M</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="H8" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="41" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr">
+      <c r="J8" s="41" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="K8" s="29" t="inlineStr">
+      <c r="K8" s="41" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="L8" s="29" t="str"/>
-      <c r="M8" s="29" t="inlineStr">
+      <c r="L8" s="41" t="str"/>
+      <c r="M8" s="41" t="inlineStr">
         <is>
           <t>6-10</t>
         </is>
       </c>
-      <c r="N8" s="29" t="inlineStr">
+      <c r="N8" s="41" t="inlineStr">
         <is>
           <t>0.5-1.2</t>
         </is>
       </c>
-      <c r="O8" s="29" t="str"/>
-      <c r="P8" s="29" t="inlineStr">
+      <c r="O8" s="41" t="str"/>
+      <c r="P8" s="41" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q8" s="29" t="str"/>
-      <c r="R8" s="29" t="inlineStr">
+      <c r="Q8" s="41" t="str"/>
+      <c r="R8" s="41" t="inlineStr">
         <is>
           <t>51,000</t>
         </is>
       </c>
-      <c r="S8" s="29" t="str"/>
-      <c r="T8" s="29" t="str"/>
-      <c r="U8" s="29" t="str"/>
-      <c r="V8" s="29" t="str"/>
-      <c r="W8" s="29" t="str"/>
-      <c r="X8" s="29" t="str"/>
-      <c r="Y8" s="29" t="str"/>
-      <c r="Z8" s="29" t="inlineStr">
+      <c r="S8" s="41" t="str"/>
+      <c r="T8" s="41" t="str"/>
+      <c r="U8" s="41" t="str"/>
+      <c r="V8" s="41" t="str"/>
+      <c r="W8" s="41" t="str"/>
+      <c r="X8" s="41" t="str"/>
+      <c r="Y8" s="41" t="str"/>
+      <c r="Z8" s="41" t="inlineStr">
         <is>
           <t>3/16-3/4</t>
         </is>
       </c>
-      <c r="AA8" s="29" t="str"/>
-      <c r="AB8" s="29" t="inlineStr">
+      <c r="AA8" s="41" t="str"/>
+      <c r="AB8" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC8" s="29" t="inlineStr">
+      <c r="AC8" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD8" s="29" t="str"/>
-      <c r="AE8" s="29" t="inlineStr">
+      <c r="AD8" s="41" t="str"/>
+      <c r="AE8" s="41" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF8" s="29" t="str"/>
-      <c r="AG8" s="29" t="inlineStr">
+      <c r="AF8" s="41" t="str"/>
+      <c r="AG8" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH8" s="29" t="inlineStr">
+      <c r="AH8" s="41" t="inlineStr">
         <is>
           <t>Bass PE 遠投 finesse：Long Cast Neko、PE Down Shot 和 No Sinker 是主軸，長距離下要維持細微違和感讀取；Small Crankbait、Topwater 是 plug 操作補充。</t>
         </is>
       </c>
-      <c r="AI8" s="29" t="inlineStr">
+      <c r="AI8" s="41" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / PE Down Shot / No Sinker / Small Crankbait / Topwater Plug</t>
         </is>
       </c>
-      <c r="AJ8" s="29" t="str"/>
-      <c r="AK8" s="29" t="str"/>
-      <c r="AL8" s="29" t="inlineStr">
+      <c r="AJ8" s="41" t="str"/>
+      <c r="AK8" s="41" t="str"/>
+      <c r="AL8" s="41" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM8" s="29" t="inlineStr">
+      <c r="AM8" s="41" t="inlineStr">
         <is>
           <t>淡水 Bass / PE 遠投 / 開放水域 light rig 與 plug</t>
         </is>
       </c>
-      <c r="AN8" s="29" t="inlineStr">
+      <c r="AN8" s="41" t="inlineStr">
         <is>
           <t>PE light rig 遠投與 plug 操作兼用直柄</t>
         </is>
       </c>
-      <c r="AO8" s="29" t="inlineStr">
+      <c r="AO8" s="41" t="inlineStr">
         <is>
           <t>7'4" 長度和 M power 支撐 Long Cast Neko、PE Down Shot 的遠距控線，遠端細微違和感更容易讀取；Small Crankbait、Topwater 可做遠投搜索補充。</t>
         </is>
       </c>
-      <c r="AP8" s="29" t="inlineStr">
+      <c r="AP8" s="41" t="inlineStr">
         <is>
           <t>PEラインを使用したライトリグの遠投に特化したモデル。しなやかでありつつ、張りのあるブランクスは遠距離での繊細な操作や僅かな違和感を逃さない感度につながる。ライトリグだけではなくプラグの操作にも対応した遠投バーサタイルモデルです。</t>
         </is>
       </c>
-      <c r="AQ8" s="29" t="str"/>
-      <c r="AR8" s="29" t="inlineStr">
+      <c r="AQ8" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / G-MAPS製法 / クワトログラファイトクロスXX / チタンフレームトルザイトリングガイド / VSSリールシート / スピゴットフェルール（印籠継）</t>
+        </is>
+      </c>
+      <c r="AR8" s="41" t="str"/>
+      <c r="AS8" s="41" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>ORD10007</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>21GVELUC-65ML</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="40" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="40" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="K9" s="40" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="L9" s="28" t="str"/>
-      <c r="M9" s="28" t="inlineStr">
+      <c r="L9" s="40" t="str"/>
+      <c r="M9" s="40" t="inlineStr">
         <is>
           <t>MAX14</t>
         </is>
       </c>
-      <c r="N9" s="28" t="str"/>
-      <c r="O9" s="28" t="str"/>
-      <c r="P9" s="28" t="inlineStr">
+      <c r="N9" s="40" t="str"/>
+      <c r="O9" s="40" t="str"/>
+      <c r="P9" s="40" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q9" s="28" t="str"/>
-      <c r="R9" s="28" t="inlineStr">
+      <c r="Q9" s="40" t="str"/>
+      <c r="R9" s="40" t="inlineStr">
         <is>
           <t>23,500</t>
         </is>
       </c>
-      <c r="S9" s="28" t="str"/>
-      <c r="T9" s="28" t="str"/>
-      <c r="U9" s="28" t="str"/>
-      <c r="V9" s="28" t="str"/>
-      <c r="W9" s="28" t="str"/>
-      <c r="X9" s="28" t="str"/>
-      <c r="Y9" s="28" t="str"/>
-      <c r="Z9" s="28" t="inlineStr">
+      <c r="S9" s="40" t="str"/>
+      <c r="T9" s="40" t="str"/>
+      <c r="U9" s="40" t="str"/>
+      <c r="V9" s="40" t="str"/>
+      <c r="W9" s="40" t="str"/>
+      <c r="X9" s="40" t="str"/>
+      <c r="Y9" s="40" t="str"/>
+      <c r="Z9" s="40" t="inlineStr">
         <is>
           <t>MAX3/4</t>
         </is>
       </c>
-      <c r="AA9" s="28" t="str"/>
-      <c r="AB9" s="28" t="inlineStr">
+      <c r="AA9" s="40" t="str"/>
+      <c r="AB9" s="40" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC9" s="28" t="inlineStr">
+      <c r="AC9" s="40" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD9" s="28" t="str"/>
-      <c r="AE9" s="28" t="inlineStr">
+      <c r="AD9" s="40" t="str"/>
+      <c r="AE9" s="40" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF9" s="28" t="str"/>
-      <c r="AG9" s="28" t="inlineStr">
+      <c r="AF9" s="40" t="str"/>
+      <c r="AG9" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH9" s="28" t="inlineStr">
+      <c r="AH9" s="40" t="inlineStr">
         <is>
           <t>Bass 小中型硬餌 / cover finesse：Topwater、Shallow Crankbait 負責搜索，Cover Neko 和 Small Rubber Jig 負責 cover 內精細打點。</t>
         </is>
       </c>
-      <c r="AI9" s="28" t="inlineStr">
+      <c r="AI9" s="40" t="inlineStr">
         <is>
           <t>Topwater Plug / Shallow Crankbait / Cover Neko / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ9" s="28" t="str"/>
-      <c r="AK9" s="28" t="str"/>
-      <c r="AL9" s="28" t="inlineStr">
+      <c r="AJ9" s="40" t="str"/>
+      <c r="AK9" s="40" t="str"/>
+      <c r="AL9" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM9" s="28" t="inlineStr">
+      <c r="AM9" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / shallow cover edge / 小中型硬餌與 cover finesse</t>
         </is>
       </c>
-      <c r="AN9" s="28" t="inlineStr">
+      <c r="AN9" s="40" t="inlineStr">
         <is>
           <t>小中型 Topwater / Shallow Crank 加 cover bait finesse</t>
         </is>
       </c>
-      <c r="AO9" s="28" t="inlineStr">
+      <c r="AO9" s="40" t="inlineStr">
         <is>
           <t>Topwater Plug、Shallow Crankbait 做近中距離搜索，Cover Neko 和 Small Rubber Jig 負責輕 cover 內精細打點；ML power 讓拋投準度和彎曲承接更友好。</t>
         </is>
       </c>
-      <c r="AP9" s="28" t="inlineStr">
+      <c r="AP9" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 トップウォータープラグやシャロークランクベイトなどの小型～中型ハードベイトをメインにカバーネコ、スモラバなどを使用したカバーベイトフィネスにも対応できるモデル。スムースなベントカーブが爽快なキャストフィールと高いキャストアキュラシーを可能にします。</t>
         </is>
       </c>
-      <c r="AQ9" s="28" t="inlineStr">
+      <c r="AQ9" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / ECSリールシート</t>
+        </is>
+      </c>
+      <c r="AR9" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR9" s="28" t="inlineStr">
+      <c r="AS9" s="40" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>ORD10008</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="40" t="inlineStr">
         <is>
           <t>21GVELUC-69MH</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="40" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H10" s="28" t="inlineStr">
+      <c r="H10" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="40" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="40" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="K10" s="28" t="inlineStr">
+      <c r="K10" s="40" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="L10" s="28" t="str"/>
-      <c r="M10" s="28" t="inlineStr">
+      <c r="L10" s="40" t="str"/>
+      <c r="M10" s="40" t="inlineStr">
         <is>
           <t>MAX20</t>
         </is>
       </c>
-      <c r="N10" s="28" t="str"/>
-      <c r="O10" s="28" t="str"/>
-      <c r="P10" s="28" t="inlineStr">
+      <c r="N10" s="40" t="str"/>
+      <c r="O10" s="40" t="str"/>
+      <c r="P10" s="40" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q10" s="28" t="str"/>
-      <c r="R10" s="28" t="inlineStr">
+      <c r="Q10" s="40" t="str"/>
+      <c r="R10" s="40" t="inlineStr">
         <is>
           <t>24,000</t>
         </is>
       </c>
-      <c r="S10" s="28" t="str"/>
-      <c r="T10" s="28" t="str"/>
-      <c r="U10" s="28" t="str"/>
-      <c r="V10" s="28" t="str"/>
-      <c r="W10" s="28" t="str"/>
-      <c r="X10" s="28" t="str"/>
-      <c r="Y10" s="28" t="str"/>
-      <c r="Z10" s="28" t="inlineStr">
+      <c r="S10" s="40" t="str"/>
+      <c r="T10" s="40" t="str"/>
+      <c r="U10" s="40" t="str"/>
+      <c r="V10" s="40" t="str"/>
+      <c r="W10" s="40" t="str"/>
+      <c r="X10" s="40" t="str"/>
+      <c r="Y10" s="40" t="str"/>
+      <c r="Z10" s="40" t="inlineStr">
         <is>
           <t>MAX1・1/4</t>
         </is>
       </c>
-      <c r="AA10" s="28" t="str"/>
-      <c r="AB10" s="28" t="inlineStr">
+      <c r="AA10" s="40" t="str"/>
+      <c r="AB10" s="40" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC10" s="28" t="inlineStr">
+      <c r="AC10" s="40" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD10" s="28" t="str"/>
-      <c r="AE10" s="28" t="inlineStr">
+      <c r="AD10" s="40" t="str"/>
+      <c r="AE10" s="40" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF10" s="28" t="str"/>
-      <c r="AG10" s="28" t="inlineStr">
+      <c r="AF10" s="40" t="str"/>
+      <c r="AG10" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH10" s="28" t="inlineStr">
+      <c r="AH10" s="40" t="inlineStr">
         <is>
           <t>Bass power finesse bait：3/16-3/8oz Texas、Light Rubber Jig 和高比重 No Sinker 是打點核心，Spinnerbait / Chatterbait 作為 3/8-1/2oz 搜索切換。</t>
         </is>
       </c>
-      <c r="AI10" s="28" t="inlineStr">
+      <c r="AI10" s="40" t="inlineStr">
         <is>
           <t>Texas Rig / Light Rubber Jig / High-density No Sinker / Spinnerbait / Chatterbait</t>
         </is>
       </c>
-      <c r="AJ10" s="28" t="str"/>
-      <c r="AK10" s="28" t="str"/>
-      <c r="AL10" s="28" t="inlineStr">
+      <c r="AJ10" s="40" t="str"/>
+      <c r="AK10" s="40" t="str"/>
+      <c r="AL10" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM10" s="28" t="inlineStr">
+      <c r="AM10" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 邊緣與開放水域切換 / bait versatile</t>
         </is>
       </c>
-      <c r="AN10" s="28" t="inlineStr">
+      <c r="AN10" s="40" t="inlineStr">
         <is>
           <t>Texas、Light Rubber Jig 主軸的打撃搜索兩用</t>
         </is>
       </c>
-      <c r="AO10" s="28" t="inlineStr">
+      <c r="AO10" s="40" t="inlineStr">
         <is>
           <t>3/16-3/8oz Texas、Light Rubber Jig 和高比重 No Sinker 可精準打點，3/8-1/2oz Spinnerbait / Chatterbait 能快速搜索；一支竿覆蓋軟餌與 wire bait 切換。</t>
         </is>
       </c>
-      <c r="AP10" s="28" t="inlineStr">
+      <c r="AP10" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 3/16～3/8ozのテキサスリグ・ライトラバージグ、高比重ワームのノーシンカー、3/8oz～1/2oz程度のスピナーベイト・チャターベイトなどを高次元で使用可能なバーサタイルロッド。</t>
         </is>
       </c>
-      <c r="AQ10" s="28" t="inlineStr">
+      <c r="AQ10" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / ECSリールシート</t>
+        </is>
+      </c>
+      <c r="AR10" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR10" s="28" t="inlineStr">
+      <c r="AS10" s="40" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>ORD10009</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>21GVELUC-610M</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="G11" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H11" s="28" t="inlineStr">
+      <c r="H11" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" s="28" t="inlineStr">
+      <c r="I11" s="40" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="40" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="K11" s="40" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="L11" s="28" t="str"/>
-      <c r="M11" s="28" t="inlineStr">
+      <c r="L11" s="40" t="str"/>
+      <c r="M11" s="40" t="inlineStr">
         <is>
           <t>MAX16</t>
         </is>
       </c>
-      <c r="N11" s="28" t="str"/>
-      <c r="O11" s="28" t="str"/>
-      <c r="P11" s="28" t="inlineStr">
+      <c r="N11" s="40" t="str"/>
+      <c r="O11" s="40" t="str"/>
+      <c r="P11" s="40" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q11" s="28" t="str"/>
-      <c r="R11" s="28" t="inlineStr">
+      <c r="Q11" s="40" t="str"/>
+      <c r="R11" s="40" t="inlineStr">
         <is>
           <t>24,500</t>
         </is>
       </c>
-      <c r="S11" s="28" t="str"/>
-      <c r="T11" s="28" t="str"/>
-      <c r="U11" s="28" t="str"/>
-      <c r="V11" s="28" t="str"/>
-      <c r="W11" s="28" t="str"/>
-      <c r="X11" s="28" t="str"/>
-      <c r="Y11" s="28" t="str"/>
-      <c r="Z11" s="28" t="inlineStr">
+      <c r="S11" s="40" t="str"/>
+      <c r="T11" s="40" t="str"/>
+      <c r="U11" s="40" t="str"/>
+      <c r="V11" s="40" t="str"/>
+      <c r="W11" s="40" t="str"/>
+      <c r="X11" s="40" t="str"/>
+      <c r="Y11" s="40" t="str"/>
+      <c r="Z11" s="40" t="inlineStr">
         <is>
           <t>MAX1</t>
         </is>
       </c>
-      <c r="AA11" s="28" t="str"/>
-      <c r="AB11" s="28" t="inlineStr">
+      <c r="AA11" s="40" t="str"/>
+      <c r="AB11" s="40" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC11" s="28" t="inlineStr">
+      <c r="AC11" s="40" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD11" s="28" t="str"/>
-      <c r="AE11" s="28" t="inlineStr">
+      <c r="AD11" s="40" t="str"/>
+      <c r="AE11" s="40" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF11" s="28" t="str"/>
-      <c r="AG11" s="28" t="inlineStr">
+      <c r="AF11" s="40" t="str"/>
+      <c r="AG11" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH11" s="28" t="inlineStr">
+      <c r="AH11" s="40" t="inlineStr">
         <is>
           <t>Bass bait versatile：中型 hardbait 和 1/2oz 內 Spinnerbait 負責搜索，高比重 No Sinker 與 1/4oz Texas 負責慢速打點；ベントカーブ重視拋投準度。</t>
         </is>
       </c>
-      <c r="AI11" s="28" t="inlineStr">
+      <c r="AI11" s="40" t="inlineStr">
         <is>
           <t>Medium Crankbait / Medium Minnow / Spinnerbait / High-density No Sinker / Texas Rig</t>
         </is>
       </c>
-      <c r="AJ11" s="28" t="str"/>
-      <c r="AK11" s="28" t="str"/>
-      <c r="AL11" s="28" t="inlineStr">
+      <c r="AJ11" s="40" t="str"/>
+      <c r="AK11" s="40" t="str"/>
+      <c r="AL11" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM11" s="28" t="inlineStr">
+      <c r="AM11" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / 開放水域中型硬餌 / 常規岸船泛用</t>
         </is>
       </c>
-      <c r="AN11" s="28" t="inlineStr">
+      <c r="AN11" s="40" t="inlineStr">
         <is>
           <t>Medium Crankbait、Spinnerbait 與高比重 No Sinker 泛用 bait</t>
         </is>
       </c>
-      <c r="AO11" s="28" t="inlineStr">
+      <c r="AO11" s="40" t="inlineStr">
         <is>
           <t>中型 Crankbait / Minnow 和 1/2oz 內 Spinnerbait 負責搜索，高比重 No Sinker、1/4oz Texas 負責慢速打點；彎曲曲線寬容，拋投手感和準度較友好。</t>
         </is>
       </c>
-      <c r="AP11" s="28" t="inlineStr">
+      <c r="AP11" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 中型のハードベイト、1/2ozまでのスピナーベイト、4～5インチ高比重ワームのノーシンカーから1/4oz前後のテキサスリグなどに高次元で対応するバーサタイルロッド。スムースなベントカーブが爽快なキャストフィールと高いキャストアキュラシーを可能にします。</t>
         </is>
       </c>
-      <c r="AQ11" s="28" t="inlineStr">
+      <c r="AQ11" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / ECSリールシート</t>
+        </is>
+      </c>
+      <c r="AR11" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR11" s="28" t="inlineStr">
+      <c r="AS11" s="40" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>ORD10010</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="40" t="inlineStr">
         <is>
           <t>21GVELUC-70H</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="40" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>2.14</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H12" s="28" t="inlineStr">
+      <c r="H12" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="40" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="40" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="K12" s="40" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="L12" s="28" t="str"/>
-      <c r="M12" s="28" t="inlineStr">
+      <c r="L12" s="40" t="str"/>
+      <c r="M12" s="40" t="inlineStr">
         <is>
           <t>MAX20</t>
         </is>
       </c>
-      <c r="N12" s="28" t="str"/>
-      <c r="O12" s="28" t="str"/>
-      <c r="P12" s="28" t="inlineStr">
+      <c r="N12" s="40" t="str"/>
+      <c r="O12" s="40" t="str"/>
+      <c r="P12" s="40" t="inlineStr">
         <is>
           <t>Fuji ECS reel seat</t>
         </is>
       </c>
-      <c r="Q12" s="28" t="str"/>
-      <c r="R12" s="28" t="inlineStr">
+      <c r="Q12" s="40" t="str"/>
+      <c r="R12" s="40" t="inlineStr">
         <is>
           <t>25,000</t>
         </is>
       </c>
-      <c r="S12" s="28" t="str"/>
-      <c r="T12" s="28" t="str"/>
-      <c r="U12" s="28" t="str"/>
-      <c r="V12" s="28" t="str"/>
-      <c r="W12" s="28" t="str"/>
-      <c r="X12" s="28" t="str"/>
-      <c r="Y12" s="28" t="str"/>
-      <c r="Z12" s="28" t="inlineStr">
+      <c r="S12" s="40" t="str"/>
+      <c r="T12" s="40" t="str"/>
+      <c r="U12" s="40" t="str"/>
+      <c r="V12" s="40" t="str"/>
+      <c r="W12" s="40" t="str"/>
+      <c r="X12" s="40" t="str"/>
+      <c r="Y12" s="40" t="str"/>
+      <c r="Z12" s="40" t="inlineStr">
         <is>
           <t>MAX1・1/2</t>
         </is>
       </c>
-      <c r="AA12" s="28" t="str"/>
-      <c r="AB12" s="28" t="inlineStr">
+      <c r="AA12" s="40" t="str"/>
+      <c r="AB12" s="40" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC12" s="28" t="inlineStr">
+      <c r="AC12" s="40" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD12" s="28" t="str"/>
-      <c r="AE12" s="28" t="inlineStr">
+      <c r="AD12" s="40" t="str"/>
+      <c r="AE12" s="40" t="inlineStr">
         <is>
           <t>GRIP TYPE A</t>
         </is>
       </c>
-      <c r="AF12" s="28" t="str"/>
-      <c r="AG12" s="28" t="inlineStr">
+      <c r="AF12" s="40" t="str"/>
+      <c r="AG12" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH12" s="28" t="inlineStr">
+      <c r="AH12" s="40" t="inlineStr">
         <is>
           <t>Bass heavy versatile：3/8oz 以上 Texas 和 Rubber Jig 是 cover game 主軸，Heavy Spinnerbait slow roll 與 Frog 用於 vegetation 和高阻力搜索。</t>
         </is>
       </c>
-      <c r="AI12" s="28" t="inlineStr">
+      <c r="AI12" s="40" t="inlineStr">
         <is>
           <t>Texas Rig / Rubber Jig / Heavy Spinnerbait / Frog</t>
         </is>
       </c>
-      <c r="AJ12" s="28" t="str"/>
-      <c r="AK12" s="28" t="str"/>
-      <c r="AL12" s="28" t="inlineStr">
+      <c r="AJ12" s="40" t="str"/>
+      <c r="AK12" s="40" t="str"/>
+      <c r="AL12" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM12" s="28" t="inlineStr">
+      <c r="AM12" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover / vegetation frog game</t>
         </is>
       </c>
-      <c r="AN12" s="28" t="inlineStr">
+      <c r="AN12" s="40" t="inlineStr">
         <is>
           <t>Texas、Rubber Jig、Heavy Spinnerbait、Frog 的重障礙泛用</t>
         </is>
       </c>
-      <c r="AO12" s="28" t="inlineStr">
+      <c r="AO12" s="40" t="inlineStr">
         <is>
           <t>3/8oz 以上 Texas 和 Rubber Jig 可攻 cover，Heavy Spinnerbait slow roll 能沿草邊搜索，Frog 可處理 vegetation；H power 更重視控魚和脫離障礙。</t>
         </is>
       </c>
-      <c r="AP12" s="28" t="inlineStr">
+      <c r="AP12" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 3/8oz以上のテキサスリグ・ラバージグを使用したカバーゲームをメインに1/2oz以上のヘビースピナーベイトのスローロール、ベジテーションエリアでのフロッグゲームに対応するヘビーバーサタイルロッド。</t>
         </is>
       </c>
-      <c r="AQ12" s="28" t="inlineStr">
+      <c r="AQ12" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / ECSリールシート</t>
+        </is>
+      </c>
+      <c r="AR12" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR12" s="28" t="inlineStr">
+      <c r="AS12" s="40" t="inlineStr">
         <is>
           <t>■GRIP TYPE A</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>ORD10011</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>21GVELUC-74X</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="40" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H13" s="28" t="inlineStr">
+      <c r="H13" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" s="28" t="inlineStr">
+      <c r="I13" s="40" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="40" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr">
+      <c r="K13" s="40" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="L13" s="28" t="str"/>
-      <c r="M13" s="28" t="inlineStr">
+      <c r="L13" s="40" t="str"/>
+      <c r="M13" s="40" t="inlineStr">
         <is>
           <t>MAX25</t>
         </is>
       </c>
-      <c r="N13" s="28" t="str"/>
-      <c r="O13" s="28" t="str"/>
-      <c r="P13" s="28" t="inlineStr">
+      <c r="N13" s="40" t="str"/>
+      <c r="O13" s="40" t="str"/>
+      <c r="P13" s="40" t="inlineStr">
         <is>
           <t>Fuji TCS reel seat</t>
         </is>
       </c>
-      <c r="Q13" s="28" t="str"/>
-      <c r="R13" s="28" t="inlineStr">
+      <c r="Q13" s="40" t="str"/>
+      <c r="R13" s="40" t="inlineStr">
         <is>
           <t>25,500</t>
         </is>
       </c>
-      <c r="S13" s="28" t="str"/>
-      <c r="T13" s="28" t="str"/>
-      <c r="U13" s="28" t="str"/>
-      <c r="V13" s="28" t="str"/>
-      <c r="W13" s="28" t="str"/>
-      <c r="X13" s="28" t="str"/>
-      <c r="Y13" s="28" t="str"/>
-      <c r="Z13" s="28" t="inlineStr">
+      <c r="S13" s="40" t="str"/>
+      <c r="T13" s="40" t="str"/>
+      <c r="U13" s="40" t="str"/>
+      <c r="V13" s="40" t="str"/>
+      <c r="W13" s="40" t="str"/>
+      <c r="X13" s="40" t="str"/>
+      <c r="Y13" s="40" t="str"/>
+      <c r="Z13" s="40" t="inlineStr">
         <is>
           <t>MAX3</t>
         </is>
       </c>
-      <c r="AA13" s="28" t="str"/>
-      <c r="AB13" s="28" t="inlineStr">
+      <c r="AA13" s="40" t="str"/>
+      <c r="AB13" s="40" t="inlineStr">
         <is>
           <t>グリップ脱着式</t>
         </is>
       </c>
-      <c r="AC13" s="28" t="inlineStr">
+      <c r="AC13" s="40" t="inlineStr">
         <is>
           <t>BAIT MODEL</t>
         </is>
       </c>
-      <c r="AD13" s="28" t="str"/>
-      <c r="AE13" s="28" t="inlineStr">
+      <c r="AD13" s="40" t="str"/>
+      <c r="AE13" s="40" t="inlineStr">
         <is>
           <t>GRIP TYPE B</t>
         </is>
       </c>
-      <c r="AF13" s="28" t="str"/>
-      <c r="AG13" s="28" t="inlineStr">
+      <c r="AF13" s="40" t="str"/>
+      <c r="AG13" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH13" s="28" t="inlineStr">
+      <c r="AH13" s="40" t="inlineStr">
         <is>
           <t>Bass 強力長竿：Heavy Texas 放首位對應 cover 打點，MAX3oz Big Bait / Swimbait 需要粘りのある blank 承接拋投負荷與跟隨咬口。</t>
         </is>
       </c>
-      <c r="AI13" s="28" t="inlineStr">
+      <c r="AI13" s="40" t="inlineStr">
         <is>
           <t>Heavy Texas Rig / Big Bait / Swimbait</t>
         </is>
       </c>
-      <c r="AJ13" s="28" t="str"/>
-      <c r="AK13" s="28" t="str"/>
-      <c r="AL13" s="28" t="inlineStr">
+      <c r="AJ13" s="40" t="str"/>
+      <c r="AK13" s="40" t="str"/>
+      <c r="AL13" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM13" s="28" t="inlineStr">
+      <c r="AM13" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover 與大型餌 / 遠距高負荷</t>
         </is>
       </c>
-      <c r="AN13" s="28" t="inlineStr">
+      <c r="AN13" s="40" t="inlineStr">
         <is>
           <t>Heavy Texas 與 MAX3oz Big Bait / Swimbait 強力竿</t>
         </is>
       </c>
-      <c r="AO13" s="28" t="inlineStr">
+      <c r="AO13" s="40" t="inlineStr">
         <is>
           <t>Heavy Texas 用於 cover 打點，Big Bait / Swimbait 可到 MAX3oz；不是單純硬竿，粘り能承接重餌拋投與咬口跟隨，grip joint 也利於攜行。</t>
         </is>
       </c>
-      <c r="AP13" s="28" t="inlineStr">
+      <c r="AP13" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 ただ硬いだけではなく適度に粘るブランクスを採用し、1/2oz以上のヘビーテキサス、MAX3ozまでのビッグベイト＆スイムベイトに対応したパワーロッド。持ち運びに便利なグリップ脱着式を採用。</t>
         </is>
       </c>
-      <c r="AQ13" s="28" t="inlineStr">
+      <c r="AQ13" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / オールダブルフット仕様 / グリップ脱着式 / TCSリールシート</t>
+        </is>
+      </c>
+      <c r="AR13" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR13" s="28" t="inlineStr">
+      <c r="AS13" s="40" t="inlineStr">
         <is>
           <t>■GRIP TYPE B</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>ORD10012</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="40" t="inlineStr">
         <is>
           <t>21GVELUS-64L</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="40" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="40" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H14" s="28" t="inlineStr">
+      <c r="H14" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="40" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="40" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="K14" s="40" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="L14" s="28" t="str"/>
-      <c r="M14" s="28" t="inlineStr">
+      <c r="L14" s="40" t="str"/>
+      <c r="M14" s="40" t="inlineStr">
         <is>
           <t>MAX6</t>
         </is>
       </c>
-      <c r="N14" s="28" t="str"/>
-      <c r="O14" s="28" t="str"/>
-      <c r="P14" s="28" t="inlineStr">
+      <c r="N14" s="40" t="str"/>
+      <c r="O14" s="40" t="str"/>
+      <c r="P14" s="40" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q14" s="28" t="str"/>
-      <c r="R14" s="28" t="inlineStr">
+      <c r="Q14" s="40" t="str"/>
+      <c r="R14" s="40" t="inlineStr">
         <is>
           <t>23,500</t>
         </is>
       </c>
-      <c r="S14" s="28" t="str"/>
-      <c r="T14" s="28" t="str"/>
-      <c r="U14" s="28" t="str"/>
-      <c r="V14" s="28" t="str"/>
-      <c r="W14" s="28" t="str"/>
-      <c r="X14" s="28" t="str"/>
-      <c r="Y14" s="28" t="str"/>
-      <c r="Z14" s="28" t="inlineStr">
+      <c r="S14" s="40" t="str"/>
+      <c r="T14" s="40" t="str"/>
+      <c r="U14" s="40" t="str"/>
+      <c r="V14" s="40" t="str"/>
+      <c r="W14" s="40" t="str"/>
+      <c r="X14" s="40" t="str"/>
+      <c r="Y14" s="40" t="str"/>
+      <c r="Z14" s="40" t="inlineStr">
         <is>
           <t>MAX1/4</t>
         </is>
       </c>
-      <c r="AA14" s="28" t="str"/>
-      <c r="AB14" s="28" t="inlineStr">
+      <c r="AA14" s="40" t="str"/>
+      <c r="AB14" s="40" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC14" s="28" t="inlineStr">
+      <c r="AC14" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD14" s="28" t="str"/>
-      <c r="AE14" s="28" t="inlineStr">
+      <c r="AD14" s="40" t="str"/>
+      <c r="AE14" s="40" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF14" s="28" t="str"/>
-      <c r="AG14" s="28" t="inlineStr">
+      <c r="AF14" s="40" t="str"/>
+      <c r="AG14" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH14" s="28" t="inlineStr">
+      <c r="AH14" s="40" t="inlineStr">
         <is>
           <t>Bass short spinning versatile：Light rig 全般是主軸，6’4” 提升近中距離操作和落點準度；Small Crankbait / Minnow 作為小型 plug 搜索補充。</t>
         </is>
       </c>
-      <c r="AI14" s="28" t="inlineStr">
+      <c r="AI14" s="40" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Crankbait / Small Minnow</t>
         </is>
       </c>
-      <c r="AJ14" s="28" t="str"/>
-      <c r="AK14" s="28" t="str"/>
-      <c r="AL14" s="28" t="inlineStr">
+      <c r="AJ14" s="40" t="str"/>
+      <c r="AK14" s="40" t="str"/>
+      <c r="AL14" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM14" s="28" t="inlineStr">
+      <c r="AM14" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / 近中距離 finesse / 小型 plug 搜索</t>
         </is>
       </c>
-      <c r="AN14" s="28" t="inlineStr">
+      <c r="AN14" s="40" t="inlineStr">
         <is>
           <t>短尺 light rig 與 small plug 直柄泛用</t>
         </is>
       </c>
-      <c r="AO14" s="28" t="inlineStr">
+      <c r="AO14" s="40" t="inlineStr">
         <is>
           <t>6'4" 長度提升近距離落點和竿尖操作，Neko、Down Shot、No Sinker 做食わせ，小型 Crankbait / Minnow 可搜索；較 regular 的調性讓拋投手感更順。</t>
         </is>
       </c>
-      <c r="AP14" s="28" t="inlineStr">
+      <c r="AP14" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 ライトリグ全般からスモールプラグまで高次元で対応したバーサタイルロッド。極端なファーストテーパーは避け、ややレギュラーよりなテーパーとすることで、爽快なキャストフィールとライトリグの操作性を追求。6’4”のレングスが高い操作性と飛距離を両立します。</t>
         </is>
       </c>
-      <c r="AQ14" s="28" t="inlineStr">
+      <c r="AQ14" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / VSSリールシート</t>
+        </is>
+      </c>
+      <c r="AR14" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR14" s="28" t="str"/>
+      <c r="AS14" s="40" t="str"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>ORD10013</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>21GVELUS-610ML</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="40" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H15" s="28" t="inlineStr">
+      <c r="H15" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" s="28" t="inlineStr">
+      <c r="I15" s="40" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="40" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr">
+      <c r="K15" s="40" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="L15" s="28" t="str"/>
-      <c r="M15" s="28" t="inlineStr">
+      <c r="L15" s="40" t="str"/>
+      <c r="M15" s="40" t="inlineStr">
         <is>
           <t>MAX6</t>
         </is>
       </c>
-      <c r="N15" s="28" t="inlineStr">
+      <c r="N15" s="40" t="inlineStr">
         <is>
           <t>MAX0.8</t>
         </is>
       </c>
-      <c r="O15" s="28" t="str"/>
-      <c r="P15" s="28" t="inlineStr">
+      <c r="O15" s="40" t="str"/>
+      <c r="P15" s="40" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q15" s="28" t="str"/>
-      <c r="R15" s="28" t="inlineStr">
+      <c r="Q15" s="40" t="str"/>
+      <c r="R15" s="40" t="inlineStr">
         <is>
           <t>24,000</t>
         </is>
       </c>
-      <c r="S15" s="28" t="str"/>
-      <c r="T15" s="28" t="str"/>
-      <c r="U15" s="28" t="str"/>
-      <c r="V15" s="28" t="str"/>
-      <c r="W15" s="28" t="str"/>
-      <c r="X15" s="28" t="str"/>
-      <c r="Y15" s="28" t="str"/>
-      <c r="Z15" s="28" t="inlineStr">
+      <c r="S15" s="40" t="str"/>
+      <c r="T15" s="40" t="str"/>
+      <c r="U15" s="40" t="str"/>
+      <c r="V15" s="40" t="str"/>
+      <c r="W15" s="40" t="str"/>
+      <c r="X15" s="40" t="str"/>
+      <c r="Y15" s="40" t="str"/>
+      <c r="Z15" s="40" t="inlineStr">
         <is>
           <t>MAX3/8</t>
         </is>
       </c>
-      <c r="AA15" s="28" t="str"/>
-      <c r="AB15" s="28" t="inlineStr">
+      <c r="AA15" s="40" t="str"/>
+      <c r="AB15" s="40" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC15" s="28" t="inlineStr">
+      <c r="AC15" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD15" s="28" t="str"/>
-      <c r="AE15" s="28" t="inlineStr">
+      <c r="AD15" s="40" t="str"/>
+      <c r="AE15" s="40" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF15" s="28" t="str"/>
-      <c r="AG15" s="28" t="inlineStr">
+      <c r="AF15" s="40" t="str"/>
+      <c r="AG15" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH15" s="28" t="inlineStr">
+      <c r="AH15" s="40" t="inlineStr">
         <is>
           <t>Bass long versatile spin：利用 6’10” 的遠投性能投送 Neko、Down Shot 和 No Sinker，輕量平衡保留細操作；Small Plug 用於遠處搜索。</t>
         </is>
       </c>
-      <c r="AI15" s="28" t="inlineStr">
+      <c r="AI15" s="40" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / Down Shot / No Sinker / Small Crankbait / Small Minnow</t>
         </is>
       </c>
-      <c r="AJ15" s="28" t="str"/>
-      <c r="AK15" s="28" t="str"/>
-      <c r="AL15" s="28" t="inlineStr">
+      <c r="AJ15" s="40" t="str"/>
+      <c r="AK15" s="40" t="str"/>
+      <c r="AL15" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM15" s="28" t="inlineStr">
+      <c r="AM15" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸投遠投 finesse / 開放水域長距離控線</t>
         </is>
       </c>
-      <c r="AN15" s="28" t="inlineStr">
+      <c r="AN15" s="40" t="inlineStr">
         <is>
           <t>Long Cast Neko、Down Shot 與小型 plug 的長尺直柄</t>
         </is>
       </c>
-      <c r="AO15" s="28" t="inlineStr">
+      <c r="AO15" s="40" t="inlineStr">
         <is>
           <t>6'10" 長度放大 light rig 投送距離，輕量平衡保留細操作；Neko、Down Shot、No Sinker 是主軸，小型 Crankbait / Minnow 用於遠處搜索。</t>
         </is>
       </c>
-      <c r="AP15" s="28" t="inlineStr">
+      <c r="AP15" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 ロッドレングスを活かしたロングキャスト性能と幅広いルアーに対応したロングバーサタイルスピン。6’10”というレングスを感じさせない軽量感とロッドバランスにより繊細な操作を可能にします。</t>
         </is>
       </c>
-      <c r="AQ15" s="28" t="inlineStr">
+      <c r="AQ15" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / VSSリールシート</t>
+        </is>
+      </c>
+      <c r="AR15" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR15" s="28" t="str"/>
+      <c r="AS15" s="40" t="str"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>ORD10014</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="40" t="inlineStr">
         <is>
           <t>21GVELUS-611H-PF</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H16" s="28" t="inlineStr">
+      <c r="H16" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" s="28" t="inlineStr">
+      <c r="I16" s="40" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="40" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="K16" s="28" t="inlineStr">
+      <c r="K16" s="40" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="L16" s="28" t="str"/>
-      <c r="M16" s="28" t="str"/>
-      <c r="N16" s="28" t="inlineStr">
+      <c r="L16" s="40" t="str"/>
+      <c r="M16" s="40" t="str"/>
+      <c r="N16" s="40" t="inlineStr">
         <is>
           <t>MAX2</t>
         </is>
       </c>
-      <c r="O16" s="28" t="str"/>
-      <c r="P16" s="28" t="inlineStr">
+      <c r="O16" s="40" t="str"/>
+      <c r="P16" s="40" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q16" s="28" t="str"/>
-      <c r="R16" s="28" t="inlineStr">
+      <c r="Q16" s="40" t="str"/>
+      <c r="R16" s="40" t="inlineStr">
         <is>
           <t>25,200</t>
         </is>
       </c>
-      <c r="S16" s="28" t="str"/>
-      <c r="T16" s="28" t="str"/>
-      <c r="U16" s="28" t="str"/>
-      <c r="V16" s="28" t="str"/>
-      <c r="W16" s="28" t="str"/>
-      <c r="X16" s="28" t="str"/>
-      <c r="Y16" s="28" t="str"/>
-      <c r="Z16" s="28" t="inlineStr">
+      <c r="S16" s="40" t="str"/>
+      <c r="T16" s="40" t="str"/>
+      <c r="U16" s="40" t="str"/>
+      <c r="V16" s="40" t="str"/>
+      <c r="W16" s="40" t="str"/>
+      <c r="X16" s="40" t="str"/>
+      <c r="Y16" s="40" t="str"/>
+      <c r="Z16" s="40" t="inlineStr">
         <is>
           <t>MAX3/4</t>
         </is>
       </c>
-      <c r="AA16" s="28" t="str"/>
-      <c r="AB16" s="28" t="inlineStr">
+      <c r="AA16" s="40" t="str"/>
+      <c r="AB16" s="40" t="inlineStr">
         <is>
           <t>1ピース</t>
         </is>
       </c>
-      <c r="AC16" s="28" t="inlineStr">
+      <c r="AC16" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD16" s="28" t="str"/>
-      <c r="AE16" s="28" t="inlineStr">
+      <c r="AD16" s="40" t="str"/>
+      <c r="AE16" s="40" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF16" s="28" t="str"/>
-      <c r="AG16" s="28" t="inlineStr">
+      <c r="AF16" s="40" t="str"/>
+      <c r="AG16" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH16" s="28" t="inlineStr">
+      <c r="AH16" s="40" t="inlineStr">
         <is>
           <t>Bass power finesse：PE 線下 Cover Neko、Small Rubber Jig 和高比重 No Sinker 能打進 heavy cover，控線和拉離障礙是重點。</t>
         </is>
       </c>
-      <c r="AI16" s="28" t="inlineStr">
+      <c r="AI16" s="40" t="inlineStr">
         <is>
           <t>Cover Neko / Small Rubber Jig / Heavy Cover No Sinker</t>
         </is>
       </c>
-      <c r="AJ16" s="28" t="str"/>
-      <c r="AK16" s="28" t="str"/>
-      <c r="AL16" s="28" t="inlineStr">
+      <c r="AJ16" s="40" t="str"/>
+      <c r="AK16" s="40" t="str"/>
+      <c r="AL16" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM16" s="28" t="inlineStr">
+      <c r="AM16" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover power finesse / PE 直柄強攻</t>
         </is>
       </c>
-      <c r="AN16" s="28" t="inlineStr">
+      <c r="AN16" s="40" t="inlineStr">
         <is>
           <t>Cover Neko 與 Small Rubber Jig 的 heavy cover power spin</t>
         </is>
       </c>
-      <c r="AO16" s="28" t="inlineStr">
+      <c r="AO16" s="40" t="inlineStr">
         <is>
           <t>PE 線下可把 Cover Neko、Small Rubber Jig 和高比重 No Sinker 打進難攻 cover，短柄提升操作和起魚節奏；重點是精細餌進 cover 後的強制控魚。</t>
         </is>
       </c>
-      <c r="AP16" s="28" t="inlineStr">
+      <c r="AP16" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉 難攻不落なヘビーカバーを攻略するパワースピニングモデル。ショートセッティングのセパレートハンドルは取り回しも抜群。他のパワーフィネスロッドと比べても圧倒的にパワフルで、通常では攻めあぐねてしまうようなヘビーカバーでも大胆に攻め込む事ができます。</t>
         </is>
       </c>
-      <c r="AQ16" s="28" t="inlineStr">
+      <c r="AQ16" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / VSSリールシート</t>
+        </is>
+      </c>
+      <c r="AR16" s="40" t="inlineStr">
         <is>
           <t>〈パワーフィネスモデル〉</t>
         </is>
       </c>
-      <c r="AR16" s="28" t="str"/>
+      <c r="AS16" s="40" t="str"/>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>ORD10015</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>OR1001</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr">
         <is>
           <t>21GVELUS-742M</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="I17" s="40" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="40" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr">
+      <c r="K17" s="40" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="L17" s="28" t="str"/>
-      <c r="M17" s="28" t="inlineStr">
+      <c r="L17" s="40" t="str"/>
+      <c r="M17" s="40" t="inlineStr">
         <is>
           <t>MAX8</t>
         </is>
       </c>
-      <c r="N17" s="28" t="inlineStr">
+      <c r="N17" s="40" t="inlineStr">
         <is>
           <t>MAX0.8</t>
         </is>
       </c>
-      <c r="O17" s="28" t="str"/>
-      <c r="P17" s="28" t="inlineStr">
+      <c r="O17" s="40" t="str"/>
+      <c r="P17" s="40" t="inlineStr">
         <is>
           <t>Fuji VSS reel seat</t>
         </is>
       </c>
-      <c r="Q17" s="28" t="str"/>
-      <c r="R17" s="28" t="inlineStr">
+      <c r="Q17" s="40" t="str"/>
+      <c r="R17" s="40" t="inlineStr">
         <is>
           <t>25,500</t>
         </is>
       </c>
-      <c r="S17" s="28" t="str"/>
-      <c r="T17" s="28" t="str"/>
-      <c r="U17" s="28" t="str"/>
-      <c r="V17" s="28" t="str"/>
-      <c r="W17" s="28" t="str"/>
-      <c r="X17" s="28" t="str"/>
-      <c r="Y17" s="28" t="str"/>
-      <c r="Z17" s="28" t="inlineStr">
+      <c r="S17" s="40" t="str"/>
+      <c r="T17" s="40" t="str"/>
+      <c r="U17" s="40" t="str"/>
+      <c r="V17" s="40" t="str"/>
+      <c r="W17" s="40" t="str"/>
+      <c r="X17" s="40" t="str"/>
+      <c r="Y17" s="40" t="str"/>
+      <c r="Z17" s="40" t="inlineStr">
         <is>
           <t>MAX1/2</t>
         </is>
       </c>
-      <c r="AA17" s="28" t="str"/>
-      <c r="AB17" s="28" t="inlineStr">
+      <c r="AA17" s="40" t="str"/>
+      <c r="AB17" s="40" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC17" s="28" t="inlineStr">
+      <c r="AC17" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD17" s="28" t="str"/>
-      <c r="AE17" s="28" t="inlineStr">
+      <c r="AD17" s="40" t="str"/>
+      <c r="AE17" s="40" t="inlineStr">
         <is>
           <t>EVA</t>
         </is>
       </c>
-      <c r="AF17" s="28" t="str"/>
-      <c r="AG17" s="28" t="inlineStr">
+      <c r="AF17" s="40" t="str"/>
+      <c r="AG17" s="40" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH17" s="28" t="inlineStr">
+      <c r="AH17" s="40" t="inlineStr">
         <is>
           <t>Bass PE long cast versatile：PE light rig 遠投是核心，Long Cast Neko、PE Down Shot 和 No Sinker 放前；1/2oz Spinnerbait、Vibration 作為較重搜索補充。</t>
         </is>
       </c>
-      <c r="AI17" s="28" t="inlineStr">
+      <c r="AI17" s="40" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / PE Down Shot / No Sinker / Spinnerbait / Vibration</t>
         </is>
       </c>
-      <c r="AJ17" s="28" t="str"/>
-      <c r="AK17" s="28" t="str"/>
-      <c r="AL17" s="28" t="inlineStr">
+      <c r="AJ17" s="40" t="str"/>
+      <c r="AK17" s="40" t="str"/>
+      <c r="AL17" s="40" t="inlineStr">
         <is>
           <t>Black Bass</t>
         </is>
       </c>
-      <c r="AM17" s="28" t="inlineStr">
+      <c r="AM17" s="40" t="inlineStr">
         <is>
           <t>淡水 Bass / PE 遠投 / light rig 到中量 moving bait</t>
         </is>
       </c>
-      <c r="AN17" s="28" t="inlineStr">
+      <c r="AN17" s="40" t="inlineStr">
         <is>
           <t>PE 遠投 light rig 兼 1/2oz moving bait 直柄</t>
         </is>
       </c>
-      <c r="AO17" s="28" t="inlineStr">
+      <c r="AO17" s="40" t="inlineStr">
         <is>
           <t>Long Cast Neko、PE Down Shot、No Sinker 是核心，7'4" 長度提升遠投與回線效率；Spinnerbait、Vibration 可作較重搜索端，混合用途邊界清楚。</t>
         </is>
       </c>
-      <c r="AP17" s="28" t="inlineStr">
+      <c r="AP17" s="40" t="inlineStr">
         <is>
           <t>PEラインを使用しライトリグを遠投するスタイルに最適なモデル。ライトリグ全般から1/2ozまでのスピナーベイト、バイブレーション等のハードベイトにも対応したバーサタイル性能を持っています。</t>
         </is>
       </c>
-      <c r="AQ17" s="28" t="str"/>
-      <c r="AR17" s="28" t="str"/>
+      <c r="AQ17" s="40" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-SリングKガイド / VSSリールシート / フェルール（逆並継）</t>
+        </is>
+      </c>
+      <c r="AR17" s="40" t="str"/>
+      <c r="AS17" s="40" t="str"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>ORD10016</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>OR1002</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D18" s="41" t="inlineStr">
         <is>
           <t>GSBS-602XUL</t>
         </is>
       </c>
-      <c r="E18" s="29" t="inlineStr">
+      <c r="E18" s="41" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr">
+      <c r="G18" s="41" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H18" s="29" t="inlineStr">
+      <c r="H18" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I18" s="29" t="inlineStr">
+      <c r="I18" s="41" t="inlineStr">
         <is>
           <t>93.7</t>
         </is>
       </c>
-      <c r="J18" s="29" t="inlineStr">
+      <c r="J18" s="41" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="K18" s="29" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L18" s="29" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>0.4-3.5</t>
         </is>
       </c>
-      <c r="M18" s="29" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="N18" s="29" t="str"/>
-      <c r="O18" s="29" t="str"/>
-      <c r="P18" s="29" t="inlineStr">
+      <c r="N18" s="41" t="str"/>
+      <c r="O18" s="41" t="str"/>
+      <c r="P18" s="41" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q18" s="29" t="str"/>
-      <c r="R18" s="29" t="inlineStr">
+      <c r="Q18" s="41" t="str"/>
+      <c r="R18" s="41" t="inlineStr">
         <is>
           <t>63,000</t>
         </is>
       </c>
-      <c r="S18" s="29" t="str"/>
-      <c r="T18" s="29" t="str"/>
-      <c r="U18" s="29" t="str"/>
-      <c r="V18" s="29" t="str"/>
-      <c r="W18" s="29" t="str"/>
-      <c r="X18" s="29" t="str"/>
-      <c r="Y18" s="29" t="str"/>
-      <c r="Z18" s="29" t="str"/>
-      <c r="AA18" s="29" t="str"/>
-      <c r="AB18" s="29" t="inlineStr">
+      <c r="S18" s="41" t="str"/>
+      <c r="T18" s="41" t="str"/>
+      <c r="U18" s="41" t="str"/>
+      <c r="V18" s="41" t="str"/>
+      <c r="W18" s="41" t="str"/>
+      <c r="X18" s="41" t="str"/>
+      <c r="Y18" s="41" t="str"/>
+      <c r="Z18" s="41" t="str"/>
+      <c r="AA18" s="41" t="str"/>
+      <c r="AB18" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC18" s="29" t="inlineStr">
+      <c r="AC18" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD18" s="29" t="str"/>
-      <c r="AE18" s="29" t="inlineStr">
+      <c r="AD18" s="41" t="str"/>
+      <c r="AE18" s="41" t="inlineStr">
         <is>
           <t>High grade cork / burl wood</t>
         </is>
       </c>
-      <c r="AF18" s="29" t="str"/>
-      <c r="AG18" s="29" t="inlineStr">
+      <c r="AF18" s="41" t="str"/>
+      <c r="AG18" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH18" s="29" t="inlineStr">
+      <c r="AH18" s="41" t="inlineStr">
         <is>
           <t>管釣 super-light：XUL、0.4-3.5g、1-3lb 對應 Micro Spoon / Micro Crankbait，重點是低負荷出線、短咬口承接和細線控魚。</t>
         </is>
       </c>
-      <c r="AI18" s="29" t="inlineStr">
+      <c r="AI18" s="41" t="inlineStr">
         <is>
           <t>Micro Spoon / Micro Crankbait / Small Spoon</t>
         </is>
       </c>
-      <c r="AJ18" s="29" t="str"/>
-      <c r="AK18" s="29" t="str"/>
-      <c r="AL18" s="29" t="inlineStr">
+      <c r="AJ18" s="41" t="str"/>
+      <c r="AK18" s="41" t="str"/>
+      <c r="AL18" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM18" s="29" t="inlineStr">
+      <c r="AM18" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 小池高壓場 / micro spoon-crank</t>
         </is>
       </c>
-      <c r="AN18" s="29" t="inlineStr">
+      <c r="AN18" s="41" t="inlineStr">
         <is>
           <t>XUL micro spoon 與 micro crank 精細型</t>
         </is>
       </c>
-      <c r="AO18" s="29" t="inlineStr">
+      <c r="AO18" s="41" t="inlineStr">
         <is>
           <t>0.4-3.5g 與 1-3lb 線組適合低負荷 Micro Spoon、Micro Crankbait；高感 cork 與輕量 guide 對短咬口和細線控魚更有幫助。</t>
         </is>
       </c>
-      <c r="AP18" s="29" t="inlineStr">
+      <c r="AP18" s="41" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="AQ18" s="29" t="str"/>
-      <c r="AR18" s="29" t="str"/>
+      <c r="AQ18" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / チタンフレームトルザイトリングガイド / Fuji TORZITE / オリジナルシート / スピゴットフェルール（印籠継）</t>
+        </is>
+      </c>
+      <c r="AR18" s="41" t="str"/>
+      <c r="AS18" s="41" t="str"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>ORD10017</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>OR1002</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="41" t="inlineStr">
         <is>
           <t>GSBS-642UL</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="41" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr">
+      <c r="G19" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H19" s="29" t="inlineStr">
+      <c r="H19" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="29" t="inlineStr">
+      <c r="I19" s="41" t="inlineStr">
         <is>
           <t>98.8</t>
         </is>
       </c>
-      <c r="J19" s="29" t="inlineStr">
+      <c r="J19" s="41" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="K19" s="29" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L19" s="29" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>0.5-5</t>
         </is>
       </c>
-      <c r="M19" s="29" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>1.5-4</t>
         </is>
       </c>
-      <c r="N19" s="29" t="str"/>
-      <c r="O19" s="29" t="str"/>
-      <c r="P19" s="29" t="inlineStr">
+      <c r="N19" s="41" t="str"/>
+      <c r="O19" s="41" t="str"/>
+      <c r="P19" s="41" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q19" s="29" t="str"/>
-      <c r="R19" s="29" t="inlineStr">
+      <c r="Q19" s="41" t="str"/>
+      <c r="R19" s="41" t="inlineStr">
         <is>
           <t>64,000</t>
         </is>
       </c>
-      <c r="S19" s="29" t="str"/>
-      <c r="T19" s="29" t="str"/>
-      <c r="U19" s="29" t="str"/>
-      <c r="V19" s="29" t="str"/>
-      <c r="W19" s="29" t="str"/>
-      <c r="X19" s="29" t="str"/>
-      <c r="Y19" s="29" t="str"/>
-      <c r="Z19" s="29" t="str"/>
-      <c r="AA19" s="29" t="str"/>
-      <c r="AB19" s="29" t="inlineStr">
+      <c r="S19" s="41" t="str"/>
+      <c r="T19" s="41" t="str"/>
+      <c r="U19" s="41" t="str"/>
+      <c r="V19" s="41" t="str"/>
+      <c r="W19" s="41" t="str"/>
+      <c r="X19" s="41" t="str"/>
+      <c r="Y19" s="41" t="str"/>
+      <c r="Z19" s="41" t="str"/>
+      <c r="AA19" s="41" t="str"/>
+      <c r="AB19" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC19" s="29" t="inlineStr">
+      <c r="AC19" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD19" s="29" t="str"/>
-      <c r="AE19" s="29" t="inlineStr">
+      <c r="AD19" s="41" t="str"/>
+      <c r="AE19" s="41" t="inlineStr">
         <is>
           <t>High grade cork / burl wood</t>
         </is>
       </c>
-      <c r="AF19" s="29" t="str"/>
-      <c r="AG19" s="29" t="inlineStr">
+      <c r="AF19" s="41" t="str"/>
+      <c r="AG19" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH19" s="29" t="inlineStr">
+      <c r="AH19" s="41" t="inlineStr">
         <is>
           <t>管釣中量 lure：Spoon、Crankbait 和 Small Minnow 的拋投與回收穩定，兼顧細線操作和中距離控魚。</t>
         </is>
       </c>
-      <c r="AI19" s="29" t="inlineStr">
+      <c r="AI19" s="41" t="inlineStr">
         <is>
           <t>Spoon / Crankbait / Small Minnow</t>
         </is>
       </c>
-      <c r="AJ19" s="29" t="str"/>
-      <c r="AK19" s="29" t="str"/>
-      <c r="AL19" s="29" t="inlineStr">
+      <c r="AJ19" s="41" t="str"/>
+      <c r="AK19" s="41" t="str"/>
+      <c r="AL19" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM19" s="29" t="inlineStr">
+      <c r="AM19" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 標準池 spoon-crank / 中距離控魚</t>
         </is>
       </c>
-      <c r="AN19" s="29" t="inlineStr">
+      <c r="AN19" s="41" t="inlineStr">
         <is>
           <t>UL spoon、crank、small minnow 中量泛用</t>
         </is>
       </c>
-      <c r="AO19" s="29" t="inlineStr">
+      <c r="AO19" s="41" t="inlineStr">
         <is>
           <t>0.5-5g、1.5-4lb 覆蓋標準 Spoon、Crankbait 和 Small Minnow，較 602XUL 更能應付中距離和稍大魚，仍保留細線操作感。</t>
         </is>
       </c>
-      <c r="AP19" s="29" t="inlineStr">
+      <c r="AP19" s="41" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="AQ19" s="29" t="str"/>
-      <c r="AR19" s="29" t="str"/>
+      <c r="AQ19" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / チタンフレームトルザイトリングガイド / Fuji TORZITE / オリジナルシート / スピゴットフェルール（印籠継）</t>
+        </is>
+      </c>
+      <c r="AR19" s="41" t="str"/>
+      <c r="AS19" s="41" t="str"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>ORD10018</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>OR1002</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="41" t="inlineStr">
         <is>
           <t>GSBS-672L</t>
         </is>
       </c>
-      <c r="E20" s="29" t="inlineStr">
+      <c r="E20" s="41" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr">
+      <c r="G20" s="41" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H20" s="29" t="inlineStr">
+      <c r="H20" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I20" s="29" t="inlineStr">
+      <c r="I20" s="41" t="inlineStr">
         <is>
           <t>102.6</t>
         </is>
       </c>
-      <c r="J20" s="29" t="inlineStr">
+      <c r="J20" s="41" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="K20" s="29" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L20" s="29" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>0.6-7</t>
         </is>
       </c>
-      <c r="M20" s="29" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>2-5</t>
         </is>
       </c>
-      <c r="N20" s="29" t="str"/>
-      <c r="O20" s="29" t="str"/>
-      <c r="P20" s="29" t="inlineStr">
+      <c r="N20" s="41" t="str"/>
+      <c r="O20" s="41" t="str"/>
+      <c r="P20" s="41" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q20" s="29" t="str"/>
-      <c r="R20" s="29" t="inlineStr">
+      <c r="Q20" s="41" t="str"/>
+      <c r="R20" s="41" t="inlineStr">
         <is>
           <t>65,000</t>
         </is>
       </c>
-      <c r="S20" s="29" t="str"/>
-      <c r="T20" s="29" t="str"/>
-      <c r="U20" s="29" t="str"/>
-      <c r="V20" s="29" t="str"/>
-      <c r="W20" s="29" t="str"/>
-      <c r="X20" s="29" t="str"/>
-      <c r="Y20" s="29" t="str"/>
-      <c r="Z20" s="29" t="str"/>
-      <c r="AA20" s="29" t="str"/>
-      <c r="AB20" s="29" t="inlineStr">
+      <c r="S20" s="41" t="str"/>
+      <c r="T20" s="41" t="str"/>
+      <c r="U20" s="41" t="str"/>
+      <c r="V20" s="41" t="str"/>
+      <c r="W20" s="41" t="str"/>
+      <c r="X20" s="41" t="str"/>
+      <c r="Y20" s="41" t="str"/>
+      <c r="Z20" s="41" t="str"/>
+      <c r="AA20" s="41" t="str"/>
+      <c r="AB20" s="41" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC20" s="29" t="inlineStr">
+      <c r="AC20" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD20" s="29" t="str"/>
-      <c r="AE20" s="29" t="inlineStr">
+      <c r="AD20" s="41" t="str"/>
+      <c r="AE20" s="41" t="inlineStr">
         <is>
           <t>High grade cork / burl wood</t>
         </is>
       </c>
-      <c r="AF20" s="29" t="str"/>
-      <c r="AG20" s="29" t="inlineStr">
+      <c r="AF20" s="41" t="str"/>
+      <c r="AG20" s="41" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH20" s="29" t="inlineStr">
+      <c r="AH20" s="41" t="inlineStr">
         <is>
           <t>管釣中大型 lure：Full-size Spoon、Crankbait 和 Minnow 負荷更高，長距離控線與大型 trout 控魚比小餌型號更有餘量。</t>
         </is>
       </c>
-      <c r="AI20" s="29" t="inlineStr">
+      <c r="AI20" s="41" t="inlineStr">
         <is>
           <t>Full-size Spoon / Crankbait / Minnow</t>
         </is>
       </c>
-      <c r="AJ20" s="29" t="str"/>
-      <c r="AK20" s="29" t="str"/>
-      <c r="AL20" s="29" t="inlineStr">
+      <c r="AJ20" s="41" t="str"/>
+      <c r="AK20" s="41" t="str"/>
+      <c r="AL20" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM20" s="29" t="inlineStr">
+      <c r="AM20" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 大池遠投 / full-size lure</t>
         </is>
       </c>
-      <c r="AN20" s="29" t="inlineStr">
+      <c r="AN20" s="41" t="inlineStr">
         <is>
           <t>L power full-size spoon / crank / minnow 強化型</t>
         </is>
       </c>
-      <c r="AO20" s="29" t="inlineStr">
+      <c r="AO20" s="41" t="inlineStr">
         <is>
           <t>0.6-7g、2-5lb 可承接 Full-size Spoon、Crankbait、Minnow，長度和 L power 更適合大池遠投與較大型 trout 控魚。</t>
         </is>
       </c>
-      <c r="AP20" s="29" t="inlineStr">
+      <c r="AP20" s="41" t="inlineStr">
         <is>
           <t>カーボン、ガイド、グリップ、全てにおいて最高級をまとい生まれ変わった二代目Super Bellezza。東レ「トレカ®T1100G」+「スーパークワトログラファイトクロスLV」の採用により軽量でトルキーなブランクスを実現。さらにバットにシリーズ初となる「G-MAPS製法」を導入、抜群のリフティングパワーを手にした。ガイドは軽量なトルザイトリング、グリップには高感度ハイグレードコルクを採用。スーパークラスのみ許された豪華なスペックで輝きを放ちます。</t>
         </is>
       </c>
-      <c r="AQ20" s="29" t="str"/>
-      <c r="AR20" s="29" t="str"/>
+      <c r="AQ20" s="41" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / チタンフレームトルザイトリングガイド / Fuji TORZITE / オリジナルシート / スピゴットフェルール（印籠継）</t>
+        </is>
+      </c>
+      <c r="AR20" s="41" t="str"/>
+      <c r="AS20" s="41" t="str"/>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>ORD10019</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="40" t="inlineStr">
         <is>
           <t>26GBELPS-572XUL-S</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="40" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="H21" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I21" s="28" t="inlineStr">
+      <c r="I21" s="40" t="inlineStr">
         <is>
           <t>87.4</t>
         </is>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr">
+      <c r="K21" s="40" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="L21" s="28" t="inlineStr">
+      <c r="L21" s="40" t="inlineStr">
         <is>
           <t>0.2-2.5</t>
         </is>
       </c>
-      <c r="M21" s="28" t="inlineStr">
+      <c r="M21" s="40" t="inlineStr">
         <is>
           <t>MAX3</t>
         </is>
       </c>
-      <c r="N21" s="28" t="str"/>
-      <c r="O21" s="28" t="str"/>
-      <c r="P21" s="28" t="inlineStr">
+      <c r="N21" s="40" t="str"/>
+      <c r="O21" s="40" t="str"/>
+      <c r="P21" s="40" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q21" s="28" t="str"/>
-      <c r="R21" s="28" t="inlineStr">
+      <c r="Q21" s="40" t="str"/>
+      <c r="R21" s="40" t="inlineStr">
         <is>
           <t>54,000</t>
         </is>
       </c>
-      <c r="S21" s="28" t="str"/>
-      <c r="T21" s="28" t="str"/>
-      <c r="U21" s="28" t="str"/>
-      <c r="V21" s="28" t="str"/>
-      <c r="W21" s="28" t="str"/>
-      <c r="X21" s="28" t="str"/>
-      <c r="Y21" s="28" t="str"/>
-      <c r="Z21" s="28" t="str"/>
-      <c r="AA21" s="28" t="str"/>
-      <c r="AB21" s="28" t="inlineStr">
+      <c r="S21" s="40" t="str"/>
+      <c r="T21" s="40" t="str"/>
+      <c r="U21" s="40" t="str"/>
+      <c r="V21" s="40" t="str"/>
+      <c r="W21" s="40" t="str"/>
+      <c r="X21" s="40" t="str"/>
+      <c r="Y21" s="40" t="str"/>
+      <c r="Z21" s="40" t="str"/>
+      <c r="AA21" s="40" t="str"/>
+      <c r="AB21" s="40" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC21" s="28" t="inlineStr">
+      <c r="AC21" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD21" s="28" t="str"/>
-      <c r="AE21" s="28" t="inlineStr">
+      <c r="AD21" s="40" t="str"/>
+      <c r="AE21" s="40" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF21" s="28" t="str"/>
-      <c r="AG21" s="28" t="inlineStr">
+      <c r="AF21" s="40" t="str"/>
+      <c r="AG21" s="40" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH21" s="28" t="inlineStr">
+      <c r="AH21" s="40" t="inlineStr">
         <is>
           <t>管釣 solid tip 微小餌：Micro Spoon、Micro Crankbait 在シビア狀況下更容易讓魚口殘留，Vertical Spoon 可利用 tubular 部分張力做縦釣り。</t>
         </is>
       </c>
-      <c r="AI21" s="28" t="inlineStr">
+      <c r="AI21" s="40" t="inlineStr">
         <is>
           <t>Micro Spoon / Micro Crankbait / Vertical Spoon</t>
         </is>
       </c>
-      <c r="AJ21" s="28" t="str"/>
-      <c r="AK21" s="28" t="str"/>
-      <c r="AL21" s="28" t="inlineStr">
+      <c r="AJ21" s="40" t="str"/>
+      <c r="AK21" s="40" t="str"/>
+      <c r="AL21" s="40" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM21" s="28" t="inlineStr">
+      <c r="AM21" s="40" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 高壓慢魚 / ester line micro lure</t>
         </is>
       </c>
-      <c r="AN21" s="28" t="inlineStr">
+      <c r="AN21" s="40" t="inlineStr">
         <is>
           <t>solid tip micro spoon / micro crank 掛け型精細</t>
         </is>
       </c>
-      <c r="AO21" s="28" t="inlineStr">
+      <c r="AO21" s="40" t="inlineStr">
         <is>
           <t>Micro Spoon、Micro Crankbait 在シビア場更容易讓魚口殘留，solid tip 吸收短咬，tubular 部分張力可補縦釣り操作。</t>
         </is>
       </c>
-      <c r="AP21" s="28" t="inlineStr">
+      <c r="AP21" s="40" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉 マイクロスプーン、マイクロクランクなどに対応したシビアな状況下で活躍するソリッドティップモデル。チューブラーティップで掛からないときでも繊細なソリッドティップが曲がり込み、フックが口に残ることで掛けることが可能に。チューブラー部分の張りを活かし、縦釣りなどにも対応する。主流となりつつあるエステルラインに対応したガイドセッティング。</t>
         </is>
       </c>
-      <c r="AQ21" s="28" t="inlineStr">
+      <c r="AQ21" s="40" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / O.S.S / チタンフレームトルザイトリングガイド / チタンフレームSiCトップガイド / スピゴットフェルール（印籠継） / オリジナルシート / エステルライン対応ガイドセッティング / ソリッドティップ</t>
+        </is>
+      </c>
+      <c r="AR21" s="40" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉</t>
         </is>
       </c>
-      <c r="AR21" s="28" t="str"/>
+      <c r="AS21" s="40" t="str"/>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>ORD10020</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="40" t="inlineStr">
         <is>
           <t>26GBELPS-582SUL-T</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="H22" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr">
+      <c r="I22" s="40" t="inlineStr">
         <is>
           <t>88.6</t>
         </is>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J22" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K22" s="28" t="inlineStr">
+      <c r="K22" s="40" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L22" s="28" t="inlineStr">
+      <c r="L22" s="40" t="inlineStr">
         <is>
           <t>0.5-3.5</t>
         </is>
       </c>
-      <c r="M22" s="28" t="inlineStr">
+      <c r="M22" s="40" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N22" s="28" t="str"/>
-      <c r="O22" s="28" t="str"/>
-      <c r="P22" s="28" t="inlineStr">
+      <c r="N22" s="40" t="str"/>
+      <c r="O22" s="40" t="str"/>
+      <c r="P22" s="40" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q22" s="28" t="str"/>
-      <c r="R22" s="28" t="inlineStr">
+      <c r="Q22" s="40" t="str"/>
+      <c r="R22" s="40" t="inlineStr">
         <is>
           <t>55,000</t>
         </is>
       </c>
-      <c r="S22" s="28" t="str"/>
-      <c r="T22" s="28" t="str"/>
-      <c r="U22" s="28" t="str"/>
-      <c r="V22" s="28" t="str"/>
-      <c r="W22" s="28" t="str"/>
-      <c r="X22" s="28" t="str"/>
-      <c r="Y22" s="28" t="str"/>
-      <c r="Z22" s="28" t="str"/>
-      <c r="AA22" s="28" t="str"/>
-      <c r="AB22" s="28" t="inlineStr">
+      <c r="S22" s="40" t="str"/>
+      <c r="T22" s="40" t="str"/>
+      <c r="U22" s="40" t="str"/>
+      <c r="V22" s="40" t="str"/>
+      <c r="W22" s="40" t="str"/>
+      <c r="X22" s="40" t="str"/>
+      <c r="Y22" s="40" t="str"/>
+      <c r="Z22" s="40" t="str"/>
+      <c r="AA22" s="40" t="str"/>
+      <c r="AB22" s="40" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC22" s="28" t="inlineStr">
+      <c r="AC22" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD22" s="28" t="str"/>
-      <c r="AE22" s="28" t="inlineStr">
+      <c r="AD22" s="40" t="str"/>
+      <c r="AE22" s="40" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF22" s="28" t="str"/>
-      <c r="AG22" s="28" t="inlineStr">
+      <c r="AF22" s="40" t="str"/>
+      <c r="AG22" s="40" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH22" s="28" t="inlineStr">
+      <c r="AH22" s="40" t="inlineStr">
         <is>
           <t>管釣掛け型巻き：1.6g Spoon 和 Crankbait 是常用主軸，張りを活かして掛けに行く；Twitching Plug 作為操作系 plug 補充。</t>
         </is>
       </c>
-      <c r="AI22" s="28" t="inlineStr">
+      <c r="AI22" s="40" t="inlineStr">
         <is>
           <t>1.6g Spoon / Crankbait / Twitching Plug</t>
         </is>
       </c>
-      <c r="AJ22" s="28" t="str"/>
-      <c r="AK22" s="28" t="str"/>
-      <c r="AL22" s="28" t="inlineStr">
+      <c r="AJ22" s="40" t="str"/>
+      <c r="AK22" s="40" t="str"/>
+      <c r="AL22" s="40" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM22" s="28" t="inlineStr">
+      <c r="AM22" s="40" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 標準放流後節奏 / spoon-crank 巻き</t>
         </is>
       </c>
-      <c r="AN22" s="28" t="inlineStr">
+      <c r="AN22" s="40" t="inlineStr">
         <is>
           <t>1.6g Spoon 與 Crankbait 的掛け型巻き竿</t>
         </is>
       </c>
-      <c r="AO22" s="28" t="inlineStr">
+      <c r="AO22" s="40" t="inlineStr">
         <is>
           <t>1.6g 前後 Spoon、Crankbait 平收時能主動掛けに行く，張りを活かして操作系 plug 也能處理；適合 ester line 主流配置。</t>
         </is>
       </c>
-      <c r="AP22" s="28" t="inlineStr">
+      <c r="AP22" s="40" t="inlineStr">
         <is>
           <t>エリアトラウトでは一般的となる1.6g前後のスプーンやクランクなどのプラグといった巻きの釣りに幅広く対応するモデル。バイトを掛けていくスタイルのロッドとなっており、張りを活かした操作系のプラグなどにも対応。主流となりつつあるエステルラインに対応したガイドセッティング。</t>
         </is>
       </c>
-      <c r="AQ22" s="28" t="str"/>
-      <c r="AR22" s="28" t="str"/>
+      <c r="AQ22" s="40" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / O.S.S / チタンフレームトルザイトリングガイド / チタンフレームSiCトップガイド / スピゴットフェルール（印籠継） / オリジナルシート / エステルライン対応ガイドセッティング</t>
+        </is>
+      </c>
+      <c r="AR22" s="40" t="str"/>
+      <c r="AS22" s="40" t="str"/>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>ORD10021</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="40" t="inlineStr">
         <is>
           <t>26GBELPS-612UL-T</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="40" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="40" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="H23" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I23" s="28" t="inlineStr">
+      <c r="I23" s="40" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J23" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K23" s="28" t="inlineStr">
+      <c r="K23" s="40" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L23" s="28" t="inlineStr">
+      <c r="L23" s="40" t="inlineStr">
         <is>
           <t>0.6-5</t>
         </is>
       </c>
-      <c r="M23" s="28" t="inlineStr">
+      <c r="M23" s="40" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N23" s="28" t="str"/>
-      <c r="O23" s="28" t="str"/>
-      <c r="P23" s="28" t="inlineStr">
+      <c r="N23" s="40" t="str"/>
+      <c r="O23" s="40" t="str"/>
+      <c r="P23" s="40" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q23" s="28" t="str"/>
-      <c r="R23" s="28" t="inlineStr">
+      <c r="Q23" s="40" t="str"/>
+      <c r="R23" s="40" t="inlineStr">
         <is>
           <t>56,000</t>
         </is>
       </c>
-      <c r="S23" s="28" t="str"/>
-      <c r="T23" s="28" t="str"/>
-      <c r="U23" s="28" t="str"/>
-      <c r="V23" s="28" t="str"/>
-      <c r="W23" s="28" t="str"/>
-      <c r="X23" s="28" t="str"/>
-      <c r="Y23" s="28" t="str"/>
-      <c r="Z23" s="28" t="str"/>
-      <c r="AA23" s="28" t="str"/>
-      <c r="AB23" s="28" t="inlineStr">
+      <c r="S23" s="40" t="str"/>
+      <c r="T23" s="40" t="str"/>
+      <c r="U23" s="40" t="str"/>
+      <c r="V23" s="40" t="str"/>
+      <c r="W23" s="40" t="str"/>
+      <c r="X23" s="40" t="str"/>
+      <c r="Y23" s="40" t="str"/>
+      <c r="Z23" s="40" t="str"/>
+      <c r="AA23" s="40" t="str"/>
+      <c r="AB23" s="40" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC23" s="28" t="inlineStr">
+      <c r="AC23" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD23" s="28" t="str"/>
-      <c r="AE23" s="28" t="inlineStr">
+      <c r="AD23" s="40" t="str"/>
+      <c r="AE23" s="40" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF23" s="28" t="str"/>
-      <c r="AG23" s="28" t="inlineStr">
+      <c r="AF23" s="40" t="str"/>
+      <c r="AG23" s="40" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH23" s="28" t="inlineStr">
+      <c r="AH23" s="40" t="inlineStr">
         <is>
           <t>管釣放流 / 大型 plug：Heavy Spoon、Full-size Crankbait 和 Minnow Twitching 負荷更高，出線和補刺要支撐大型 trout。</t>
         </is>
       </c>
-      <c r="AI23" s="28" t="inlineStr">
+      <c r="AI23" s="40" t="inlineStr">
         <is>
           <t>Heavy Spoon / Full-size Crankbait / Minnow Twitching</t>
         </is>
       </c>
-      <c r="AJ23" s="28" t="str"/>
-      <c r="AK23" s="28" t="str"/>
-      <c r="AL23" s="28" t="inlineStr">
+      <c r="AJ23" s="40" t="str"/>
+      <c r="AK23" s="40" t="str"/>
+      <c r="AL23" s="40" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM23" s="28" t="inlineStr">
+      <c r="AM23" s="40" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 放流狩り / 大型 plug 與色物</t>
         </is>
       </c>
-      <c r="AN23" s="28" t="inlineStr">
+      <c r="AN23" s="40" t="inlineStr">
         <is>
           <t>Heavy Spoon、Full-size Crank、Minnow Twitching 攻擊型</t>
         </is>
       </c>
-      <c r="AO23" s="28" t="inlineStr">
+      <c r="AO23" s="40" t="inlineStr">
         <is>
           <t>重め Spoon 和 Full-size Crank 用於放流魚快速搜索，Fast taper 可做 Minnow Twitching；bat power 對大型 trout 和色物更安心。</t>
         </is>
       </c>
-      <c r="AP23" s="28" t="inlineStr">
+      <c r="AP23" s="40" t="inlineStr">
         <is>
           <t>放流狩りなどで使用する重めのスプーンや、フルサイズクランクなどの大型プラグの使用を想定したモデル。ファーストテーパーなアクションはミノーのトゥイッチングにも対応。バットパワーがあるので色物など大型狙いにもおすすめ。</t>
         </is>
       </c>
-      <c r="AQ23" s="28" t="str"/>
-      <c r="AR23" s="28" t="str"/>
+      <c r="AQ23" s="40" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / トレカ®M40X / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / O.S.S / チタンフレームトルザイトリングガイド / チタンフレームSiCトップガイド / スピゴットフェルール（印籠継） / オリジナルシート / エステルライン対応ガイドセッティング</t>
+        </is>
+      </c>
+      <c r="AR23" s="40" t="str"/>
+      <c r="AS23" s="40" t="str"/>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>ORD10022</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="40" t="inlineStr">
         <is>
           <t>26GBELPS-642L-T</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="40" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="40" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
+      <c r="I24" s="40" t="inlineStr">
         <is>
           <t>98.8</t>
         </is>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J24" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K24" s="28" t="inlineStr">
+      <c r="K24" s="40" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="L24" s="28" t="inlineStr">
+      <c r="L24" s="40" t="inlineStr">
         <is>
           <t>1-7</t>
         </is>
       </c>
-      <c r="M24" s="28" t="inlineStr">
+      <c r="M24" s="40" t="inlineStr">
         <is>
           <t>MAX5</t>
         </is>
       </c>
-      <c r="N24" s="28" t="str"/>
-      <c r="O24" s="28" t="str"/>
-      <c r="P24" s="28" t="inlineStr">
+      <c r="N24" s="40" t="str"/>
+      <c r="O24" s="40" t="str"/>
+      <c r="P24" s="40" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q24" s="28" t="str"/>
-      <c r="R24" s="28" t="inlineStr">
+      <c r="Q24" s="40" t="str"/>
+      <c r="R24" s="40" t="inlineStr">
         <is>
           <t>57,000</t>
         </is>
       </c>
-      <c r="S24" s="28" t="str"/>
-      <c r="T24" s="28" t="str"/>
-      <c r="U24" s="28" t="str"/>
-      <c r="V24" s="28" t="str"/>
-      <c r="W24" s="28" t="str"/>
-      <c r="X24" s="28" t="str"/>
-      <c r="Y24" s="28" t="str"/>
-      <c r="Z24" s="28" t="str"/>
-      <c r="AA24" s="28" t="str"/>
-      <c r="AB24" s="28" t="inlineStr">
+      <c r="S24" s="40" t="str"/>
+      <c r="T24" s="40" t="str"/>
+      <c r="U24" s="40" t="str"/>
+      <c r="V24" s="40" t="str"/>
+      <c r="W24" s="40" t="str"/>
+      <c r="X24" s="40" t="str"/>
+      <c r="Y24" s="40" t="str"/>
+      <c r="Z24" s="40" t="str"/>
+      <c r="AA24" s="40" t="str"/>
+      <c r="AB24" s="40" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC24" s="28" t="inlineStr">
+      <c r="AC24" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD24" s="28" t="str"/>
-      <c r="AE24" s="28" t="inlineStr">
+      <c r="AD24" s="40" t="str"/>
+      <c r="AE24" s="40" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF24" s="28" t="str"/>
-      <c r="AG24" s="28" t="inlineStr">
+      <c r="AF24" s="40" t="str"/>
+      <c r="AG24" s="40" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH24" s="28" t="inlineStr">
+      <c r="AH24" s="40" t="inlineStr">
         <is>
           <t>管釣大型 trout：Large Plug、Full-size Spoon 和 Full-size Crankbait 為主，較粗線徑與高負荷 lure 出線更穩。</t>
         </is>
       </c>
-      <c r="AI24" s="28" t="inlineStr">
+      <c r="AI24" s="40" t="inlineStr">
         <is>
           <t>Large Plug / Full-size Spoon / Full-size Crankbait</t>
         </is>
       </c>
-      <c r="AJ24" s="28" t="str"/>
-      <c r="AK24" s="28" t="str"/>
-      <c r="AL24" s="28" t="inlineStr">
+      <c r="AJ24" s="40" t="str"/>
+      <c r="AK24" s="40" t="str"/>
+      <c r="AL24" s="40" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM24" s="28" t="inlineStr">
+      <c r="AM24" s="40" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 大規模 pond / 超大型 trout</t>
         </is>
       </c>
-      <c r="AN24" s="28" t="inlineStr">
+      <c r="AN24" s="40" t="inlineStr">
         <is>
           <t>Large Plug、Full-size Spoon 的大型魚 power 型</t>
         </is>
       </c>
-      <c r="AO24" s="28" t="inlineStr">
+      <c r="AO24" s="40" t="inlineStr">
         <is>
           <t>L power 對大型 plug、Full-size Spoon 負荷更穩，適合大規模 pond 搜索和超大型 trout 控魚；不是 micro lure 精細路線。</t>
         </is>
       </c>
-      <c r="AP24" s="28" t="inlineStr">
+      <c r="AP24" s="40" t="inlineStr">
         <is>
           <t>比較的大規模なポンドで大型のプラグやスプーンなどを使用し、大型のトラウトを狙うことを想定したモデル。シリーズ内で最もパワーがあるので超大型といわれるサイズとも渡り合えるロッド。</t>
         </is>
       </c>
-      <c r="AQ24" s="28" t="str"/>
-      <c r="AR24" s="28" t="str"/>
+      <c r="AQ24" s="40" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / トレカ®M40X / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / O.S.S / チタンフレームトルザイトリングガイド / チタンフレームSiCトップガイド / スピゴットフェルール（印籠継） / オリジナルシート / エステルライン対応ガイドセッティング</t>
+        </is>
+      </c>
+      <c r="AR24" s="40" t="str"/>
+      <c r="AS24" s="40" t="str"/>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>ORD10023</t>
         </is>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>OR1003</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="40" t="inlineStr">
         <is>
           <t>26GBELPS-672SUL-T</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="40" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="40" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H25" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I25" s="28" t="inlineStr">
+      <c r="I25" s="40" t="inlineStr">
         <is>
           <t>102.6</t>
         </is>
       </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J25" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K25" s="28" t="inlineStr">
+      <c r="K25" s="40" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L25" s="28" t="inlineStr">
+      <c r="L25" s="40" t="inlineStr">
         <is>
           <t>0.5-4</t>
         </is>
       </c>
-      <c r="M25" s="28" t="inlineStr">
+      <c r="M25" s="40" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N25" s="28" t="str"/>
-      <c r="O25" s="28" t="str"/>
-      <c r="P25" s="28" t="inlineStr">
+      <c r="N25" s="40" t="str"/>
+      <c r="O25" s="40" t="str"/>
+      <c r="P25" s="40" t="inlineStr">
         <is>
           <t>Olympic original reel seat</t>
         </is>
       </c>
-      <c r="Q25" s="28" t="str"/>
-      <c r="R25" s="28" t="inlineStr">
+      <c r="Q25" s="40" t="str"/>
+      <c r="R25" s="40" t="inlineStr">
         <is>
           <t>58,000</t>
         </is>
       </c>
-      <c r="S25" s="28" t="str"/>
-      <c r="T25" s="28" t="str"/>
-      <c r="U25" s="28" t="str"/>
-      <c r="V25" s="28" t="str"/>
-      <c r="W25" s="28" t="str"/>
-      <c r="X25" s="28" t="str"/>
-      <c r="Y25" s="28" t="str"/>
-      <c r="Z25" s="28" t="str"/>
-      <c r="AA25" s="28" t="str"/>
-      <c r="AB25" s="28" t="inlineStr">
+      <c r="S25" s="40" t="str"/>
+      <c r="T25" s="40" t="str"/>
+      <c r="U25" s="40" t="str"/>
+      <c r="V25" s="40" t="str"/>
+      <c r="W25" s="40" t="str"/>
+      <c r="X25" s="40" t="str"/>
+      <c r="Y25" s="40" t="str"/>
+      <c r="Z25" s="40" t="str"/>
+      <c r="AA25" s="40" t="str"/>
+      <c r="AB25" s="40" t="inlineStr">
         <is>
           <t>印籠継</t>
         </is>
       </c>
-      <c r="AC25" s="28" t="inlineStr">
+      <c r="AC25" s="40" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD25" s="28" t="str"/>
-      <c r="AE25" s="28" t="inlineStr">
+      <c r="AD25" s="40" t="str"/>
+      <c r="AE25" s="40" t="inlineStr">
         <is>
           <t>High grade cork / maple wood</t>
         </is>
       </c>
-      <c r="AF25" s="28" t="str"/>
-      <c r="AG25" s="28" t="inlineStr">
+      <c r="AF25" s="40" t="str"/>
+      <c r="AG25" s="40" t="inlineStr">
         <is>
           <t>チタンフレームトルザイトリングガイド：軽量化と感度を重視した導環構成</t>
         </is>
       </c>
-      <c r="AH25" s="28" t="inlineStr">
+      <c r="AH25" s="40" t="inlineStr">
         <is>
           <t>管釣遠投：Long Cast Spoon、Crankbait 和 Minnow 用於大池沖目搜索，長竿出線與遠距離控魚是重點。</t>
         </is>
       </c>
-      <c r="AI25" s="28" t="inlineStr">
+      <c r="AI25" s="40" t="inlineStr">
         <is>
           <t>Long Cast Spoon / Long Cast Crankbait / Minnow</t>
         </is>
       </c>
-      <c r="AJ25" s="28" t="str"/>
-      <c r="AK25" s="28" t="str"/>
-      <c r="AL25" s="28" t="inlineStr">
+      <c r="AJ25" s="40" t="str"/>
+      <c r="AK25" s="40" t="str"/>
+      <c r="AL25" s="40" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM25" s="28" t="inlineStr">
+      <c r="AM25" s="40" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 大池沖目遠投 / 未被打擾魚群</t>
         </is>
       </c>
-      <c r="AN25" s="28" t="inlineStr">
+      <c r="AN25" s="40" t="inlineStr">
         <is>
           <t>Long Cast Spoon / Crank 遠投搜索型</t>
         </is>
       </c>
-      <c r="AO25" s="28" t="inlineStr">
+      <c r="AO25" s="40" t="inlineStr">
         <is>
           <t>6'7" 長度把 Spoon、Crankbait 投到大池沖目，SUL 調性在遠距離中魚後更不易脫鉤；適合找未被釣壓干擾的魚。</t>
         </is>
       </c>
-      <c r="AP25" s="28" t="inlineStr">
+      <c r="AP25" s="40" t="inlineStr">
         <is>
           <t>大規模ポンドなどで狙われていない沖にいる大型を遠投して釣っていくことを想定したモデル。様々なルアーを扱えるアクションに設定。また、その6’7”というレングスを活かし、バラシを抑えて寄せてくることが可能。</t>
         </is>
       </c>
-      <c r="AQ25" s="28" t="str"/>
-      <c r="AR25" s="28" t="str"/>
+      <c r="AQ25" s="40" t="inlineStr">
+        <is>
+          <t>トレカ®T1100G / トレカ®M40X / ナノアロイ® / スーパークワトログラファイトクロスLV / G-MAPS製法 / O.S.S / チタンフレームトルザイトリングガイド / チタンフレームSiCトップガイド / スピゴットフェルール（印籠継） / オリジナルシート / エステルライン対応ガイドセッティング</t>
+        </is>
+      </c>
+      <c r="AR25" s="40" t="str"/>
+      <c r="AS25" s="40" t="str"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>ORD10024</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="41" t="inlineStr">
         <is>
           <t>24GBELUS-582XUL-T</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="41" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F26" s="29" t="inlineStr">
+      <c r="F26" s="41" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="G26" s="29" t="inlineStr">
+      <c r="G26" s="41" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="H26" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I26" s="29" t="inlineStr">
+      <c r="I26" s="41" t="inlineStr">
         <is>
           <t>89.5</t>
         </is>
       </c>
-      <c r="J26" s="29" t="inlineStr">
+      <c r="J26" s="41" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="K26" s="29" t="inlineStr">
+      <c r="K26" s="41" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="L26" s="29" t="inlineStr">
+      <c r="L26" s="41" t="inlineStr">
         <is>
           <t>0.4-3.5</t>
         </is>
       </c>
-      <c r="M26" s="29" t="inlineStr">
+      <c r="M26" s="41" t="inlineStr">
         <is>
           <t>MAX3</t>
         </is>
       </c>
-      <c r="N26" s="29" t="str"/>
-      <c r="O26" s="29" t="str"/>
-      <c r="P26" s="29" t="inlineStr">
+      <c r="N26" s="41" t="str"/>
+      <c r="O26" s="41" t="str"/>
+      <c r="P26" s="41" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q26" s="29" t="str"/>
-      <c r="R26" s="29" t="inlineStr">
+      <c r="Q26" s="41" t="str"/>
+      <c r="R26" s="41" t="inlineStr">
         <is>
           <t>23,500</t>
         </is>
       </c>
-      <c r="S26" s="29" t="str"/>
-      <c r="T26" s="29" t="str"/>
-      <c r="U26" s="29" t="str"/>
-      <c r="V26" s="29" t="str"/>
-      <c r="W26" s="29" t="str"/>
-      <c r="X26" s="29" t="str"/>
-      <c r="Y26" s="29" t="str"/>
-      <c r="Z26" s="29" t="str"/>
-      <c r="AA26" s="29" t="str"/>
-      <c r="AB26" s="29" t="inlineStr">
+      <c r="S26" s="41" t="str"/>
+      <c r="T26" s="41" t="str"/>
+      <c r="U26" s="41" t="str"/>
+      <c r="V26" s="41" t="str"/>
+      <c r="W26" s="41" t="str"/>
+      <c r="X26" s="41" t="str"/>
+      <c r="Y26" s="41" t="str"/>
+      <c r="Z26" s="41" t="str"/>
+      <c r="AA26" s="41" t="str"/>
+      <c r="AB26" s="41" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC26" s="29" t="inlineStr">
+      <c r="AC26" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD26" s="29" t="str"/>
-      <c r="AE26" s="29" t="str"/>
-      <c r="AF26" s="29" t="str"/>
-      <c r="AG26" s="29" t="inlineStr">
+      <c r="AD26" s="41" t="str"/>
+      <c r="AE26" s="41" t="str"/>
+      <c r="AF26" s="41" t="str"/>
+      <c r="AG26" s="41" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH26" s="29" t="inlineStr">
+      <c r="AH26" s="41" t="inlineStr">
         <is>
           <t>管釣 micro 巻き：Micro Spoon 和 Micro Crankbait 一定速 retrieve 是核心，XUL tubular 保持低負荷出線，柔軟性用來承接 short bite。</t>
         </is>
       </c>
-      <c r="AI26" s="29" t="inlineStr">
+      <c r="AI26" s="41" t="inlineStr">
         <is>
           <t>Micro Spoon / Micro Crankbait</t>
         </is>
       </c>
-      <c r="AJ26" s="29" t="str"/>
-      <c r="AK26" s="29" t="str"/>
-      <c r="AL26" s="29" t="inlineStr">
+      <c r="AJ26" s="41" t="str"/>
+      <c r="AK26" s="41" t="str"/>
+      <c r="AL26" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM26" s="29" t="inlineStr">
+      <c r="AM26" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / micro spoon-crank 定速巻き</t>
         </is>
       </c>
-      <c r="AN26" s="29" t="inlineStr">
+      <c r="AN26" s="41" t="inlineStr">
         <is>
           <t>Micro Spoon、Micro Crankbait short-bite 對應型</t>
         </is>
       </c>
-      <c r="AO26" s="29" t="inlineStr">
+      <c r="AO26" s="41" t="inlineStr">
         <is>
           <t>定速 retrieve micro lure 時，XUL tubular 和柔軟性降低彈口；OP-01 碳纖 reel seat 提升短咬口感知。</t>
         </is>
       </c>
-      <c r="AP26" s="29" t="inlineStr">
+      <c r="AP26" s="41" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉 マイクロスプーンやマイクロクランクを一定スピードでリトリーブするような巻きの釣りを主体としたモデル。ショートバイトを弾かず乗せることができる柔軟性を持ちながらもオリジナルカーボンリールシートによって高感度化も実現しました。</t>
         </is>
       </c>
-      <c r="AQ26" s="29" t="inlineStr">
+      <c r="AQ26" s="41" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-Sリングガイド / スリップオーバーフェルール（逆並継） / オリジナルカーボンリールシート OP-01</t>
+        </is>
+      </c>
+      <c r="AR26" s="41" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉</t>
         </is>
       </c>
-      <c r="AR26" s="29" t="str"/>
+      <c r="AS26" s="41" t="str"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>ORD10025</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="41" t="inlineStr">
         <is>
           <t>25GBELUS-612SUL-S</t>
         </is>
       </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="E27" s="41" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F27" s="29" t="inlineStr">
+      <c r="F27" s="41" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="G27" s="29" t="inlineStr">
+      <c r="G27" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H27" s="29" t="inlineStr">
+      <c r="H27" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I27" s="29" t="inlineStr">
+      <c r="I27" s="41" t="inlineStr">
         <is>
           <t>95.0</t>
         </is>
       </c>
-      <c r="J27" s="29" t="inlineStr">
+      <c r="J27" s="41" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="K27" s="29" t="inlineStr">
+      <c r="K27" s="41" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="L27" s="29" t="inlineStr">
+      <c r="L27" s="41" t="inlineStr">
         <is>
           <t>0.4-4.0</t>
         </is>
       </c>
-      <c r="M27" s="29" t="inlineStr">
+      <c r="M27" s="41" t="inlineStr">
         <is>
           <t>MAX 4</t>
         </is>
       </c>
-      <c r="N27" s="29" t="str"/>
-      <c r="O27" s="29" t="str"/>
-      <c r="P27" s="29" t="inlineStr">
+      <c r="N27" s="41" t="str"/>
+      <c r="O27" s="41" t="str"/>
+      <c r="P27" s="41" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q27" s="29" t="str"/>
-      <c r="R27" s="29" t="inlineStr">
+      <c r="Q27" s="41" t="str"/>
+      <c r="R27" s="41" t="inlineStr">
         <is>
           <t>22,500</t>
         </is>
       </c>
-      <c r="S27" s="29" t="str"/>
-      <c r="T27" s="29" t="str"/>
-      <c r="U27" s="29" t="str"/>
-      <c r="V27" s="29" t="str"/>
-      <c r="W27" s="29" t="str"/>
-      <c r="X27" s="29" t="str"/>
-      <c r="Y27" s="29" t="str"/>
-      <c r="Z27" s="29" t="str"/>
-      <c r="AA27" s="29" t="str"/>
-      <c r="AB27" s="29" t="inlineStr">
+      <c r="S27" s="41" t="str"/>
+      <c r="T27" s="41" t="str"/>
+      <c r="U27" s="41" t="str"/>
+      <c r="V27" s="41" t="str"/>
+      <c r="W27" s="41" t="str"/>
+      <c r="X27" s="41" t="str"/>
+      <c r="Y27" s="41" t="str"/>
+      <c r="Z27" s="41" t="str"/>
+      <c r="AA27" s="41" t="str"/>
+      <c r="AB27" s="41" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC27" s="29" t="inlineStr">
+      <c r="AC27" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD27" s="29" t="str"/>
-      <c r="AE27" s="29" t="str"/>
-      <c r="AF27" s="29" t="str"/>
-      <c r="AG27" s="29" t="inlineStr">
+      <c r="AD27" s="41" t="str"/>
+      <c r="AE27" s="41" t="str"/>
+      <c r="AF27" s="41" t="str"/>
+      <c r="AG27" s="41" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH27" s="29" t="inlineStr">
+      <c r="AH27" s="41" t="inlineStr">
         <is>
           <t>管釣 slow retrieve：Slow Spoon 與 Micro Crankbait 是主軸，solid tip 讓 short bite 時 hook 留在口內，掛けた後由 belly 順暢吸收魚的反撲。</t>
         </is>
       </c>
-      <c r="AI27" s="29" t="inlineStr">
+      <c r="AI27" s="41" t="inlineStr">
         <is>
           <t>Slow Retrieve Spoon / Micro Crankbait / Spoon</t>
         </is>
       </c>
-      <c r="AJ27" s="29" t="str"/>
-      <c r="AK27" s="29" t="str"/>
-      <c r="AL27" s="29" t="inlineStr">
+      <c r="AJ27" s="41" t="str"/>
+      <c r="AK27" s="41" t="str"/>
+      <c r="AL27" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM27" s="29" t="inlineStr">
+      <c r="AM27" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / slow retrieve / 高壓短咬</t>
         </is>
       </c>
-      <c r="AN27" s="29" t="inlineStr">
+      <c r="AN27" s="41" t="inlineStr">
         <is>
           <t>Slow Spoon 與 Micro Crank solid tip 乗せ掛け型</t>
         </is>
       </c>
-      <c r="AO27" s="29" t="inlineStr">
+      <c r="AO27" s="41" t="inlineStr">
         <is>
           <t>Slow Spoon、Micro Crankbait 是主軸，solid tip 讓高壓短咬時 hook 留在口內，掛けた後 belly 順暢彎曲降低脫鉤。</t>
         </is>
       </c>
-      <c r="AP27" s="29" t="inlineStr">
+      <c r="AP27" s="41" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉 スプーニングとマイクロクランクのスローリトリーブがメインとなるモデル。繊細なソリッドティップを採用することで、ショートバイトが多発するシビアな状況下でもフックを口に残し、掛けた後はスムースに曲がりこむベリーで魚をバラさずにキャッチすることが可能です。</t>
         </is>
       </c>
-      <c r="AQ27" s="29" t="inlineStr">
+      <c r="AQ27" s="41" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-Sリングガイド / スリップオーバーフェルール（逆並継） / オリジナルカーボンリールシート OP-01 / ソリッドティップ</t>
+        </is>
+      </c>
+      <c r="AR27" s="41" t="inlineStr">
         <is>
           <t>〈ソリッドティップ〉</t>
         </is>
       </c>
-      <c r="AR27" s="29" t="str"/>
+      <c r="AS27" s="41" t="str"/>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="41" t="inlineStr">
         <is>
           <t>ORD10026</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="41" t="inlineStr">
         <is>
           <t>24GBELUS-622SUL-T</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="E28" s="41" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F28" s="29" t="inlineStr">
+      <c r="F28" s="41" t="inlineStr">
         <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="G28" s="29" t="inlineStr">
+      <c r="G28" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H28" s="29" t="inlineStr">
+      <c r="H28" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I28" s="29" t="inlineStr">
+      <c r="I28" s="41" t="inlineStr">
         <is>
           <t>97.0</t>
         </is>
       </c>
-      <c r="J28" s="29" t="inlineStr">
+      <c r="J28" s="41" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="K28" s="29" t="inlineStr">
+      <c r="K28" s="41" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="L28" s="29" t="inlineStr">
+      <c r="L28" s="41" t="inlineStr">
         <is>
           <t>0.5-5</t>
         </is>
       </c>
-      <c r="M28" s="29" t="inlineStr">
+      <c r="M28" s="41" t="inlineStr">
         <is>
           <t>MAX4</t>
         </is>
       </c>
-      <c r="N28" s="29" t="str"/>
-      <c r="O28" s="29" t="str"/>
-      <c r="P28" s="29" t="inlineStr">
+      <c r="N28" s="41" t="str"/>
+      <c r="O28" s="41" t="str"/>
+      <c r="P28" s="41" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q28" s="29" t="str"/>
-      <c r="R28" s="29" t="inlineStr">
+      <c r="Q28" s="41" t="str"/>
+      <c r="R28" s="41" t="inlineStr">
         <is>
           <t>24,000</t>
         </is>
       </c>
-      <c r="S28" s="29" t="str"/>
-      <c r="T28" s="29" t="str"/>
-      <c r="U28" s="29" t="str"/>
-      <c r="V28" s="29" t="str"/>
-      <c r="W28" s="29" t="str"/>
-      <c r="X28" s="29" t="str"/>
-      <c r="Y28" s="29" t="str"/>
-      <c r="Z28" s="29" t="str"/>
-      <c r="AA28" s="29" t="str"/>
-      <c r="AB28" s="29" t="inlineStr">
+      <c r="S28" s="41" t="str"/>
+      <c r="T28" s="41" t="str"/>
+      <c r="U28" s="41" t="str"/>
+      <c r="V28" s="41" t="str"/>
+      <c r="W28" s="41" t="str"/>
+      <c r="X28" s="41" t="str"/>
+      <c r="Y28" s="41" t="str"/>
+      <c r="Z28" s="41" t="str"/>
+      <c r="AA28" s="41" t="str"/>
+      <c r="AB28" s="41" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC28" s="29" t="inlineStr">
+      <c r="AC28" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD28" s="29" t="str"/>
-      <c r="AE28" s="29" t="str"/>
-      <c r="AF28" s="29" t="str"/>
-      <c r="AG28" s="29" t="inlineStr">
+      <c r="AD28" s="41" t="str"/>
+      <c r="AE28" s="41" t="str"/>
+      <c r="AF28" s="41" t="str"/>
+      <c r="AG28" s="41" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH28" s="29" t="inlineStr">
+      <c r="AH28" s="41" t="inlineStr">
         <is>
           <t>管釣操作系 plug：Vibration、Minnow Twitching 和 Bottom Bump Plug 的抖動、跳底與停頓更清楚，也能切回 spooning。</t>
         </is>
       </c>
-      <c r="AI28" s="29" t="inlineStr">
+      <c r="AI28" s="41" t="inlineStr">
         <is>
           <t>Vibration / Minnow Twitching / Spoon / Bottom Bump Plug</t>
         </is>
       </c>
-      <c r="AJ28" s="29" t="str"/>
-      <c r="AK28" s="29" t="str"/>
-      <c r="AL28" s="29" t="inlineStr">
+      <c r="AJ28" s="41" t="str"/>
+      <c r="AK28" s="41" t="str"/>
+      <c r="AL28" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM28" s="29" t="inlineStr">
+      <c r="AM28" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / bottom-twitch 操作系 plug / spooning 兼用</t>
         </is>
       </c>
-      <c r="AN28" s="29" t="inlineStr">
+      <c r="AN28" s="41" t="inlineStr">
         <is>
           <t>Vibration、Minnow Twitching、Bottom Bump 操作型</t>
         </is>
       </c>
-      <c r="AO28" s="29" t="inlineStr">
+      <c r="AO28" s="41" t="inlineStr">
         <is>
           <t>Fast-ish action 讓 Vibration、Minnow Twitching 和 Bottom Bump 更清楚，遇到穩定魚情可切回 Spoon；不是單純慢巻き型。</t>
         </is>
       </c>
-      <c r="AP28" s="29" t="inlineStr">
+      <c r="AP28" s="41" t="inlineStr">
         <is>
           <t>ファーストよりのアクションでボトムバンプやトゥイッチングなどルアーを操作しやすいモデル。バイブレーションやミノーなどのプラグ全般を得意としていますが、スプーニングにも高次元で対応します。</t>
         </is>
       </c>
-      <c r="AQ28" s="29" t="str"/>
-      <c r="AR28" s="29" t="str"/>
+      <c r="AQ28" s="41" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-Sリングガイド / スリップオーバーフェルール（逆並継） / オリジナルカーボンリールシート OP-01</t>
+        </is>
+      </c>
+      <c r="AR28" s="41" t="str"/>
+      <c r="AS28" s="41" t="str"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>ORD10027</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="41" t="inlineStr">
         <is>
           <t>24GBELUS-652UL-T</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E29" s="41" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F29" s="29" t="inlineStr">
+      <c r="F29" s="41" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="G29" s="29" t="inlineStr">
+      <c r="G29" s="41" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H29" s="29" t="inlineStr">
+      <c r="H29" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I29" s="29" t="inlineStr">
+      <c r="I29" s="41" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="J29" s="29" t="inlineStr">
+      <c r="J29" s="41" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="K29" s="29" t="inlineStr">
+      <c r="K29" s="41" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="L29" s="29" t="inlineStr">
+      <c r="L29" s="41" t="inlineStr">
         <is>
           <t>0.6-7</t>
         </is>
       </c>
-      <c r="M29" s="29" t="inlineStr">
+      <c r="M29" s="41" t="inlineStr">
         <is>
           <t>MAX5</t>
         </is>
       </c>
-      <c r="N29" s="29" t="str"/>
-      <c r="O29" s="29" t="str"/>
-      <c r="P29" s="29" t="inlineStr">
+      <c r="N29" s="41" t="str"/>
+      <c r="O29" s="41" t="str"/>
+      <c r="P29" s="41" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q29" s="29" t="str"/>
-      <c r="R29" s="29" t="inlineStr">
+      <c r="Q29" s="41" t="str"/>
+      <c r="R29" s="41" t="inlineStr">
         <is>
           <t>24,500</t>
         </is>
       </c>
-      <c r="S29" s="29" t="str"/>
-      <c r="T29" s="29" t="str"/>
-      <c r="U29" s="29" t="str"/>
-      <c r="V29" s="29" t="str"/>
-      <c r="W29" s="29" t="str"/>
-      <c r="X29" s="29" t="str"/>
-      <c r="Y29" s="29" t="str"/>
-      <c r="Z29" s="29" t="str"/>
-      <c r="AA29" s="29" t="str"/>
-      <c r="AB29" s="29" t="inlineStr">
+      <c r="S29" s="41" t="str"/>
+      <c r="T29" s="41" t="str"/>
+      <c r="U29" s="41" t="str"/>
+      <c r="V29" s="41" t="str"/>
+      <c r="W29" s="41" t="str"/>
+      <c r="X29" s="41" t="str"/>
+      <c r="Y29" s="41" t="str"/>
+      <c r="Z29" s="41" t="str"/>
+      <c r="AA29" s="41" t="str"/>
+      <c r="AB29" s="41" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC29" s="29" t="inlineStr">
+      <c r="AC29" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD29" s="29" t="str"/>
-      <c r="AE29" s="29" t="str"/>
-      <c r="AF29" s="29" t="str"/>
-      <c r="AG29" s="29" t="inlineStr">
+      <c r="AD29" s="41" t="str"/>
+      <c r="AE29" s="41" t="str"/>
+      <c r="AF29" s="41" t="str"/>
+      <c r="AG29" s="41" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH29" s="29" t="inlineStr">
+      <c r="AH29" s="41" t="inlineStr">
         <is>
           <t>管釣遠投 / 大型 trout：Long Cast Crankbait、Spoon 和 Minnow 覆蓋沖目魚群，張りのある blank 支撐遠距離補刺。</t>
         </is>
       </c>
-      <c r="AI29" s="29" t="inlineStr">
+      <c r="AI29" s="41" t="inlineStr">
         <is>
           <t>Long Cast Crankbait / Long Cast Spoon / Minnow</t>
         </is>
       </c>
-      <c r="AJ29" s="29" t="str"/>
-      <c r="AK29" s="29" t="str"/>
-      <c r="AL29" s="29" t="inlineStr">
+      <c r="AJ29" s="41" t="str"/>
+      <c r="AK29" s="41" t="str"/>
+      <c r="AL29" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM29" s="29" t="inlineStr">
+      <c r="AM29" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 沖目遠投 / 大型 trout</t>
         </is>
       </c>
-      <c r="AN29" s="29" t="inlineStr">
+      <c r="AN29" s="41" t="inlineStr">
         <is>
           <t>Long Cast Crankbait / Spoon 遠投泛用型</t>
         </is>
       </c>
-      <c r="AO29" s="29" t="inlineStr">
+      <c r="AO29" s="41" t="inlineStr">
         <is>
           <t>較長竿身和系列最強 bat power 讓 Long Cast Crankbait、Spoon、Minnow 能覆蓋沖目魚，對大型 trout 補刺和控魚更穩。</t>
         </is>
       </c>
-      <c r="AP29" s="29" t="inlineStr">
+      <c r="AP29" s="41" t="inlineStr">
         <is>
           <t>長めのレングスで、ロングキャストして沖の魚を狙って獲っていくモデル。全体的に張りのあるブランクスでプラグ全般からスプーニングまで幅広く対応。シリーズ中もっともバットパワーがあるので大型トラウト狙いにもおすすめの1本です。</t>
         </is>
       </c>
-      <c r="AQ29" s="29" t="str"/>
-      <c r="AR29" s="29" t="str"/>
+      <c r="AQ29" s="41" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-Sリングガイド / スリップオーバーフェルール（逆並継） / オリジナルカーボンリールシート OP-01</t>
+        </is>
+      </c>
+      <c r="AR29" s="41" t="str"/>
+      <c r="AS29" s="41" t="str"/>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="41" t="inlineStr">
         <is>
           <t>ORD10028</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>OR1004</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" s="41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="41" t="inlineStr">
         <is>
           <t>25GBELUS-682SUL-T</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="41" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="F30" s="41" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="G30" s="29" t="inlineStr">
+      <c r="G30" s="41" t="inlineStr">
         <is>
           <t>Regular-Fast</t>
         </is>
       </c>
-      <c r="H30" s="29" t="inlineStr">
+      <c r="H30" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I30" s="29" t="inlineStr">
+      <c r="I30" s="41" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="J30" s="29" t="inlineStr">
+      <c r="J30" s="41" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="K30" s="29" t="inlineStr">
+      <c r="K30" s="41" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="L30" s="29" t="inlineStr">
+      <c r="L30" s="41" t="inlineStr">
         <is>
           <t>0.5-5.0</t>
         </is>
       </c>
-      <c r="M30" s="29" t="inlineStr">
+      <c r="M30" s="41" t="inlineStr">
         <is>
           <t>MAX 4</t>
         </is>
       </c>
-      <c r="N30" s="29" t="str"/>
-      <c r="O30" s="29" t="str"/>
-      <c r="P30" s="29" t="inlineStr">
+      <c r="N30" s="41" t="str"/>
+      <c r="O30" s="41" t="str"/>
+      <c r="P30" s="41" t="inlineStr">
         <is>
           <t>Olympic OP-01 carbon reel seat</t>
         </is>
       </c>
-      <c r="Q30" s="29" t="str"/>
-      <c r="R30" s="29" t="inlineStr">
+      <c r="Q30" s="41" t="str"/>
+      <c r="R30" s="41" t="inlineStr">
         <is>
           <t>23,000</t>
         </is>
       </c>
-      <c r="S30" s="29" t="str"/>
-      <c r="T30" s="29" t="str"/>
-      <c r="U30" s="29" t="str"/>
-      <c r="V30" s="29" t="str"/>
-      <c r="W30" s="29" t="str"/>
-      <c r="X30" s="29" t="str"/>
-      <c r="Y30" s="29" t="str"/>
-      <c r="Z30" s="29" t="str"/>
-      <c r="AA30" s="29" t="str"/>
-      <c r="AB30" s="29" t="inlineStr">
+      <c r="S30" s="41" t="str"/>
+      <c r="T30" s="41" t="str"/>
+      <c r="U30" s="41" t="str"/>
+      <c r="V30" s="41" t="str"/>
+      <c r="W30" s="41" t="str"/>
+      <c r="X30" s="41" t="str"/>
+      <c r="Y30" s="41" t="str"/>
+      <c r="Z30" s="41" t="str"/>
+      <c r="AA30" s="41" t="str"/>
+      <c r="AB30" s="41" t="inlineStr">
         <is>
           <t>逆並継</t>
         </is>
       </c>
-      <c r="AC30" s="29" t="inlineStr">
+      <c r="AC30" s="41" t="inlineStr">
         <is>
           <t>SPINNING MODEL</t>
         </is>
       </c>
-      <c r="AD30" s="29" t="str"/>
-      <c r="AE30" s="29" t="str"/>
-      <c r="AF30" s="29" t="str"/>
-      <c r="AG30" s="29" t="inlineStr">
+      <c r="AD30" s="41" t="str"/>
+      <c r="AE30" s="41" t="str"/>
+      <c r="AF30" s="41" t="str"/>
+      <c r="AG30" s="41" t="inlineStr">
         <is>
           <t>ステンレスフレーム SiC-S / K ガイド：耐久性とライン抜けを重視した導環構成</t>
         </is>
       </c>
-      <c r="AH30" s="29" t="inlineStr">
+      <c r="AH30" s="41" t="inlineStr">
         <is>
           <t>管釣最長尺遠投：Long Cast Crankbait、Spoon 和 Minnow Twitching 覆蓋大場沖目，回收、操作與控魚距離更清楚。</t>
         </is>
       </c>
-      <c r="AI30" s="29" t="inlineStr">
+      <c r="AI30" s="41" t="inlineStr">
         <is>
           <t>Long Cast Crankbait / Long Cast Spoon / Minnow Twitching</t>
         </is>
       </c>
-      <c r="AJ30" s="29" t="str"/>
-      <c r="AK30" s="29" t="str"/>
-      <c r="AL30" s="29" t="inlineStr">
+      <c r="AJ30" s="41" t="str"/>
+      <c r="AK30" s="41" t="str"/>
+      <c r="AL30" s="41" t="inlineStr">
         <is>
           <t>Area Trout</t>
         </is>
       </c>
-      <c r="AM30" s="29" t="inlineStr">
+      <c r="AM30" s="41" t="inlineStr">
         <is>
           <t>淡水 Area Trout / 廣大場地最遠投 / plug-spoon 操作回收</t>
         </is>
       </c>
-      <c r="AN30" s="29" t="inlineStr">
+      <c r="AN30" s="41" t="inlineStr">
         <is>
           <t>最長尺 Long Cast Crank / Spoon / Minnow Twitching 型</t>
         </is>
       </c>
-      <c r="AO30" s="29" t="inlineStr">
+      <c r="AO30" s="41" t="inlineStr">
         <is>
           <t>6'8" 最長尺用來觸及大場未被打擾的沖目魚，Crankbait、Spoon 和 Minnow Twitching 都能處理，遠距離回收和控魚距離更有優勢。</t>
         </is>
       </c>
-      <c r="AP30" s="29" t="inlineStr">
+      <c r="AP30" s="41" t="inlineStr">
         <is>
           <t>プラグ全般からスプーンなど幅広いルアーのリトリーブや操作系の釣りに高次元に対応。シリーズ最長のレングスで、広大なエリアフィールドにおいて今まで手付かずだった沖にいるスレていない魚をロングキャストで狙うことができるモデル。</t>
         </is>
       </c>
-      <c r="AQ30" s="29" t="str"/>
-      <c r="AR30" s="29" t="str"/>
+      <c r="AQ30" s="41" t="inlineStr">
+        <is>
+          <t>グラファイトクロスLV / ステンレスフレームSiC-Sリングガイド / スリップオーバーフェルール（逆並継） / オリジナルカーボンリールシート OP-01</t>
+        </is>
+      </c>
+      <c r="AR30" s="41" t="str"/>
+      <c r="AS30" s="41" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
